--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="M2" t="n">
         <v>3.45</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="M4" t="n">
         <v>3.55</v>
       </c>
       <c r="N4" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="M17" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="O17" t="n">
         <v>7.1</v>
@@ -2489,10 +2489,10 @@
         <v>3.28</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AC17" t="n">
         <v>3.45</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Gent II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5113,10 +5113,10 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5232,10 +5232,10 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G59" t="n">

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Western Sydney Wanderers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Western Sydney Wanderers</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Gent II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Gent II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5232,10 +5232,10 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5470,10 +5470,10 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G59" t="n">

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Western Sydney Wanderers</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Western Sydney Wanderers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Gent II</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Gent II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4994,10 +4994,10 @@
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5470,10 +5470,10 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G59" t="n">

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Western Sydney Wanderers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Western Sydney Wanderers</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Gent II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Gent II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4994,10 +4994,10 @@
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5113,10 +5113,10 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G59" t="n">

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gent II</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5113,10 +5113,10 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5470,10 +5470,10 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G59" t="n">

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Western Sydney Wanderers</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Western Sydney Wanderers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5113,10 +5113,10 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5470,10 +5470,10 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G59" t="n">

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G59" t="n">

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Western Sydney Wanderers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Western Sydney Wanderers</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G59" t="n">

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Western Sydney Wanderers</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Western Sydney Wanderers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5113,10 +5113,10 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5351,10 +5351,10 @@
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G59" t="n">

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Western Sydney Wanderers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Western Sydney Wanderers</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5232,10 +5232,10 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5351,10 +5351,10 @@
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,10 +5776,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="M45" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N45" t="n">
         <v>2.55</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="M50" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="N50" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G59" t="n">

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="M17" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="N17" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="O17" t="n">
         <v>7.1</v>
@@ -2489,10 +2489,10 @@
         <v>3.28</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="AC17" t="n">
         <v>3.45</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.8</v>
+        <v>1.86</v>
       </c>
       <c r="M43" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N43" t="n">
-        <v>2.55</v>
+        <v>3.77</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="M45" t="n">
-        <v>3.25</v>
+        <v>2.91</v>
       </c>
       <c r="N45" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G59" t="n">

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="M21" t="n">
         <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N33" t="n">
         <v>3.55</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.86</v>
+        <v>2.63</v>
       </c>
       <c r="M43" t="n">
-        <v>3.15</v>
+        <v>2.91</v>
       </c>
       <c r="N43" t="n">
-        <v>3.77</v>
+        <v>2.53</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="M45" t="n">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="N45" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.65</v>
+        <v>1.86</v>
       </c>
       <c r="M46" t="n">
         <v>3.15</v>
       </c>
       <c r="N46" t="n">
-        <v>2.6</v>
+        <v>3.77</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G59" t="n">

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI59"/>
+  <dimension ref="A1:AI61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1561,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46010.41666666666</v>
+        <v>46010.40625</v>
       </c>
     </row>
     <row r="10">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46010.44791666666</v>
+        <v>46010.41666666666</v>
       </c>
     </row>
     <row r="15">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46010.47916666666</v>
+        <v>46010.44791666666</v>
       </c>
     </row>
     <row r="16">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46010.5</v>
+        <v>46010.47916666666</v>
       </c>
     </row>
     <row r="17">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,76 +2444,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>46010.52083333334</v>
+        <v>46010.5</v>
       </c>
     </row>
     <row r="18">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46010.58333333334</v>
+        <v>46010.51041666666</v>
       </c>
     </row>
     <row r="19">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,76 +2682,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>46010.58333333334</v>
+        <v>46010.52083333334</v>
       </c>
     </row>
     <row r="20">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46010.60416666666</v>
+        <v>46010.58333333334</v>
       </c>
     </row>
     <row r="22">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3108,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46010.60416666666</v>
+        <v>46010.58333333334</v>
       </c>
     </row>
     <row r="23">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3346,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46010.61458333334</v>
+        <v>46010.60416666666</v>
       </c>
     </row>
     <row r="25">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>46010.625</v>
+        <v>46010.60416666666</v>
       </c>
     </row>
     <row r="26">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3584,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
-        <v>46010.625</v>
+        <v>46010.61458333334</v>
       </c>
     </row>
     <row r="27">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46010.64583333334</v>
+        <v>46010.625</v>
       </c>
     </row>
     <row r="28">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3822,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
-        <v>46010.66666666666</v>
+        <v>46010.625</v>
       </c>
     </row>
     <row r="29">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
-        <v>46010.66666666666</v>
+        <v>46010.64583333334</v>
       </c>
     </row>
     <row r="30">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N35" t="n">
-        <v>2.89</v>
+        <v>3.55</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4655,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
-        <v>46010.67708333334</v>
+        <v>46010.66666666666</v>
       </c>
     </row>
     <row r="36">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4774,7 +4774,7 @@
         <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
-        <v>46010.67708333334</v>
+        <v>46010.66666666666</v>
       </c>
     </row>
     <row r="37">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4893,7 +4893,7 @@
         <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
-        <v>46010.6875</v>
+        <v>46010.67708333334</v>
       </c>
     </row>
     <row r="38">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
-        <v>46010.6875</v>
+        <v>46010.67708333334</v>
       </c>
     </row>
     <row r="39">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5232,10 +5232,10 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.63</v>
+        <v>1.48</v>
       </c>
       <c r="M43" t="n">
-        <v>2.91</v>
+        <v>4.6</v>
       </c>
       <c r="N43" t="n">
-        <v>2.53</v>
+        <v>5.7</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,16 +5583,16 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -5607,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
-        <v>46010.69791666666</v>
+        <v>46010.6875</v>
       </c>
     </row>
     <row r="44">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5726,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
-        <v>46010.69791666666</v>
+        <v>46010.6875</v>
       </c>
     </row>
     <row r="45">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="M45" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N45" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.86</v>
+        <v>2.55</v>
       </c>
       <c r="M46" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N46" t="n">
-        <v>3.77</v>
+        <v>2.55</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.42</v>
+        <v>2.63</v>
       </c>
       <c r="M49" t="n">
-        <v>3.09</v>
+        <v>2.91</v>
       </c>
       <c r="N49" t="n">
-        <v>3</v>
+        <v>2.53</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="AI49" s="3" t="n">
-        <v>46010.70833333334</v>
+        <v>46010.69791666666</v>
       </c>
     </row>
     <row r="50">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6440,7 +6440,7 @@
         <v>0</v>
       </c>
       <c r="AI50" s="3" t="n">
-        <v>46010.70833333334</v>
+        <v>46010.69791666666</v>
       </c>
     </row>
     <row r="51">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         <v>0</v>
       </c>
       <c r="AI51" s="3" t="n">
-        <v>46010.71875</v>
+        <v>46010.70833333334</v>
       </c>
     </row>
     <row r="52">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6678,7 +6678,7 @@
         <v>0</v>
       </c>
       <c r="AI52" s="3" t="n">
-        <v>46010.875</v>
+        <v>46010.70833333334</v>
       </c>
     </row>
     <row r="53">
@@ -6687,12 +6687,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="AI53" s="3" t="n">
-        <v>46010.875</v>
+        <v>46010.71875</v>
       </c>
     </row>
     <row r="54">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7511,6 +7511,244 @@
         <v>0</v>
       </c>
       <c r="AI59" s="3" t="n">
+        <v>46010.875</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Serbia SuperLiga</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>IMT Novi Beograd</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Partizan</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI60" s="3" t="n">
+        <v>46010.875</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Serbia SuperLiga</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Napredak</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Radnički Kragujevac</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3" t="n">
         <v>46010.875</v>
       </c>
     </row>

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Western Sydney Wanderers</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Western Sydney Wanderers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="M24" t="n">
         <v>3.6</v>
       </c>
       <c r="N24" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4042,10 +4042,10 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5232,10 +5232,10 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5589,10 +5589,10 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.65</v>
+        <v>1.86</v>
       </c>
       <c r="M45" t="n">
         <v>3.15</v>
       </c>
       <c r="N45" t="n">
-        <v>2.6</v>
+        <v>3.77</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="M46" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N46" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="M49" t="n">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="N49" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G61" t="n">

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6</v>
+        <v>3.02</v>
       </c>
       <c r="N23" t="n">
-        <v>3.4</v>
+        <v>3.83</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="M24" t="n">
         <v>3.6</v>
       </c>
       <c r="N24" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5.9</v>
+        <v>1.95</v>
       </c>
       <c r="M30" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>1.45</v>
+        <v>3.55</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4042,10 +4042,10 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.93</v>
+        <v>5.9</v>
       </c>
       <c r="M36" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="N36" t="n">
-        <v>3.55</v>
+        <v>1.45</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4756,10 +4756,10 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.65</v>
+        <v>1.86</v>
       </c>
       <c r="M46" t="n">
         <v>3.15</v>
       </c>
       <c r="N46" t="n">
-        <v>2.6</v>
+        <v>3.77</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G61" t="n">

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Western Sydney Wanderers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Western Sydney Wanderers</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.95</v>
+        <v>5.9</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N30" t="n">
-        <v>3.55</v>
+        <v>1.45</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4042,10 +4042,10 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4756,10 +4756,10 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5232,10 +5232,10 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5351,10 +5351,10 @@
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.86</v>
+        <v>2.65</v>
       </c>
       <c r="M46" t="n">
         <v>3.15</v>
       </c>
       <c r="N46" t="n">
-        <v>3.77</v>
+        <v>2.6</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.55</v>
+        <v>1.86</v>
       </c>
       <c r="M48" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N48" t="n">
-        <v>2.55</v>
+        <v>3.77</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G60" t="n">

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5.9</v>
+        <v>1.95</v>
       </c>
       <c r="M30" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>1.45</v>
+        <v>3.55</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4042,10 +4042,10 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4161,10 +4161,10 @@
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,10 +4586,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N35" t="n">
         <v>3.55</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5232,10 +5232,10 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5351,10 +5351,10 @@
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.65</v>
+        <v>1.86</v>
       </c>
       <c r="M46" t="n">
         <v>3.15</v>
       </c>
       <c r="N46" t="n">
-        <v>2.6</v>
+        <v>3.77</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="M49" t="n">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="N49" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G61" t="n">

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N30" t="n">
         <v>3.55</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4161,10 +4161,10 @@
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4399,10 +4399,10 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5232,10 +5232,10 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5470,10 +5470,10 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.86</v>
+        <v>2.65</v>
       </c>
       <c r="M46" t="n">
         <v>3.15</v>
       </c>
       <c r="N46" t="n">
-        <v>3.77</v>
+        <v>2.6</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="M47" t="n">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="N47" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G60" t="n">

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>3.02</v>
       </c>
       <c r="N24" t="n">
-        <v>3.4</v>
+        <v>3.83</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="M30" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
         <v>3.55</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4399,10 +4399,10 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4756,10 +4756,10 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.12</v>
+        <v>3.64</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>2.89</v>
+        <v>1.79</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5113,10 +5113,10 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5470,10 +5470,10 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.86</v>
+        <v>2.63</v>
       </c>
       <c r="M45" t="n">
-        <v>3.15</v>
+        <v>2.91</v>
       </c>
       <c r="N45" t="n">
-        <v>3.77</v>
+        <v>2.53</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.65</v>
+        <v>1.78</v>
       </c>
       <c r="M46" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="N46" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.55</v>
+        <v>1.86</v>
       </c>
       <c r="M47" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N47" t="n">
-        <v>2.55</v>
+        <v>3.77</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="M48" t="n">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="N48" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G61" t="n">

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.64</v>
+        <v>2.12</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>1.79</v>
+        <v>2.89</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.12</v>
+        <v>3.64</v>
       </c>
       <c r="M38" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>2.89</v>
+        <v>1.79</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.48</v>
+        <v>2.58</v>
       </c>
       <c r="M39" t="n">
-        <v>4.6</v>
+        <v>3.06</v>
       </c>
       <c r="N39" t="n">
-        <v>5.7</v>
+        <v>2.81</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,16 +5107,16 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5470,10 +5470,10 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.63</v>
+        <v>1.78</v>
       </c>
       <c r="M45" t="n">
-        <v>2.91</v>
+        <v>3.17</v>
       </c>
       <c r="N45" t="n">
-        <v>2.53</v>
+        <v>4.1</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="M46" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="N46" t="n">
-        <v>4.1</v>
+        <v>3.77</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="M47" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="N47" t="n">
-        <v>3.77</v>
+        <v>3.59</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.9</v>
+        <v>2.63</v>
       </c>
       <c r="M49" t="n">
-        <v>3.19</v>
+        <v>2.91</v>
       </c>
       <c r="N49" t="n">
-        <v>3.59</v>
+        <v>2.53</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G61" t="n">

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4161,10 +4161,10 @@
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4756,10 +4756,10 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.12</v>
+        <v>3.64</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>2.89</v>
+        <v>1.79</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.64</v>
+        <v>2.12</v>
       </c>
       <c r="M38" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>1.79</v>
+        <v>2.89</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5351,10 +5351,10 @@
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5470,10 +5470,10 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.78</v>
+        <v>2.63</v>
       </c>
       <c r="M45" t="n">
-        <v>3.17</v>
+        <v>2.91</v>
       </c>
       <c r="N45" t="n">
-        <v>4.1</v>
+        <v>2.53</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.55</v>
+        <v>1.78</v>
       </c>
       <c r="M48" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="N48" t="n">
-        <v>2.55</v>
+        <v>4.1</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="M49" t="n">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="N49" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G61" t="n">

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI61"/>
+  <dimension ref="A1:AI47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46010.44791666666</v>
+        <v>46010.5</v>
       </c>
     </row>
     <row r="16">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46010.47916666666</v>
+        <v>46010.51041666666</v>
       </c>
     </row>
     <row r="17">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,76 +2444,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>46010.5</v>
+        <v>46010.52083333334</v>
       </c>
     </row>
     <row r="18">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46010.51041666666</v>
+        <v>46010.58333333334</v>
       </c>
     </row>
     <row r="19">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,76 +2682,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>46010.52083333334</v>
+        <v>46010.58333333334</v>
       </c>
     </row>
     <row r="20">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46010.58333333334</v>
+        <v>46010.60416666666</v>
       </c>
     </row>
     <row r="22">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3108,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46010.58333333334</v>
+        <v>46010.60416666666</v>
       </c>
     </row>
     <row r="23">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>46010.60416666666</v>
+        <v>46010.61458333334</v>
       </c>
     </row>
     <row r="24">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3346,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46010.60416666666</v>
+        <v>46010.625</v>
       </c>
     </row>
     <row r="25">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>46010.60416666666</v>
+        <v>46010.64583333334</v>
       </c>
     </row>
     <row r="26">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3584,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
-        <v>46010.61458333334</v>
+        <v>46010.66666666666</v>
       </c>
     </row>
     <row r="27">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46010.625</v>
+        <v>46010.66666666666</v>
       </c>
     </row>
     <row r="28">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3822,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
-        <v>46010.625</v>
+        <v>46010.66666666666</v>
       </c>
     </row>
     <row r="29">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3923,10 +3923,10 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
-        <v>46010.64583333334</v>
+        <v>46010.66666666666</v>
       </c>
     </row>
     <row r="30">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>5.9</v>
+        <v>1.95</v>
       </c>
       <c r="M31" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>1.45</v>
+        <v>3.55</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4161,10 +4161,10 @@
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4307,12 +4307,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4417,7 +4417,7 @@
         <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
-        <v>46010.66666666666</v>
+        <v>46010.67708333334</v>
       </c>
     </row>
     <row r="34">
@@ -4426,12 +4426,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
-        <v>46010.66666666666</v>
+        <v>46010.67708333334</v>
       </c>
     </row>
     <row r="35">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4655,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
-        <v>46010.66666666666</v>
+        <v>46010.6875</v>
       </c>
     </row>
     <row r="36">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
-        <v>46010.66666666666</v>
+        <v>46010.6875</v>
       </c>
     </row>
     <row r="37">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.64</v>
+        <v>1.48</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="N37" t="n">
-        <v>1.79</v>
+        <v>5.7</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4875,10 +4875,10 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
-        <v>46010.67708333334</v>
+        <v>46010.6875</v>
       </c>
     </row>
     <row r="38">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
-        <v>46010.67708333334</v>
+        <v>46010.6875</v>
       </c>
     </row>
     <row r="39">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5250,7 +5250,7 @@
         <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
-        <v>46010.6875</v>
+        <v>46010.69791666666</v>
       </c>
     </row>
     <row r="41">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.48</v>
+        <v>2.26</v>
       </c>
       <c r="M41" t="n">
-        <v>4.6</v>
+        <v>2.83</v>
       </c>
       <c r="N41" t="n">
-        <v>5.7</v>
+        <v>3.08</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,16 +5345,16 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -5369,7 +5369,7 @@
         <v>0</v>
       </c>
       <c r="AI41" s="3" t="n">
-        <v>46010.6875</v>
+        <v>46010.69791666666</v>
       </c>
     </row>
     <row r="42">
@@ -5378,12 +5378,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5488,7 +5488,7 @@
         <v>0</v>
       </c>
       <c r="AI42" s="3" t="n">
-        <v>46010.6875</v>
+        <v>46010.69791666666</v>
       </c>
     </row>
     <row r="43">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="M43" t="n">
-        <v>3.06</v>
+        <v>2.91</v>
       </c>
       <c r="N43" t="n">
-        <v>2.81</v>
+        <v>2.53</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5607,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
-        <v>46010.6875</v>
+        <v>46010.69791666666</v>
       </c>
     </row>
     <row r="44">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.19</v>
+        <v>1.78</v>
       </c>
       <c r="M44" t="n">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="N44" t="n">
-        <v>3.39</v>
+        <v>4.1</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5726,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
-        <v>46010.6875</v>
+        <v>46010.69791666666</v>
       </c>
     </row>
     <row r="45">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.63</v>
+        <v>1.86</v>
       </c>
       <c r="M45" t="n">
-        <v>2.91</v>
+        <v>3.15</v>
       </c>
       <c r="N45" t="n">
-        <v>2.53</v>
+        <v>3.77</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5854,12 +5854,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.86</v>
+        <v>2.42</v>
       </c>
       <c r="M46" t="n">
-        <v>3.15</v>
+        <v>3.09</v>
       </c>
       <c r="N46" t="n">
-        <v>3.77</v>
+        <v>3</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5943,7 +5943,7 @@
         <v>2.15</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
         <v>0</v>
       </c>
       <c r="AI46" s="3" t="n">
-        <v>46010.69791666666</v>
+        <v>46010.70833333334</v>
       </c>
     </row>
     <row r="47">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="M47" t="n">
-        <v>3.19</v>
+        <v>3.45</v>
       </c>
       <c r="N47" t="n">
-        <v>3.59</v>
+        <v>1.92</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6083,1673 +6083,7 @@
         <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
-        <v>46010.69791666666</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>England EFL League Two</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Crewe Alexandra</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Bristol Rovers</t>
-        </is>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L48" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="M48" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="N48" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI48" s="3" t="n">
-        <v>46010.69791666666</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Northern Ireland NIFL Premiership</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Glentoran</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Coleraine</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L49" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="M49" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N49" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI49" s="3" t="n">
-        <v>46010.69791666666</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>England EFL League One</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Northampton Town</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>AFC Wimbledon</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L50" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="M50" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="N50" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" t="n">
-        <v>0</v>
-      </c>
-      <c r="W50" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI50" s="3" t="n">
-        <v>46010.69791666666</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Spain La Liga</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Valencia CF</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>RCD Mallorca</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI51" s="3" t="n">
-        <v>46010.70833333334</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>England Championship</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Swansea City</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Wrexham</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L52" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="M52" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="N52" t="n">
-        <v>3</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" t="n">
-        <v>0</v>
-      </c>
-      <c r="W52" t="n">
-        <v>0</v>
-      </c>
-      <c r="X52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI52" s="3" t="n">
-        <v>46010.70833333334</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Portugal Liga NOS</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>GD Estoril Praia</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Sporting Braga</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L53" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="M53" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N53" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI53" s="3" t="n">
         <v>46010.71875</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Serbia SuperLiga</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Javor Ivanjica</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Vojvodina</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI54" s="3" t="n">
-        <v>46010.875</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Serbia SuperLiga</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>OFK Beograd</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Bačka Topola</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI55" s="3" t="n">
-        <v>46010.875</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Serbia SuperLiga</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>IMT Novi Beograd</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Partizan</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" t="n">
-        <v>0</v>
-      </c>
-      <c r="W56" t="n">
-        <v>0</v>
-      </c>
-      <c r="X56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI56" s="3" t="n">
-        <v>46010.875</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Serbia SuperLiga</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Radnički Niš</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Železničar Pančevo</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" t="n">
-        <v>0</v>
-      </c>
-      <c r="W57" t="n">
-        <v>0</v>
-      </c>
-      <c r="X57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI57" s="3" t="n">
-        <v>46010.875</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Serbia SuperLiga</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Red Star Belgrade</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>LFK Mladost Lučani</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" t="n">
-        <v>0</v>
-      </c>
-      <c r="W58" t="n">
-        <v>0</v>
-      </c>
-      <c r="X58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI58" s="3" t="n">
-        <v>46010.875</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Serbia SuperLiga</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Napredak</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Radnički Kragujevac</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" t="n">
-        <v>0</v>
-      </c>
-      <c r="W59" t="n">
-        <v>0</v>
-      </c>
-      <c r="X59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI59" s="3" t="n">
-        <v>46010.875</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Serbia SuperLiga</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Radnik Surdulica</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Novi Pazar</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" t="n">
-        <v>0</v>
-      </c>
-      <c r="W60" t="n">
-        <v>0</v>
-      </c>
-      <c r="X60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI60" s="3" t="n">
-        <v>46010.875</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Serbia SuperLiga</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Spartak Subotica</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Čukarički</t>
-        </is>
-      </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" t="n">
-        <v>0</v>
-      </c>
-      <c r="W61" t="n">
-        <v>0</v>
-      </c>
-      <c r="X61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI61" s="3" t="n">
-        <v>46010.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI47"/>
+  <dimension ref="A1:AI61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46010.5</v>
+        <v>46010.44791666666</v>
       </c>
     </row>
     <row r="16">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46010.51041666666</v>
+        <v>46010.47916666666</v>
       </c>
     </row>
     <row r="17">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,76 +2444,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>46010.52083333334</v>
+        <v>46010.5</v>
       </c>
     </row>
     <row r="18">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46010.58333333334</v>
+        <v>46010.51041666666</v>
       </c>
     </row>
     <row r="19">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,76 +2682,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>46010.58333333334</v>
+        <v>46010.52083333334</v>
       </c>
     </row>
     <row r="20">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46010.60416666666</v>
+        <v>46010.58333333334</v>
       </c>
     </row>
     <row r="22">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3108,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46010.60416666666</v>
+        <v>46010.58333333334</v>
       </c>
     </row>
     <row r="23">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>46010.61458333334</v>
+        <v>46010.60416666666</v>
       </c>
     </row>
     <row r="24">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3346,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46010.625</v>
+        <v>46010.60416666666</v>
       </c>
     </row>
     <row r="25">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>46010.64583333334</v>
+        <v>46010.60416666666</v>
       </c>
     </row>
     <row r="26">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3584,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
-        <v>46010.66666666666</v>
+        <v>46010.61458333334</v>
       </c>
     </row>
     <row r="27">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46010.66666666666</v>
+        <v>46010.625</v>
       </c>
     </row>
     <row r="28">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
-        <v>46010.66666666666</v>
+        <v>46010.625</v>
       </c>
     </row>
     <row r="29">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5.9</v>
+        <v>3.59</v>
       </c>
       <c r="M29" t="n">
-        <v>4.5</v>
+        <v>3.58</v>
       </c>
       <c r="N29" t="n">
-        <v>1.45</v>
+        <v>1.92</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3923,10 +3923,10 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
-        <v>46010.66666666666</v>
+        <v>46010.64583333334</v>
       </c>
     </row>
     <row r="30">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,10 +4229,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="M32" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
         <v>3.55</v>
@@ -4307,12 +4307,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N33" t="n">
-        <v>2.89</v>
+        <v>3.55</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4417,7 +4417,7 @@
         <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
-        <v>46010.67708333334</v>
+        <v>46010.66666666666</v>
       </c>
     </row>
     <row r="34">
@@ -4426,12 +4426,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.64</v>
+        <v>5.9</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N34" t="n">
-        <v>1.79</v>
+        <v>1.45</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4518,10 +4518,10 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
-        <v>46010.67708333334</v>
+        <v>46010.66666666666</v>
       </c>
     </row>
     <row r="35">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4655,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
-        <v>46010.6875</v>
+        <v>46010.66666666666</v>
       </c>
     </row>
     <row r="36">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
-        <v>46010.6875</v>
+        <v>46010.66666666666</v>
       </c>
     </row>
     <row r="37">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.48</v>
+        <v>3.64</v>
       </c>
       <c r="M37" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>5.7</v>
+        <v>1.79</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,16 +4869,16 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
-        <v>46010.6875</v>
+        <v>46010.67708333334</v>
       </c>
     </row>
     <row r="38">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
-        <v>46010.6875</v>
+        <v>46010.67708333334</v>
       </c>
     </row>
     <row r="39">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5113,10 +5113,10 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
@@ -5140,12 +5140,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5250,7 +5250,7 @@
         <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
-        <v>46010.69791666666</v>
+        <v>46010.6875</v>
       </c>
     </row>
     <row r="41">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5369,7 +5369,7 @@
         <v>0</v>
       </c>
       <c r="AI41" s="3" t="n">
-        <v>46010.69791666666</v>
+        <v>46010.6875</v>
       </c>
     </row>
     <row r="42">
@@ -5378,12 +5378,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.9</v>
+        <v>2.19</v>
       </c>
       <c r="M42" t="n">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="N42" t="n">
-        <v>3.59</v>
+        <v>3.39</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5488,7 +5488,7 @@
         <v>0</v>
       </c>
       <c r="AI42" s="3" t="n">
-        <v>46010.69791666666</v>
+        <v>46010.6875</v>
       </c>
     </row>
     <row r="43">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="M43" t="n">
-        <v>2.91</v>
+        <v>3.06</v>
       </c>
       <c r="N43" t="n">
-        <v>2.53</v>
+        <v>2.81</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5607,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
-        <v>46010.69791666666</v>
+        <v>46010.6875</v>
       </c>
     </row>
     <row r="44">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5726,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
-        <v>46010.69791666666</v>
+        <v>46010.6875</v>
       </c>
     </row>
     <row r="45">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.42</v>
+        <v>2.26</v>
       </c>
       <c r="M46" t="n">
-        <v>3.09</v>
+        <v>2.83</v>
       </c>
       <c r="N46" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
         <v>0</v>
       </c>
       <c r="AI46" s="3" t="n">
-        <v>46010.70833333334</v>
+        <v>46010.69791666666</v>
       </c>
     </row>
     <row r="47">
@@ -5973,117 +5973,1783 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Crewe Alexandra</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Bristol Rovers</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="M47" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="N47" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" s="3" t="n">
+        <v>46010.69791666666</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Barrow</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Cheltenham Town</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M48" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" s="3" t="n">
+        <v>46010.69791666666</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Belgium Pro League</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Sporting Charleroi</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>KRC Genk</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="M49" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" s="3" t="n">
+        <v>46010.69791666666</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Northern Ireland NIFL Premiership</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Glentoran</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Coleraine</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M50" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3" t="n">
+        <v>46010.69791666666</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Swansea City</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Wrexham</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M51" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="N51" t="n">
+        <v>3</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3" t="n">
+        <v>46010.70833333334</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Valencia CF</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>RCD Mallorca</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="3" t="n">
+        <v>46010.70833333334</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Portugal Liga NOS</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>GD Estoril Praia</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Sporting Braga</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="inlineStr">
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L47" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="M47" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N47" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI47" s="3" t="n">
+      <c r="L53" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M53" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N53" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3" t="n">
         <v>46010.71875</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Serbia SuperLiga</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Radnik Surdulica</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Novi Pazar</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI54" s="3" t="n">
+        <v>46010.875</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Serbia SuperLiga</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Spartak Subotica</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Čukarički</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI55" s="3" t="n">
+        <v>46010.875</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Serbia SuperLiga</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Red Star Belgrade</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>LFK Mladost Lučani</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI56" s="3" t="n">
+        <v>46010.875</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Serbia SuperLiga</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Napredak</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Radnički Kragujevac</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI57" s="3" t="n">
+        <v>46010.875</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Serbia SuperLiga</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Javor Ivanjica</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vojvodina</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="3" t="n">
+        <v>46010.875</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Serbia SuperLiga</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>IMT Novi Beograd</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Partizan</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI59" s="3" t="n">
+        <v>46010.875</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Serbia SuperLiga</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Radnički Niš</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Železničar Pančevo</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI60" s="3" t="n">
+        <v>46010.875</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Serbia SuperLiga</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>OFK Beograd</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Bačka Topola</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3" t="n">
+        <v>46010.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="M23" t="n">
-        <v>3.52</v>
+        <v>3.02</v>
       </c>
       <c r="N23" t="n">
-        <v>3.4</v>
+        <v>3.83</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3206,7 +3206,7 @@
         <v>1.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4518,10 +4518,10 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4756,10 +4756,10 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.48</v>
+        <v>2.19</v>
       </c>
       <c r="M39" t="n">
-        <v>4.6</v>
+        <v>3.14</v>
       </c>
       <c r="N39" t="n">
-        <v>5.7</v>
+        <v>3.39</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,16 +5107,16 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,16 +5345,16 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.86</v>
+        <v>2.26</v>
       </c>
       <c r="M45" t="n">
-        <v>3.15</v>
+        <v>2.83</v>
       </c>
       <c r="N45" t="n">
-        <v>3.77</v>
+        <v>3.08</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.26</v>
+        <v>1.78</v>
       </c>
       <c r="M46" t="n">
-        <v>2.83</v>
+        <v>3.17</v>
       </c>
       <c r="N46" t="n">
-        <v>3.08</v>
+        <v>4.1</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="M47" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="N47" t="n">
-        <v>4.1</v>
+        <v>3.59</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.9</v>
+        <v>2.63</v>
       </c>
       <c r="M48" t="n">
-        <v>3.19</v>
+        <v>2.91</v>
       </c>
       <c r="N48" t="n">
-        <v>3.59</v>
+        <v>2.53</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="M49" t="n">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="N49" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.55</v>
+        <v>1.86</v>
       </c>
       <c r="M50" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N50" t="n">
-        <v>2.55</v>
+        <v>3.77</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G61" t="n">

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Western Sydney Wanderers</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Western Sydney Wanderers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N30" t="n">
         <v>3.55</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="M33" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
         <v>3.55</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4518,10 +4518,10 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4756,10 +4756,10 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.64</v>
+        <v>2.12</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>1.79</v>
+        <v>2.89</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.12</v>
+        <v>3.64</v>
       </c>
       <c r="M38" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>2.89</v>
+        <v>1.79</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.19</v>
+        <v>2.58</v>
       </c>
       <c r="M39" t="n">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="N39" t="n">
-        <v>3.39</v>
+        <v>2.81</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,16 +5345,16 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,16 +5702,16 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.26</v>
+        <v>2.63</v>
       </c>
       <c r="M45" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="N45" t="n">
-        <v>3.08</v>
+        <v>2.53</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="M47" t="n">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="N47" t="n">
-        <v>3.59</v>
+        <v>3.77</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.63</v>
+        <v>2.26</v>
       </c>
       <c r="M48" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="N48" t="n">
-        <v>2.53</v>
+        <v>3.08</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="M50" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="N50" t="n">
-        <v>3.77</v>
+        <v>3.59</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G61" t="n">

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="M24" t="n">
-        <v>3.52</v>
+        <v>3.02</v>
       </c>
       <c r="N24" t="n">
-        <v>3.4</v>
+        <v>3.83</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3325,7 +3325,7 @@
         <v>1.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="M25" t="n">
-        <v>3.02</v>
+        <v>3.52</v>
       </c>
       <c r="N25" t="n">
-        <v>3.83</v>
+        <v>3.4</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3444,7 +3444,7 @@
         <v>1.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.93</v>
+        <v>5.9</v>
       </c>
       <c r="M30" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="N30" t="n">
-        <v>3.55</v>
+        <v>1.45</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4042,10 +4042,10 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5.9</v>
+        <v>1.93</v>
       </c>
       <c r="M34" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="N34" t="n">
-        <v>1.45</v>
+        <v>3.55</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4518,10 +4518,10 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.12</v>
+        <v>3.64</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>2.89</v>
+        <v>1.79</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.64</v>
+        <v>2.12</v>
       </c>
       <c r="M38" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>1.79</v>
+        <v>2.89</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.58</v>
+        <v>1.48</v>
       </c>
       <c r="M39" t="n">
-        <v>3.06</v>
+        <v>4.6</v>
       </c>
       <c r="N39" t="n">
-        <v>2.81</v>
+        <v>5.7</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,16 +5107,16 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.65</v>
+        <v>2.45</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.48</v>
+        <v>2.58</v>
       </c>
       <c r="M44" t="n">
-        <v>4.6</v>
+        <v>3.06</v>
       </c>
       <c r="N44" t="n">
-        <v>5.7</v>
+        <v>2.81</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,16 +5702,16 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.45</v>
+        <v>1.65</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.63</v>
+        <v>1.78</v>
       </c>
       <c r="M45" t="n">
-        <v>2.91</v>
+        <v>3.17</v>
       </c>
       <c r="N45" t="n">
-        <v>2.53</v>
+        <v>4.1</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.78</v>
+        <v>2.26</v>
       </c>
       <c r="M46" t="n">
-        <v>3.17</v>
+        <v>2.83</v>
       </c>
       <c r="N46" t="n">
-        <v>4.1</v>
+        <v>3.08</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="M47" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="N47" t="n">
-        <v>3.77</v>
+        <v>3.59</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.26</v>
+        <v>2.63</v>
       </c>
       <c r="M48" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="N48" t="n">
-        <v>3.08</v>
+        <v>2.53</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="M50" t="n">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="N50" t="n">
-        <v>3.59</v>
+        <v>3.77</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G61" t="n">

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5.9</v>
+        <v>1.95</v>
       </c>
       <c r="M30" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>1.45</v>
+        <v>3.55</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4042,10 +4042,10 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N31" t="n">
         <v>3.55</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4399,10 +4399,10 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.48</v>
+        <v>2.58</v>
       </c>
       <c r="M39" t="n">
-        <v>4.6</v>
+        <v>3.06</v>
       </c>
       <c r="N39" t="n">
-        <v>5.7</v>
+        <v>2.81</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,16 +5107,16 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.45</v>
+        <v>1.65</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.58</v>
+        <v>1.48</v>
       </c>
       <c r="M44" t="n">
-        <v>3.06</v>
+        <v>4.6</v>
       </c>
       <c r="N44" t="n">
-        <v>2.81</v>
+        <v>5.7</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,16 +5702,16 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.65</v>
+        <v>2.45</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.78</v>
+        <v>2.63</v>
       </c>
       <c r="M45" t="n">
-        <v>3.17</v>
+        <v>2.91</v>
       </c>
       <c r="N45" t="n">
-        <v>4.1</v>
+        <v>2.53</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.26</v>
+        <v>1.78</v>
       </c>
       <c r="M46" t="n">
-        <v>2.83</v>
+        <v>3.17</v>
       </c>
       <c r="N46" t="n">
-        <v>3.08</v>
+        <v>4.1</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="M47" t="n">
-        <v>3.19</v>
+        <v>2.83</v>
       </c>
       <c r="N47" t="n">
-        <v>3.59</v>
+        <v>3.08</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.63</v>
+        <v>1.86</v>
       </c>
       <c r="M48" t="n">
-        <v>2.91</v>
+        <v>3.15</v>
       </c>
       <c r="N48" t="n">
-        <v>2.53</v>
+        <v>3.77</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="M49" t="n">
-        <v>3.25</v>
+        <v>3.19</v>
       </c>
       <c r="N49" t="n">
-        <v>2.55</v>
+        <v>3.59</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.86</v>
+        <v>2.55</v>
       </c>
       <c r="M50" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N50" t="n">
-        <v>3.77</v>
+        <v>2.55</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G61" t="n">

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Western Sydney Wanderers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Western Sydney Wanderers</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="M4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>1.76</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1424,10 +1424,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2138,10 +2138,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.59</v>
+        <v>3.45</v>
       </c>
       <c r="M29" t="n">
-        <v>3.58</v>
+        <v>3.41</v>
       </c>
       <c r="N29" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4399,10 +4399,10 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.64</v>
+        <v>2.12</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>1.79</v>
+        <v>2.89</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.12</v>
+        <v>3.64</v>
       </c>
       <c r="M38" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>2.89</v>
+        <v>1.79</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.58</v>
+        <v>1.48</v>
       </c>
       <c r="M39" t="n">
-        <v>3.06</v>
+        <v>4.6</v>
       </c>
       <c r="N39" t="n">
-        <v>2.81</v>
+        <v>5.7</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,16 +5107,16 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.65</v>
+        <v>2.45</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.48</v>
+        <v>2.58</v>
       </c>
       <c r="M44" t="n">
-        <v>4.6</v>
+        <v>3.06</v>
       </c>
       <c r="N44" t="n">
-        <v>5.7</v>
+        <v>2.81</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,16 +5702,16 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.45</v>
+        <v>1.65</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.63</v>
+        <v>2.26</v>
       </c>
       <c r="M45" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="N45" t="n">
-        <v>2.53</v>
+        <v>3.08</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.78</v>
+        <v>2.63</v>
       </c>
       <c r="M46" t="n">
-        <v>3.17</v>
+        <v>2.91</v>
       </c>
       <c r="N46" t="n">
-        <v>4.1</v>
+        <v>2.53</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.26</v>
+        <v>2.55</v>
       </c>
       <c r="M47" t="n">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="N47" t="n">
-        <v>3.08</v>
+        <v>2.55</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="M48" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="N48" t="n">
-        <v>3.77</v>
+        <v>4.1</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.55</v>
+        <v>1.86</v>
       </c>
       <c r="M50" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N50" t="n">
-        <v>2.55</v>
+        <v>3.77</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G61" t="n">

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2138,10 +2138,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>5.8</v>
+        <v>1.95</v>
       </c>
       <c r="M32" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>1.37</v>
+        <v>3.55</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.95</v>
+        <v>5.8</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="N35" t="n">
-        <v>3.55</v>
+        <v>1.37</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,16 +4631,16 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.12</v>
+        <v>3.64</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>2.89</v>
+        <v>1.79</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.64</v>
+        <v>2.12</v>
       </c>
       <c r="M38" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>1.79</v>
+        <v>2.89</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.48</v>
+        <v>2.19</v>
       </c>
       <c r="M39" t="n">
-        <v>4.6</v>
+        <v>3.14</v>
       </c>
       <c r="N39" t="n">
-        <v>5.7</v>
+        <v>3.39</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,16 +5107,16 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.45</v>
+        <v>1.6</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.58</v>
+        <v>1.48</v>
       </c>
       <c r="M44" t="n">
-        <v>3.06</v>
+        <v>4.6</v>
       </c>
       <c r="N44" t="n">
-        <v>2.81</v>
+        <v>5.7</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,16 +5702,16 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.65</v>
+        <v>2.45</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.26</v>
+        <v>1.86</v>
       </c>
       <c r="M45" t="n">
-        <v>2.83</v>
+        <v>3.15</v>
       </c>
       <c r="N45" t="n">
-        <v>3.08</v>
+        <v>3.77</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.63</v>
+        <v>1.78</v>
       </c>
       <c r="M46" t="n">
-        <v>2.91</v>
+        <v>3.17</v>
       </c>
       <c r="N46" t="n">
-        <v>2.53</v>
+        <v>4.1</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="M47" t="n">
-        <v>3.25</v>
+        <v>2.91</v>
       </c>
       <c r="N47" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.78</v>
+        <v>2.55</v>
       </c>
       <c r="M48" t="n">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="N48" t="n">
-        <v>4.1</v>
+        <v>2.55</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="M49" t="n">
-        <v>3.19</v>
+        <v>2.83</v>
       </c>
       <c r="N49" t="n">
-        <v>3.59</v>
+        <v>3.08</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="M50" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="N50" t="n">
-        <v>3.77</v>
+        <v>3.59</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G61" t="n">

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Western Sydney Wanderers</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>2.35</v>
+        <v>1.76</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Western Sydney Wanderers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N4" t="n">
-        <v>1.76</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2483,10 +2483,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,16 +4631,16 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.64</v>
+        <v>2.12</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>1.79</v>
+        <v>2.89</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.12</v>
+        <v>3.64</v>
       </c>
       <c r="M38" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>2.89</v>
+        <v>1.79</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.19</v>
+        <v>1.48</v>
       </c>
       <c r="M39" t="n">
-        <v>3.14</v>
+        <v>4.6</v>
       </c>
       <c r="N39" t="n">
-        <v>3.39</v>
+        <v>5.7</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,16 +5107,16 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.6</v>
+        <v>2.45</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.58</v>
+        <v>2.19</v>
       </c>
       <c r="M40" t="n">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="N40" t="n">
-        <v>2.81</v>
+        <v>3.39</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,16 +5702,16 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.86</v>
+        <v>2.26</v>
       </c>
       <c r="M45" t="n">
-        <v>3.15</v>
+        <v>2.83</v>
       </c>
       <c r="N45" t="n">
-        <v>3.77</v>
+        <v>3.08</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.78</v>
+        <v>2.55</v>
       </c>
       <c r="M46" t="n">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="N46" t="n">
-        <v>4.1</v>
+        <v>2.55</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.63</v>
+        <v>1.9</v>
       </c>
       <c r="M47" t="n">
-        <v>2.91</v>
+        <v>3.19</v>
       </c>
       <c r="N47" t="n">
-        <v>2.53</v>
+        <v>3.59</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.55</v>
+        <v>1.86</v>
       </c>
       <c r="M48" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N48" t="n">
-        <v>2.55</v>
+        <v>3.77</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.26</v>
+        <v>1.78</v>
       </c>
       <c r="M49" t="n">
-        <v>2.83</v>
+        <v>3.17</v>
       </c>
       <c r="N49" t="n">
-        <v>3.08</v>
+        <v>4.1</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.9</v>
+        <v>2.63</v>
       </c>
       <c r="M50" t="n">
-        <v>3.19</v>
+        <v>2.91</v>
       </c>
       <c r="N50" t="n">
-        <v>3.59</v>
+        <v>2.53</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G61" t="n">

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI61"/>
+  <dimension ref="A1:AI52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Western Sydney Wanderers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>1.76</v>
+        <v>2.35</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Western Sydney Wanderers</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="M4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>1.76</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46010.41666666666</v>
+        <v>46010.4375</v>
       </c>
     </row>
     <row r="12">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46010.41666666666</v>
+        <v>46010.44791666666</v>
       </c>
     </row>
     <row r="13">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46010.41666666666</v>
+        <v>46010.47916666666</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46010.41666666666</v>
+        <v>46010.5</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46010.44791666666</v>
+        <v>46010.51041666666</v>
       </c>
     </row>
     <row r="16">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,76 +2325,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46010.47916666666</v>
+        <v>46010.52083333334</v>
       </c>
     </row>
     <row r="17">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2483,10 +2483,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>46010.5</v>
+        <v>46010.54166666666</v>
       </c>
     </row>
     <row r="18">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46010.51041666666</v>
+        <v>46010.58333333334</v>
       </c>
     </row>
     <row r="19">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,76 +2682,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>46010.52083333334</v>
+        <v>46010.58333333334</v>
       </c>
     </row>
     <row r="20">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3108,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46010.58333333334</v>
+        <v>46010.60416666666</v>
       </c>
     </row>
     <row r="23">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="M24" t="n">
-        <v>3.02</v>
+        <v>3.52</v>
       </c>
       <c r="N24" t="n">
-        <v>3.83</v>
+        <v>3.4</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3355,12 +3355,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="M25" t="n">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.12</v>
+        <v>1.62</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>46010.60416666666</v>
+        <v>46010.61458333334</v>
       </c>
     </row>
     <row r="26">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.98</v>
+        <v>2.64</v>
       </c>
       <c r="M26" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3563,7 +3563,7 @@
         <v>2.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3584,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
-        <v>46010.61458333334</v>
+        <v>46010.625</v>
       </c>
     </row>
     <row r="27">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.64</v>
+        <v>3.45</v>
       </c>
       <c r="M28" t="n">
-        <v>2.94</v>
+        <v>3.41</v>
       </c>
       <c r="N28" t="n">
-        <v>2.5</v>
+        <v>1.86</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
-        <v>46010.625</v>
+        <v>46010.64583333334</v>
       </c>
     </row>
     <row r="29">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
-        <v>46010.64583333334</v>
+        <v>46010.66666666666</v>
       </c>
     </row>
     <row r="30">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,16 +4631,16 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
-        <v>46010.66666666666</v>
+        <v>46010.67708333334</v>
       </c>
     </row>
     <row r="37">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.12</v>
+        <v>3.64</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>2.89</v>
+        <v>1.79</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4902,12 +4902,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
-        <v>46010.67708333334</v>
+        <v>46010.6875</v>
       </c>
     </row>
     <row r="39">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,16 +5107,16 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.19</v>
+        <v>1.48</v>
       </c>
       <c r="M40" t="n">
-        <v>3.14</v>
+        <v>4.6</v>
       </c>
       <c r="N40" t="n">
-        <v>3.39</v>
+        <v>5.7</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,16 +5226,16 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.6</v>
+        <v>2.45</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5616,12 +5616,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5726,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
-        <v>46010.6875</v>
+        <v>46010.69791666666</v>
       </c>
     </row>
     <row r="45">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.26</v>
+        <v>2.55</v>
       </c>
       <c r="M45" t="n">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="N45" t="n">
-        <v>3.08</v>
+        <v>2.55</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.55</v>
+        <v>1.78</v>
       </c>
       <c r="M46" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="N46" t="n">
-        <v>2.55</v>
+        <v>4.1</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="M47" t="n">
-        <v>3.19</v>
+        <v>2.83</v>
       </c>
       <c r="N47" t="n">
-        <v>3.59</v>
+        <v>3.08</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.86</v>
+        <v>2.63</v>
       </c>
       <c r="M48" t="n">
-        <v>3.15</v>
+        <v>2.91</v>
       </c>
       <c r="N48" t="n">
-        <v>3.77</v>
+        <v>2.53</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="M49" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="N49" t="n">
-        <v>4.1</v>
+        <v>3.59</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6330,12 +6330,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.63</v>
+        <v>2.42</v>
       </c>
       <c r="M50" t="n">
-        <v>2.91</v>
+        <v>3.09</v>
       </c>
       <c r="N50" t="n">
-        <v>2.53</v>
+        <v>3</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6440,7 +6440,7 @@
         <v>0</v>
       </c>
       <c r="AI50" s="3" t="n">
-        <v>46010.69791666666</v>
+        <v>46010.70833333334</v>
       </c>
     </row>
     <row r="51">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6568,12 +6568,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6678,1078 +6678,7 @@
         <v>0</v>
       </c>
       <c r="AI52" s="3" t="n">
-        <v>46010.70833333334</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Portugal Liga NOS</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>GD Estoril Praia</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Sporting Braga</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L53" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="M53" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N53" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI53" s="3" t="n">
         <v>46010.71875</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Serbia SuperLiga</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Javor Ivanjica</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Vojvodina</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI54" s="3" t="n">
-        <v>46010.875</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Serbia SuperLiga</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>OFK Beograd</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Bačka Topola</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI55" s="3" t="n">
-        <v>46010.875</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Serbia SuperLiga</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Spartak Subotica</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Čukarički</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" t="n">
-        <v>0</v>
-      </c>
-      <c r="W56" t="n">
-        <v>0</v>
-      </c>
-      <c r="X56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI56" s="3" t="n">
-        <v>46010.875</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Serbia SuperLiga</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Red Star Belgrade</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>LFK Mladost Lučani</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" t="n">
-        <v>0</v>
-      </c>
-      <c r="W57" t="n">
-        <v>0</v>
-      </c>
-      <c r="X57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI57" s="3" t="n">
-        <v>46010.875</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Serbia SuperLiga</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>IMT Novi Beograd</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Partizan</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" t="n">
-        <v>0</v>
-      </c>
-      <c r="W58" t="n">
-        <v>0</v>
-      </c>
-      <c r="X58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI58" s="3" t="n">
-        <v>46010.875</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Serbia SuperLiga</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Radnik Surdulica</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Novi Pazar</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" t="n">
-        <v>0</v>
-      </c>
-      <c r="W59" t="n">
-        <v>0</v>
-      </c>
-      <c r="X59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI59" s="3" t="n">
-        <v>46010.875</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Serbia SuperLiga</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Napredak</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Radnički Kragujevac</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" t="n">
-        <v>0</v>
-      </c>
-      <c r="W60" t="n">
-        <v>0</v>
-      </c>
-      <c r="X60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI60" s="3" t="n">
-        <v>46010.875</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Serbia SuperLiga</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Radnički Niš</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Železničar Pančevo</t>
-        </is>
-      </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" t="n">
-        <v>0</v>
-      </c>
-      <c r="W61" t="n">
-        <v>0</v>
-      </c>
-      <c r="X61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI61" s="3" t="n">
-        <v>46010.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI52"/>
+  <dimension ref="A1:AI51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Western Sydney Wanderers</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>2.35</v>
+        <v>1.76</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Western Sydney Wanderers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N4" t="n">
-        <v>1.76</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46010.58333333334</v>
+        <v>46010.60416666666</v>
       </c>
     </row>
     <row r="22">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="M23" t="n">
-        <v>3.02</v>
+        <v>3.52</v>
       </c>
       <c r="N23" t="n">
-        <v>3.83</v>
+        <v>3.4</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="M24" t="n">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="N24" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.12</v>
+        <v>1.62</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3346,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46010.60416666666</v>
+        <v>46010.61458333334</v>
       </c>
     </row>
     <row r="25">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>46010.61458333334</v>
+        <v>46010.625</v>
       </c>
     </row>
     <row r="26">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46010.625</v>
+        <v>46010.64583333334</v>
       </c>
     </row>
     <row r="28">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
-        <v>46010.64583333334</v>
+        <v>46010.66666666666</v>
       </c>
     </row>
     <row r="29">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N31" t="n">
         <v>3.55</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -4545,12 +4545,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>5.8</v>
+        <v>3.64</v>
       </c>
       <c r="M35" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="N35" t="n">
-        <v>1.37</v>
+        <v>1.79</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,16 +4631,16 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.43</v>
+        <v>1.95</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -4655,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
-        <v>46010.66666666666</v>
+        <v>46010.67708333334</v>
       </c>
     </row>
     <row r="36">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
-        <v>46010.67708333334</v>
+        <v>46010.6875</v>
       </c>
     </row>
     <row r="38">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,16 +5226,16 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.58</v>
+        <v>1.48</v>
       </c>
       <c r="M42" t="n">
-        <v>3.06</v>
+        <v>4.6</v>
       </c>
       <c r="N42" t="n">
-        <v>2.81</v>
+        <v>5.7</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,16 +5464,16 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.65</v>
+        <v>2.45</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5497,12 +5497,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.19</v>
+        <v>2.63</v>
       </c>
       <c r="M43" t="n">
-        <v>3.14</v>
+        <v>2.91</v>
       </c>
       <c r="N43" t="n">
-        <v>3.39</v>
+        <v>2.53</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5607,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
-        <v>46010.6875</v>
+        <v>46010.69791666666</v>
       </c>
     </row>
     <row r="44">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.86</v>
+        <v>2.55</v>
       </c>
       <c r="M44" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N44" t="n">
-        <v>3.77</v>
+        <v>2.55</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.55</v>
+        <v>1.78</v>
       </c>
       <c r="M45" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="N45" t="n">
-        <v>2.55</v>
+        <v>4.1</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.78</v>
+        <v>2.26</v>
       </c>
       <c r="M46" t="n">
-        <v>3.17</v>
+        <v>2.83</v>
       </c>
       <c r="N46" t="n">
-        <v>4.1</v>
+        <v>3.08</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.26</v>
+        <v>1.9</v>
       </c>
       <c r="M47" t="n">
-        <v>2.83</v>
+        <v>3.19</v>
       </c>
       <c r="N47" t="n">
-        <v>3.08</v>
+        <v>3.59</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.63</v>
+        <v>1.86</v>
       </c>
       <c r="M48" t="n">
-        <v>2.91</v>
+        <v>3.15</v>
       </c>
       <c r="N48" t="n">
-        <v>2.53</v>
+        <v>3.77</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="AI49" s="3" t="n">
-        <v>46010.69791666666</v>
+        <v>46010.70833333334</v>
       </c>
     </row>
     <row r="50">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6559,125 +6559,6 @@
         <v>0</v>
       </c>
       <c r="AI51" s="3" t="n">
-        <v>46010.70833333334</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Portugal Liga NOS</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>GD Estoril Praia</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Sporting Braga</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L52" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="M52" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N52" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" t="n">
-        <v>0</v>
-      </c>
-      <c r="W52" t="n">
-        <v>0</v>
-      </c>
-      <c r="X52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI52" s="3" t="n">
         <v>46010.71875</v>
       </c>
     </row>

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI51"/>
+  <dimension ref="A1:AI52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,40 +668,40 @@
         <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA2" t="n">
         <v>1.75</v>
@@ -710,22 +710,22 @@
         <v>1.95</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46010.16666666666</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Western Sydney Wanderers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>1.76</v>
+        <v>2.35</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46010.25</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Western Sydney Wanderers</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="M4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>1.76</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46010.60416666666</v>
+        <v>46010.58333333334</v>
       </c>
     </row>
     <row r="22">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>3.83</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.62</v>
+        <v>2.17</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3346,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46010.61458333334</v>
+        <v>46010.60416666666</v>
       </c>
     </row>
     <row r="25">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>46010.625</v>
+        <v>46010.61458333334</v>
       </c>
     </row>
     <row r="26">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3593,12 +3593,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.45</v>
+        <v>2.64</v>
       </c>
       <c r="M27" t="n">
-        <v>3.41</v>
+        <v>2.94</v>
       </c>
       <c r="N27" t="n">
-        <v>1.86</v>
+        <v>2.5</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46010.64583333334</v>
+        <v>46010.625</v>
       </c>
     </row>
     <row r="28">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
-        <v>46010.66666666666</v>
+        <v>46010.64583333334</v>
       </c>
     </row>
     <row r="29">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,61 +4110,61 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="M31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC31" t="n">
         <v>1.93</v>
       </c>
-      <c r="M31" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N31" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5.8</v>
+        <v>1.95</v>
       </c>
       <c r="M34" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>1.37</v>
+        <v>3.55</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.43</v>
+        <v>1.95</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -4545,12 +4545,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.64</v>
+        <v>1.93</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N35" t="n">
-        <v>1.79</v>
+        <v>3.55</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4655,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
-        <v>46010.67708333334</v>
+        <v>46010.66666666666</v>
       </c>
     </row>
     <row r="36">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
-        <v>46010.6875</v>
+        <v>46010.67708333334</v>
       </c>
     </row>
     <row r="38">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,16 +5345,16 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,16 +5464,16 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5497,12 +5497,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="M43" t="n">
-        <v>2.91</v>
+        <v>3.06</v>
       </c>
       <c r="N43" t="n">
-        <v>2.53</v>
+        <v>2.81</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5607,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
-        <v>46010.69791666666</v>
+        <v>46010.6875</v>
       </c>
     </row>
     <row r="44">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.55</v>
+        <v>1.86</v>
       </c>
       <c r="M44" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N44" t="n">
-        <v>2.55</v>
+        <v>3.77</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.26</v>
+        <v>2.55</v>
       </c>
       <c r="M46" t="n">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="N46" t="n">
-        <v>3.08</v>
+        <v>2.55</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.9</v>
+        <v>2.63</v>
       </c>
       <c r="M47" t="n">
-        <v>3.19</v>
+        <v>2.91</v>
       </c>
       <c r="N47" t="n">
-        <v>3.59</v>
+        <v>2.53</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="M48" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="N48" t="n">
-        <v>3.77</v>
+        <v>3.59</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="AI49" s="3" t="n">
-        <v>46010.70833333334</v>
+        <v>46010.69791666666</v>
       </c>
     </row>
     <row r="50">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6449,116 +6449,235 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Swansea City</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Wrexham</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M51" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="N51" t="n">
+        <v>3</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3" t="n">
+        <v>46010.70833333334</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Portugal Liga NOS</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>GD Estoril Praia</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Sporting Braga</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="inlineStr">
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L51" t="n">
+      <c r="L52" t="n">
         <v>4.2</v>
       </c>
-      <c r="M51" t="n">
+      <c r="M52" t="n">
         <v>3.5</v>
       </c>
-      <c r="N51" t="n">
+      <c r="N52" t="n">
         <v>1.85</v>
       </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51" t="n">
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB51" t="n">
+      <c r="AB52" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI51" s="3" t="n">
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="3" t="n">
         <v>46010.71875</v>
       </c>
     </row>

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -659,34 +659,34 @@
         </is>
       </c>
       <c r="L2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P2" t="n">
         <v>2.25</v>
       </c>
-      <c r="M2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3</v>
-      </c>
-      <c r="O2" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.23</v>
-      </c>
       <c r="Q2" t="n">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="R2" t="n">
         <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>2.98</v>
+        <v>2.89</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="U2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V2" t="n">
         <v>6.9</v>
@@ -695,28 +695,28 @@
         <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z2" t="n">
         <v>3.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.12</v>
+        <v>3.36</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AF2" t="n">
         <v>2.05</v>
@@ -725,7 +725,7 @@
         <v>1.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46010.16666666666</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N3" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="O3" t="n">
         <v>3.14</v>
@@ -793,7 +793,7 @@
         <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
         <v>1.32</v>
@@ -802,7 +802,7 @@
         <v>3.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="U3" t="n">
         <v>1.46</v>
@@ -820,19 +820,19 @@
         <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.17</v>
+        <v>3.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AE3" t="n">
         <v>1.6</v>
@@ -841,10 +841,10 @@
         <v>2.25</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46010.25</v>
@@ -1141,7 +1141,7 @@
         <v>2.97</v>
       </c>
       <c r="N6" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Western Sydney Wanderers</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.56</v>
+        <v>3.9</v>
       </c>
       <c r="M3" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>2.55</v>
+        <v>1.76</v>
       </c>
       <c r="O3" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46010.25</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Western Sydney Wanderers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.9</v>
+        <v>2.56</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N4" t="n">
-        <v>1.76</v>
+        <v>2.55</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46010.25</v>
@@ -1141,7 +1141,7 @@
         <v>2.97</v>
       </c>
       <c r="N6" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46010.58333333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="M24" t="n">
-        <v>3.02</v>
+        <v>3.52</v>
       </c>
       <c r="N24" t="n">
-        <v>3.83</v>
+        <v>3.4</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3405,40 +3405,40 @@
         <v>3.5</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA25" t="n">
         <v>2.2</v>
@@ -3447,22 +3447,22 @@
         <v>1.62</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46010.61458333334</v>
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46010.625</v>
@@ -3643,40 +3643,40 @@
         <v>2.5</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA27" t="n">
         <v>1.9</v>
@@ -3685,22 +3685,22 @@
         <v>1.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46010.625</v>
@@ -3762,40 +3762,40 @@
         <v>1.86</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA28" t="n">
         <v>1.65</v>
@@ -3804,22 +3804,22 @@
         <v>2.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46010.64583333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N34" t="n">
         <v>3.55</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.12</v>
+        <v>3.64</v>
       </c>
       <c r="M36" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>2.89</v>
+        <v>1.79</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.64</v>
+        <v>2.12</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>1.79</v>
+        <v>2.89</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.48</v>
+        <v>2.58</v>
       </c>
       <c r="M41" t="n">
-        <v>4.6</v>
+        <v>3.06</v>
       </c>
       <c r="N41" t="n">
-        <v>5.7</v>
+        <v>2.81</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,16 +5345,16 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.45</v>
+        <v>1.65</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.58</v>
+        <v>1.48</v>
       </c>
       <c r="M43" t="n">
-        <v>3.06</v>
+        <v>4.6</v>
       </c>
       <c r="N43" t="n">
-        <v>2.81</v>
+        <v>5.7</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,16 +5583,16 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.65</v>
+        <v>2.45</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.86</v>
+        <v>2.26</v>
       </c>
       <c r="M44" t="n">
-        <v>3.15</v>
+        <v>2.83</v>
       </c>
       <c r="N44" t="n">
-        <v>3.77</v>
+        <v>3.08</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.78</v>
+        <v>2.63</v>
       </c>
       <c r="M45" t="n">
-        <v>3.17</v>
+        <v>2.91</v>
       </c>
       <c r="N45" t="n">
-        <v>4.1</v>
+        <v>2.53</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.63</v>
+        <v>1.78</v>
       </c>
       <c r="M47" t="n">
-        <v>2.91</v>
+        <v>3.17</v>
       </c>
       <c r="N47" t="n">
-        <v>2.53</v>
+        <v>4.1</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.26</v>
+        <v>1.86</v>
       </c>
       <c r="M49" t="n">
-        <v>2.83</v>
+        <v>3.15</v>
       </c>
       <c r="N49" t="n">
-        <v>3.08</v>
+        <v>3.77</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="M2" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N2" t="n">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
         <v>2.9</v>
@@ -704,10 +704,10 @@
         <v>3.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC2" t="n">
         <v>3.36</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N4" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
         <v>3.14</v>
@@ -942,10 +942,10 @@
         <v>3.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AC4" t="n">
         <v>3</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="M19" t="n">
-        <v>3.74</v>
+        <v>3.64</v>
       </c>
       <c r="N19" t="n">
-        <v>3.29</v>
+        <v>5.35</v>
       </c>
       <c r="O19" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="P19" t="n">
-        <v>2.51</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.23</v>
+        <v>1.43</v>
       </c>
       <c r="S19" t="n">
-        <v>3.42</v>
+        <v>2.62</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="U19" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>5.15</v>
+        <v>8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.56</v>
+        <v>2.11</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.38</v>
+        <v>3.54</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF21" t="n">
         <v>2.5</v>
       </c>
-      <c r="M21" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="O21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V21" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG21" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46010.58333333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46010.60416666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="M24" t="n">
-        <v>3.52</v>
+        <v>3.02</v>
       </c>
       <c r="N24" t="n">
-        <v>3.4</v>
+        <v>3.83</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46010.60416666666</v>
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="O25" t="n">
         <v>2.64</v>
@@ -3441,7 +3441,7 @@
         <v>2.83</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AB25" t="n">
         <v>1.62</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.95</v>
+        <v>5.8</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="N29" t="n">
-        <v>3.55</v>
+        <v>1.37</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.76</v>
+        <v>1.36</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.64</v>
+        <v>2.12</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N36" t="n">
-        <v>1.79</v>
+        <v>2.89</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.12</v>
+        <v>3.64</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>2.89</v>
+        <v>1.79</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.19</v>
+        <v>2.45</v>
       </c>
       <c r="M39" t="n">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="N39" t="n">
-        <v>3.39</v>
+        <v>2.85</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB39" t="n">
         <v>1.6</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46010.6875</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,16 +5464,16 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.48</v>
+        <v>2.58</v>
       </c>
       <c r="M43" t="n">
-        <v>4.6</v>
+        <v>3.06</v>
       </c>
       <c r="N43" t="n">
-        <v>5.7</v>
+        <v>2.81</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,16 +5583,16 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.45</v>
+        <v>1.65</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="M45" t="n">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="N45" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="M46" t="n">
-        <v>3.25</v>
+        <v>2.91</v>
       </c>
       <c r="N46" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="M47" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="N47" t="n">
-        <v>4.1</v>
+        <v>3.77</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="M48" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="N48" t="n">
-        <v>3.59</v>
+        <v>4.1</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="M49" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="N49" t="n">
-        <v>3.77</v>
+        <v>3.59</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="M25" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
         <v>2.64</v>
@@ -3441,7 +3441,7 @@
         <v>2.83</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AB25" t="n">
         <v>1.62</v>
@@ -3643,19 +3643,19 @@
         <v>2.5</v>
       </c>
       <c r="O27" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P27" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S27" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="T27" t="n">
         <v>2.81</v>
@@ -3685,7 +3685,7 @@
         <v>1.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD27" t="n">
         <v>1.3</v>
@@ -3697,10 +3697,10 @@
         <v>2.05</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46010.625</v>
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.45</v>
+        <v>2.19</v>
       </c>
       <c r="M39" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="N39" t="n">
-        <v>2.85</v>
+        <v>3.39</v>
       </c>
       <c r="O39" t="n">
         <v>2.9</v>
@@ -5107,7 +5107,7 @@
         <v>2.75</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB39" t="n">
         <v>1.6</v>
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="M50" t="n">
-        <v>3.09</v>
+        <v>3.18</v>
       </c>
       <c r="N50" t="n">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA50" t="n">
         <v>2.15</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46010.70833333334</v>
@@ -6490,73 +6490,73 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46010.70833333334</v>
@@ -6618,40 +6618,40 @@
         <v>1.85</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA52" t="n">
         <v>1.85</v>
@@ -6660,22 +6660,22 @@
         <v>1.85</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46010.71875</v>

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Western Sydney Wanderers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>1.76</v>
+        <v>2.35</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46010.25</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Western Sydney Wanderers</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="M4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>1.76</v>
       </c>
       <c r="O4" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AC4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46010.25</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="M21" t="n">
-        <v>3.74</v>
+        <v>2.97</v>
       </c>
       <c r="N21" t="n">
-        <v>3.29</v>
+        <v>2.97</v>
       </c>
       <c r="O21" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="P21" t="n">
-        <v>2.51</v>
+        <v>2.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.23</v>
+        <v>1.47</v>
       </c>
       <c r="S21" t="n">
-        <v>3.42</v>
+        <v>2.47</v>
       </c>
       <c r="T21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA21" t="n">
         <v>2.2</v>
       </c>
-      <c r="U21" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AB21" t="n">
-        <v>2.45</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.38</v>
+        <v>3.82</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46010.58333333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,37 +3158,37 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="M23" t="n">
-        <v>3.52</v>
+        <v>3.02</v>
       </c>
       <c r="N23" t="n">
-        <v>3.4</v>
+        <v>3.83</v>
       </c>
       <c r="O23" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="P23" t="n">
         <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>3.02</v>
+        <v>2.89</v>
       </c>
       <c r="T23" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="U23" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="V23" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="W23" t="n">
         <v>1.07</v>
@@ -3197,19 +3197,19 @@
         <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AD23" t="n">
         <v>1.4</v>
@@ -3218,13 +3218,13 @@
         <v>1.57</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AG23" t="n">
         <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46010.60416666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,37 +3277,37 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="M24" t="n">
-        <v>3.02</v>
+        <v>3.52</v>
       </c>
       <c r="N24" t="n">
-        <v>3.83</v>
+        <v>3.4</v>
       </c>
       <c r="O24" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="P24" t="n">
         <v>2.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>2.89</v>
+        <v>3.02</v>
       </c>
       <c r="T24" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="U24" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="V24" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="W24" t="n">
         <v>1.07</v>
@@ -3316,19 +3316,19 @@
         <v>1.04</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z24" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AD24" t="n">
         <v>1.4</v>
@@ -3337,13 +3337,13 @@
         <v>1.57</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG24" t="n">
         <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46010.60416666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.12</v>
+        <v>3.64</v>
       </c>
       <c r="M36" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>2.89</v>
+        <v>1.79</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46010.67708333334</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.64</v>
+        <v>2.12</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>1.79</v>
+        <v>2.89</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46010.67708333334</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.19</v>
+        <v>2.58</v>
       </c>
       <c r="M39" t="n">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="N39" t="n">
-        <v>3.39</v>
+        <v>2.81</v>
       </c>
       <c r="O39" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC39" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46010.6875</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46010.6875</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46010.6875</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,16 +5464,16 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.26</v>
+        <v>2.63</v>
       </c>
       <c r="M44" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="N44" t="n">
-        <v>3.08</v>
+        <v>2.53</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.55</v>
+        <v>2.26</v>
       </c>
       <c r="M45" t="n">
-        <v>3.25</v>
+        <v>2.83</v>
       </c>
       <c r="N45" t="n">
-        <v>2.55</v>
+        <v>3.08</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA45" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46010.69791666666</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="M46" t="n">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="N46" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="M47" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="N47" t="n">
-        <v>3.77</v>
+        <v>4.1</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="M48" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="N48" t="n">
-        <v>4.1</v>
+        <v>3.77</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.31</v>
+        <v>2.42</v>
       </c>
       <c r="M50" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="N50" t="n">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="O50" t="n">
         <v>2.8</v>
@@ -6419,7 +6419,7 @@
         <v>2.15</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC50" t="n">
         <v>4</v>

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -674,13 +674,13 @@
         <v>2.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S2" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="T2" t="n">
         <v>2.73</v>
@@ -695,10 +695,10 @@
         <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z2" t="n">
         <v>3.3</v>
@@ -710,7 +710,7 @@
         <v>1.95</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.36</v>
+        <v>3.18</v>
       </c>
       <c r="AD2" t="n">
         <v>1.3</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Western Sydney Wanderers</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>2.35</v>
+        <v>1.76</v>
       </c>
       <c r="O3" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AC3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46010.25</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Western Sydney Wanderers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N4" t="n">
-        <v>1.76</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46010.25</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1769,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -2334,40 +2334,40 @@
         <v>1.27</v>
       </c>
       <c r="O16" t="n">
-        <v>7.1</v>
+        <v>6.25</v>
       </c>
       <c r="P16" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="R16" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S16" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="T16" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V16" t="n">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="AA16" t="n">
         <v>1.74</v>
@@ -2376,22 +2376,22 @@
         <v>1.96</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AF16" t="n">
         <v>1.62</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46010.52083333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="M18" t="n">
-        <v>3.74</v>
+        <v>3.64</v>
       </c>
       <c r="N18" t="n">
-        <v>3.29</v>
+        <v>5.35</v>
       </c>
       <c r="O18" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="P18" t="n">
-        <v>2.51</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.23</v>
+        <v>1.43</v>
       </c>
       <c r="S18" t="n">
-        <v>3.42</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="U18" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>5.15</v>
+        <v>8</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.56</v>
+        <v>2.11</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.38</v>
+        <v>3.54</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.69</v>
+        <v>2.5</v>
       </c>
       <c r="M19" t="n">
-        <v>3.64</v>
+        <v>2.97</v>
       </c>
       <c r="N19" t="n">
-        <v>5.35</v>
+        <v>2.97</v>
       </c>
       <c r="O19" t="n">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="P19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA19" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q19" t="n">
-        <v>5</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V19" t="n">
-        <v>8</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.11</v>
-      </c>
       <c r="AB19" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.54</v>
+        <v>3.82</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF21" t="n">
         <v>2.5</v>
       </c>
-      <c r="M21" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="O21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V21" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG21" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46010.58333333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46010.60416666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,37 +3158,37 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="M23" t="n">
-        <v>3.02</v>
+        <v>3.52</v>
       </c>
       <c r="N23" t="n">
-        <v>3.83</v>
+        <v>3.4</v>
       </c>
       <c r="O23" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="P23" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>2.89</v>
+        <v>3.04</v>
       </c>
       <c r="T23" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="U23" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="V23" t="n">
-        <v>5.4</v>
+        <v>5.85</v>
       </c>
       <c r="W23" t="n">
         <v>1.07</v>
@@ -3197,34 +3197,34 @@
         <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z23" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AD23" t="n">
         <v>1.4</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AG23" t="n">
         <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46010.60416666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46010.60416666666</v>
@@ -3405,7 +3405,7 @@
         <v>3.5</v>
       </c>
       <c r="O25" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="P25" t="n">
         <v>1.94</v>
@@ -3438,7 +3438,7 @@
         <v>1.33</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="AA25" t="n">
         <v>2.2</v>
@@ -3447,10 +3447,10 @@
         <v>1.62</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.92</v>
+        <v>3.99</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE25" t="n">
         <v>1.89</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.74</v>
+        <v>2.64</v>
       </c>
       <c r="M26" t="n">
-        <v>3.68</v>
+        <v>2.94</v>
       </c>
       <c r="N26" t="n">
-        <v>3.91</v>
+        <v>2.5</v>
       </c>
       <c r="O26" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="S26" t="n">
-        <v>3.18</v>
+        <v>2.73</v>
       </c>
       <c r="T26" t="n">
-        <v>2.27</v>
+        <v>2.85</v>
       </c>
       <c r="U26" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="V26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W26" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X26" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.45</v>
+        <v>3.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46010.625</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.64</v>
+        <v>1.74</v>
       </c>
       <c r="M27" t="n">
-        <v>2.94</v>
+        <v>3.68</v>
       </c>
       <c r="N27" t="n">
-        <v>2.5</v>
+        <v>3.91</v>
       </c>
       <c r="O27" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="S27" t="n">
-        <v>2.77</v>
+        <v>3.18</v>
       </c>
       <c r="T27" t="n">
-        <v>2.81</v>
+        <v>2.27</v>
       </c>
       <c r="U27" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="V27" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="W27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X27" t="n">
         <v>1.03</v>
       </c>
-      <c r="X27" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y27" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46010.625</v>
@@ -3777,7 +3777,7 @@
         <v>3.15</v>
       </c>
       <c r="T28" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="U28" t="n">
         <v>1.5</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46010.66666666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.95</v>
+        <v>5.8</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="N31" t="n">
-        <v>3.55</v>
+        <v>1.37</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.76</v>
+        <v>1.36</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4729,13 +4729,13 @@
         <v>2.9</v>
       </c>
       <c r="T36" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="U36" t="n">
         <v>1.43</v>
       </c>
       <c r="V36" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="W36" t="n">
         <v>1.07</v>
@@ -4744,7 +4744,7 @@
         <v>1.04</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z36" t="n">
         <v>3.8</v>
@@ -4768,10 +4768,10 @@
         <v>2.1</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46010.67708333334</v>
@@ -4854,7 +4854,7 @@
         <v>1.5</v>
       </c>
       <c r="V37" t="n">
-        <v>5.55</v>
+        <v>5.45</v>
       </c>
       <c r="W37" t="n">
         <v>1.08</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46010.6875</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.58</v>
+        <v>2.19</v>
       </c>
       <c r="M39" t="n">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="N39" t="n">
-        <v>2.81</v>
+        <v>3.39</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46010.6875</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.19</v>
+        <v>2.58</v>
       </c>
       <c r="M40" t="n">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="N40" t="n">
-        <v>3.39</v>
+        <v>2.81</v>
       </c>
       <c r="O40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC40" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46010.6875</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46010.6875</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.63</v>
+        <v>1.86</v>
       </c>
       <c r="M44" t="n">
-        <v>2.91</v>
+        <v>3.15</v>
       </c>
       <c r="N44" t="n">
-        <v>2.53</v>
+        <v>3.77</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46010.69791666666</v>
@@ -5788,7 +5788,7 @@
         <v>2.9</v>
       </c>
       <c r="P45" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="Q45" t="n">
         <v>3.8</v>
@@ -5800,7 +5800,7 @@
         <v>2.44</v>
       </c>
       <c r="T45" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="U45" t="n">
         <v>1.28</v>
@@ -5904,40 +5904,40 @@
         <v>2.55</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA46" t="n">
         <v>2</v>
@@ -5946,22 +5946,22 @@
         <v>1.72</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46010.69791666666</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="M47" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="N47" t="n">
-        <v>4.1</v>
+        <v>3.59</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46010.69791666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.86</v>
+        <v>2.63</v>
       </c>
       <c r="M48" t="n">
-        <v>3.15</v>
+        <v>2.91</v>
       </c>
       <c r="N48" t="n">
-        <v>3.77</v>
+        <v>2.53</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46010.69791666666</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="M49" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="N49" t="n">
-        <v>3.59</v>
+        <v>4.1</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB49" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE49" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>0</v>
-      </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46010.69791666666</v>
@@ -6395,13 +6395,13 @@
         <v>2.53</v>
       </c>
       <c r="T50" t="n">
-        <v>3.1</v>
+        <v>3.21</v>
       </c>
       <c r="U50" t="n">
         <v>1.32</v>
       </c>
       <c r="V50" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W50" t="n">
         <v>1.02</v>
@@ -6410,7 +6410,7 @@
         <v>1.08</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z50" t="n">
         <v>2.9</v>
@@ -6422,7 +6422,7 @@
         <v>1.63</v>
       </c>
       <c r="AC50" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="AD50" t="n">
         <v>1.22</v>
@@ -6618,7 +6618,7 @@
         <v>1.85</v>
       </c>
       <c r="O52" t="n">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="P52" t="n">
         <v>2.3</v>
@@ -6627,10 +6627,10 @@
         <v>2.15</v>
       </c>
       <c r="R52" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S52" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="T52" t="n">
         <v>2.62</v>
@@ -6639,19 +6639,19 @@
         <v>1.43</v>
       </c>
       <c r="V52" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="W52" t="n">
         <v>1.06</v>
       </c>
       <c r="X52" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z52" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA52" t="n">
         <v>1.85</v>
@@ -6660,16 +6660,16 @@
         <v>1.85</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AD52" t="n">
         <v>1.36</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AF52" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AG52" t="n">
         <v>1.29</v>

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Western Sydney Wanderers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>1.76</v>
+        <v>2.35</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46010.25</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Western Sydney Wanderers</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="M4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>1.76</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46010.25</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF19" t="n">
         <v>2.5</v>
       </c>
-      <c r="M19" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG19" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.89</v>
+        <v>1.66</v>
       </c>
       <c r="M21" t="n">
-        <v>3.74</v>
+        <v>3.66</v>
       </c>
       <c r="N21" t="n">
-        <v>3.29</v>
+        <v>5.25</v>
       </c>
       <c r="O21" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="P21" t="n">
-        <v>2.51</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.5</v>
+        <v>5.7</v>
       </c>
       <c r="R21" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="S21" t="n">
-        <v>3.42</v>
+        <v>2.65</v>
       </c>
       <c r="T21" t="n">
-        <v>2.2</v>
+        <v>2.99</v>
       </c>
       <c r="U21" t="n">
-        <v>1.54</v>
+        <v>1.34</v>
       </c>
       <c r="V21" t="n">
-        <v>5.15</v>
+        <v>7.8</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.56</v>
+        <v>2.04</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.38</v>
+        <v>3.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46010.58333333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,37 +3039,37 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="M22" t="n">
-        <v>3.02</v>
+        <v>3.52</v>
       </c>
       <c r="N22" t="n">
-        <v>3.83</v>
+        <v>3.4</v>
       </c>
       <c r="O22" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="P22" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
       <c r="T22" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="U22" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="V22" t="n">
-        <v>6</v>
+        <v>5.85</v>
       </c>
       <c r="W22" t="n">
         <v>1.07</v>
@@ -3078,34 +3078,34 @@
         <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z22" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AD22" t="n">
         <v>1.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AG22" t="n">
         <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46010.60416666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,37 +3158,37 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="M23" t="n">
-        <v>3.52</v>
+        <v>3.02</v>
       </c>
       <c r="N23" t="n">
-        <v>3.4</v>
+        <v>3.83</v>
       </c>
       <c r="O23" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>3.04</v>
+        <v>2.94</v>
       </c>
       <c r="T23" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="U23" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="V23" t="n">
-        <v>5.85</v>
+        <v>6</v>
       </c>
       <c r="W23" t="n">
         <v>1.07</v>
@@ -3197,34 +3197,34 @@
         <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AD23" t="n">
         <v>1.4</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AG23" t="n">
         <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46010.60416666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.64</v>
+        <v>1.82</v>
       </c>
       <c r="M26" t="n">
-        <v>2.94</v>
+        <v>3.8</v>
       </c>
       <c r="N26" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="O26" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q26" t="n">
-        <v>3</v>
+        <v>4.52</v>
       </c>
       <c r="R26" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="S26" t="n">
-        <v>2.73</v>
+        <v>3.18</v>
       </c>
       <c r="T26" t="n">
-        <v>2.85</v>
+        <v>2.41</v>
       </c>
       <c r="U26" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="V26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X26" t="n">
         <v>1.03</v>
       </c>
-      <c r="X26" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y26" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.3</v>
+        <v>2.48</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46010.625</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.74</v>
+        <v>2.64</v>
       </c>
       <c r="M27" t="n">
-        <v>3.68</v>
+        <v>2.94</v>
       </c>
       <c r="N27" t="n">
-        <v>3.91</v>
+        <v>2.5</v>
       </c>
       <c r="O27" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="P27" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="S27" t="n">
-        <v>3.18</v>
+        <v>2.73</v>
       </c>
       <c r="T27" t="n">
-        <v>2.27</v>
+        <v>2.85</v>
       </c>
       <c r="U27" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.45</v>
+        <v>3.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46010.625</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="M29" t="n">
         <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>3.55</v>
+        <v>2.85</v>
       </c>
       <c r="O29" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="P29" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.12</v>
+        <v>3.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S29" t="n">
-        <v>2.91</v>
+        <v>3.28</v>
       </c>
       <c r="T29" t="n">
-        <v>2.45</v>
+        <v>2.27</v>
       </c>
       <c r="U29" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE29" t="n">
         <v>1.44</v>
       </c>
-      <c r="V29" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AF29" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46010.66666666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="M30" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
         <v>3.55</v>
       </c>
       <c r="O30" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="P30" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.25</v>
+        <v>4.12</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S30" t="n">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="T30" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="U30" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="V30" t="n">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="W30" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X30" t="n">
         <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.84</v>
+        <v>3.58</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>5.8</v>
+        <v>1.93</v>
       </c>
       <c r="M31" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="N31" t="n">
-        <v>1.37</v>
+        <v>3.55</v>
       </c>
       <c r="O31" t="n">
-        <v>6.5</v>
+        <v>2.41</v>
       </c>
       <c r="P31" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.73</v>
+        <v>4.25</v>
       </c>
       <c r="R31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y31" t="n">
         <v>1.22</v>
       </c>
-      <c r="S31" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.11</v>
-      </c>
       <c r="Z31" t="n">
-        <v>6</v>
+        <v>3.84</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.9</v>
+        <v>2.06</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.93</v>
+        <v>2.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.77</v>
+        <v>1.39</v>
       </c>
       <c r="AE31" t="n">
         <v>1.6</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>7.22</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R38" t="n">
         <v>1.48</v>
       </c>
-      <c r="M38" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N38" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.23</v>
-      </c>
       <c r="S38" t="n">
-        <v>3.75</v>
+        <v>2.47</v>
       </c>
       <c r="T38" t="n">
-        <v>2.31</v>
+        <v>3.27</v>
       </c>
       <c r="U38" t="n">
-        <v>1.67</v>
+        <v>1.31</v>
       </c>
       <c r="V38" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="W38" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="X38" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="Z38" t="n">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.45</v>
+        <v>1.65</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.63</v>
+        <v>1.22</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46010.6875</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46010.6875</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.26</v>
+        <v>2.63</v>
       </c>
       <c r="M45" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="N45" t="n">
-        <v>3.08</v>
+        <v>2.53</v>
       </c>
       <c r="O45" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q45" t="n">
         <v>2.9</v>
       </c>
-      <c r="P45" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>3.8</v>
-      </c>
       <c r="R45" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="S45" t="n">
-        <v>2.44</v>
+        <v>2.69</v>
       </c>
       <c r="T45" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="U45" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="V45" t="n">
-        <v>9.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="W45" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X45" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AC45" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AG45" t="n">
         <v>1.36</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46010.69791666666</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,58 +5895,58 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.55</v>
+        <v>1.78</v>
       </c>
       <c r="M46" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="N46" t="n">
-        <v>2.55</v>
+        <v>4.1</v>
       </c>
       <c r="O46" t="n">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="P46" t="n">
         <v>2.2</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.8</v>
+        <v>4.82</v>
       </c>
       <c r="R46" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U46" t="n">
         <v>1.39</v>
       </c>
-      <c r="S46" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.36</v>
-      </c>
       <c r="V46" t="n">
-        <v>7.1</v>
+        <v>6.85</v>
       </c>
       <c r="W46" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X46" t="n">
         <v>1.06</v>
       </c>
-      <c r="X46" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y46" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AD46" t="n">
         <v>1.3</v>
@@ -5958,10 +5958,10 @@
         <v>1.98</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46010.69791666666</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="M47" t="n">
-        <v>3.19</v>
+        <v>2.83</v>
       </c>
       <c r="N47" t="n">
-        <v>3.59</v>
+        <v>3.08</v>
       </c>
       <c r="O47" t="n">
-        <v>2.58</v>
+        <v>2.9</v>
       </c>
       <c r="P47" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.45</v>
+        <v>3.8</v>
       </c>
       <c r="R47" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S47" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V47" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG47" t="n">
         <v>1.36</v>
       </c>
-      <c r="S47" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V47" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X47" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH47" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46010.69791666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="M48" t="n">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="N48" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="O48" t="n">
         <v>3.3</v>
       </c>
       <c r="P48" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="R48" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S48" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="T48" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="U48" t="n">
         <v>1.36</v>
       </c>
       <c r="V48" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="W48" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X48" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y48" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD48" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.25</v>
       </c>
       <c r="AE48" t="n">
         <v>1.75</v>
       </c>
       <c r="AF48" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AG48" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH48" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.4</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46010.69791666666</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,37 +6252,37 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="M49" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="N49" t="n">
-        <v>4.1</v>
+        <v>3.59</v>
       </c>
       <c r="O49" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="P49" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.82</v>
+        <v>4.45</v>
       </c>
       <c r="R49" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S49" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="T49" t="n">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="U49" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="V49" t="n">
-        <v>6.85</v>
+        <v>7.1</v>
       </c>
       <c r="W49" t="n">
         <v>1.04</v>
@@ -6291,34 +6291,34 @@
         <v>1.06</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AG49" t="n">
         <v>1.3</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46010.69791666666</v>
@@ -6490,16 +6490,16 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="M51" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="N51" t="n">
-        <v>3.75</v>
+        <v>4.17</v>
       </c>
       <c r="O51" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="P51" t="n">
         <v>2.05</v>
@@ -6514,13 +6514,13 @@
         <v>2.55</v>
       </c>
       <c r="T51" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U51" t="n">
         <v>1.33</v>
       </c>
       <c r="V51" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W51" t="n">
         <v>1.04</v>
@@ -6535,13 +6535,13 @@
         <v>2.7</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AB51" t="n">
         <v>1.6</v>
       </c>
       <c r="AC51" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AD51" t="n">
         <v>1.18</v>

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Western Sydney Wanderers</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>2.35</v>
+        <v>1.76</v>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46010.25</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Western Sydney Wanderers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N4" t="n">
-        <v>1.76</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46010.25</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="M19" t="n">
-        <v>3.74</v>
+        <v>3.66</v>
       </c>
       <c r="N19" t="n">
-        <v>3.29</v>
+        <v>5.25</v>
       </c>
       <c r="O19" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="P19" t="n">
-        <v>2.51</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.82</v>
+        <v>5.7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>3.34</v>
+        <v>2.65</v>
       </c>
       <c r="T19" t="n">
-        <v>2.32</v>
+        <v>2.99</v>
       </c>
       <c r="U19" t="n">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="V19" t="n">
-        <v>5.15</v>
+        <v>7.8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.5</v>
+        <v>2.04</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.25</v>
+        <v>3.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="M20" t="n">
-        <v>3.05</v>
+        <v>3.74</v>
       </c>
       <c r="N20" t="n">
-        <v>2.98</v>
+        <v>3.29</v>
       </c>
       <c r="O20" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>2.51</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>2.44</v>
+        <v>3.34</v>
       </c>
       <c r="T20" t="n">
-        <v>3.16</v>
+        <v>2.32</v>
       </c>
       <c r="U20" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="V20" t="n">
-        <v>8.5</v>
+        <v>5.15</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>2.45</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.88</v>
+        <v>2.25</v>
       </c>
       <c r="AD20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46010.58333333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="O29" t="n">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="P29" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="Q29" t="n">
         <v>3.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S29" t="n">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="T29" t="n">
-        <v>2.27</v>
+        <v>2.44</v>
       </c>
       <c r="U29" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="V29" t="n">
-        <v>4.6</v>
+        <v>5.75</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE29" t="n">
         <v>1.57</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AF29" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2.55</v>
       </c>
       <c r="AG29" t="n">
         <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46010.66666666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.95</v>
+        <v>1.16</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="N30" t="n">
-        <v>3.55</v>
+        <v>11</v>
       </c>
       <c r="O30" t="n">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="P30" t="n">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.12</v>
+        <v>8.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="S30" t="n">
-        <v>2.91</v>
+        <v>5.1</v>
       </c>
       <c r="T30" t="n">
-        <v>2.45</v>
+        <v>1.71</v>
       </c>
       <c r="U30" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="V30" t="n">
-        <v>5.75</v>
+        <v>3.12</v>
       </c>
       <c r="W30" t="n">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.58</v>
+        <v>9.6</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.73</v>
+        <v>1.18</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.91</v>
+        <v>4.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.78</v>
+        <v>1.53</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.34</v>
+        <v>2.38</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="M31" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
         <v>3.55</v>
       </c>
       <c r="O31" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="P31" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.25</v>
+        <v>4.12</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S31" t="n">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="T31" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="U31" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="V31" t="n">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="W31" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X31" t="n">
         <v>1.04</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.84</v>
+        <v>3.58</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>5.8</v>
+        <v>1.31</v>
       </c>
       <c r="M32" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="N32" t="n">
-        <v>1.37</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O32" t="n">
-        <v>6.5</v>
+        <v>1.73</v>
       </c>
       <c r="P32" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.73</v>
+        <v>7.22</v>
       </c>
       <c r="R32" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S32" t="n">
-        <v>3.78</v>
+        <v>3.94</v>
       </c>
       <c r="T32" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="U32" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="V32" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="W32" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X32" t="n">
         <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Z32" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AF32" t="n">
         <v>2.25</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.11</v>
+        <v>3.3</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.31</v>
+        <v>5.8</v>
       </c>
       <c r="M33" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="N33" t="n">
-        <v>8.550000000000001</v>
+        <v>1.37</v>
       </c>
       <c r="O33" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q33" t="n">
         <v>1.73</v>
       </c>
-      <c r="P33" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>7.22</v>
-      </c>
       <c r="R33" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S33" t="n">
-        <v>3.94</v>
+        <v>3.78</v>
       </c>
       <c r="T33" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="U33" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="V33" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="W33" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X33" t="n">
         <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z33" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB33" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AF33" t="n">
         <v>2.25</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AH33" t="n">
-        <v>3.3</v>
+        <v>1.11</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="M34" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="O34" t="n">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="P34" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="Q34" t="n">
         <v>3.2</v>
       </c>
       <c r="R34" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S34" t="n">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="T34" t="n">
-        <v>2.44</v>
+        <v>2.27</v>
       </c>
       <c r="U34" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="V34" t="n">
-        <v>5.75</v>
+        <v>4.6</v>
       </c>
       <c r="W34" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X34" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.63</v>
+        <v>2.28</v>
       </c>
       <c r="AD34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE34" t="n">
         <v>1.44</v>
       </c>
-      <c r="AE34" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AF34" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AG34" t="n">
         <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.16</v>
+        <v>1.93</v>
       </c>
       <c r="M35" t="n">
-        <v>7.5</v>
+        <v>3.55</v>
       </c>
       <c r="N35" t="n">
-        <v>11</v>
+        <v>3.55</v>
       </c>
       <c r="O35" t="n">
-        <v>1.44</v>
+        <v>2.41</v>
       </c>
       <c r="P35" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>8.5</v>
+        <v>4.25</v>
       </c>
       <c r="R35" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="S35" t="n">
-        <v>5.1</v>
+        <v>3.08</v>
       </c>
       <c r="T35" t="n">
-        <v>1.71</v>
+        <v>2.41</v>
       </c>
       <c r="U35" t="n">
-        <v>2.05</v>
+        <v>1.47</v>
       </c>
       <c r="V35" t="n">
-        <v>3.12</v>
+        <v>5.4</v>
       </c>
       <c r="W35" t="n">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="Z35" t="n">
-        <v>9.6</v>
+        <v>3.84</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.18</v>
+        <v>1.68</v>
       </c>
       <c r="AB35" t="n">
-        <v>4.4</v>
+        <v>2.06</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.53</v>
+        <v>2.7</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AH35" t="n">
-        <v>4.8</v>
+        <v>1.75</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.64</v>
+        <v>2.12</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N36" t="n">
-        <v>1.79</v>
+        <v>2.89</v>
       </c>
       <c r="O36" t="n">
-        <v>3.6</v>
+        <v>2.63</v>
       </c>
       <c r="P36" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.46</v>
+        <v>3.25</v>
       </c>
       <c r="R36" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="S36" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="T36" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="U36" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="V36" t="n">
-        <v>6</v>
+        <v>5.45</v>
       </c>
       <c r="W36" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X36" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.21</v>
+        <v>1.62</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46010.67708333334</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.12</v>
+        <v>3.64</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>2.89</v>
+        <v>1.79</v>
       </c>
       <c r="O37" t="n">
-        <v>2.63</v>
+        <v>3.6</v>
       </c>
       <c r="P37" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.25</v>
+        <v>2.46</v>
       </c>
       <c r="R37" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="S37" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="T37" t="n">
-        <v>2.33</v>
+        <v>2.62</v>
       </c>
       <c r="U37" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="V37" t="n">
-        <v>5.45</v>
+        <v>6</v>
       </c>
       <c r="W37" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X37" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z37" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.62</v>
+        <v>1.21</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46010.67708333334</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.58</v>
+        <v>2.19</v>
       </c>
       <c r="M38" t="n">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="N38" t="n">
-        <v>2.81</v>
+        <v>3.39</v>
       </c>
       <c r="O38" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="P38" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.25</v>
+        <v>3.72</v>
       </c>
       <c r="R38" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S38" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="T38" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="U38" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="V38" t="n">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="W38" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X38" t="n">
         <v>1.08</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC38" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE38" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF38" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.86</v>
       </c>
       <c r="AG38" t="n">
         <v>1.36</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46010.6875</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46010.6875</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46010.6875</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.86</v>
+        <v>2.26</v>
       </c>
       <c r="M44" t="n">
-        <v>3.15</v>
+        <v>2.83</v>
       </c>
       <c r="N44" t="n">
-        <v>3.77</v>
+        <v>3.08</v>
       </c>
       <c r="O44" t="n">
-        <v>2.23</v>
+        <v>2.9</v>
       </c>
       <c r="P44" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="Q44" t="n">
-        <v>5.75</v>
+        <v>3.8</v>
       </c>
       <c r="R44" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="S44" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="T44" t="n">
-        <v>3.19</v>
+        <v>3.25</v>
       </c>
       <c r="U44" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="V44" t="n">
-        <v>8.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W44" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X44" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC44" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE44" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46010.69791666666</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.63</v>
+        <v>1.86</v>
       </c>
       <c r="M45" t="n">
-        <v>2.91</v>
+        <v>3.15</v>
       </c>
       <c r="N45" t="n">
-        <v>2.53</v>
+        <v>3.77</v>
       </c>
       <c r="O45" t="n">
-        <v>3.3</v>
+        <v>2.23</v>
       </c>
       <c r="P45" t="n">
         <v>2.15</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.9</v>
+        <v>5.75</v>
       </c>
       <c r="R45" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S45" t="n">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="T45" t="n">
-        <v>2.96</v>
+        <v>3.19</v>
       </c>
       <c r="U45" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="V45" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W45" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X45" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y45" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG45" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z45" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH45" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46010.69791666666</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.26</v>
+        <v>2.55</v>
       </c>
       <c r="M47" t="n">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="N47" t="n">
-        <v>3.08</v>
+        <v>2.55</v>
       </c>
       <c r="O47" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="P47" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="R47" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="S47" t="n">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="T47" t="n">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="U47" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="V47" t="n">
-        <v>9.300000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="W47" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="X47" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AC47" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AG47" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH47" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>1.6</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46010.69791666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,31 +6133,31 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="M48" t="n">
-        <v>3.25</v>
+        <v>3.19</v>
       </c>
       <c r="N48" t="n">
-        <v>2.55</v>
+        <v>3.59</v>
       </c>
       <c r="O48" t="n">
-        <v>3.3</v>
+        <v>2.58</v>
       </c>
       <c r="P48" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.8</v>
+        <v>4.45</v>
       </c>
       <c r="R48" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S48" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="T48" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="U48" t="n">
         <v>1.36</v>
@@ -6166,40 +6166,40 @@
         <v>7.1</v>
       </c>
       <c r="W48" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X48" t="n">
         <v>1.06</v>
       </c>
-      <c r="X48" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y48" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA48" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AD48" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG48" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE48" t="n">
+      <c r="AH48" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.36</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46010.69791666666</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,40 +6252,40 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.9</v>
+        <v>2.63</v>
       </c>
       <c r="M49" t="n">
-        <v>3.19</v>
+        <v>2.91</v>
       </c>
       <c r="N49" t="n">
-        <v>3.59</v>
+        <v>2.53</v>
       </c>
       <c r="O49" t="n">
-        <v>2.58</v>
+        <v>3.3</v>
       </c>
       <c r="P49" t="n">
         <v>2.15</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.45</v>
+        <v>2.9</v>
       </c>
       <c r="R49" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S49" t="n">
         <v>2.69</v>
       </c>
       <c r="T49" t="n">
-        <v>2.85</v>
+        <v>2.96</v>
       </c>
       <c r="U49" t="n">
         <v>1.36</v>
       </c>
       <c r="V49" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="W49" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X49" t="n">
         <v>1.06</v>
@@ -6297,28 +6297,28 @@
         <v>3.2</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="AD49" t="n">
         <v>1.25</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46010.69791666666</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.42</v>
+        <v>1.93</v>
       </c>
       <c r="M50" t="n">
-        <v>3.09</v>
+        <v>3.42</v>
       </c>
       <c r="N50" t="n">
-        <v>3</v>
+        <v>4.17</v>
       </c>
       <c r="O50" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="P50" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="R50" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="S50" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="T50" t="n">
-        <v>3.21</v>
+        <v>3.4</v>
       </c>
       <c r="U50" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V50" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W50" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X50" t="n">
         <v>1.08</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.97</v>
+        <v>4.2</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46010.70833333334</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,73 +6490,73 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.93</v>
+        <v>2.42</v>
       </c>
       <c r="M51" t="n">
-        <v>3.42</v>
+        <v>3.09</v>
       </c>
       <c r="N51" t="n">
-        <v>4.17</v>
+        <v>3</v>
       </c>
       <c r="O51" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="P51" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="R51" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="S51" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="T51" t="n">
-        <v>3.4</v>
+        <v>3.21</v>
       </c>
       <c r="U51" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V51" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W51" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X51" t="n">
         <v>1.08</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AC51" t="n">
-        <v>4.2</v>
+        <v>3.97</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE51" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46010.70833333334</v>

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI52"/>
+  <dimension ref="A1:V52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,90 +523,25 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over05</t>
+          <t>Odd_Over25</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under05</t>
+          <t>Odd_Under25</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over15</t>
+          <t>Odd_BTTS_Yes</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under15</t>
+          <t>Odd_BTTS_No</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>HT_Odd_Over25</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>HT_Odd_Under25</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>FT_Odd_Over05</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Over15</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Under15</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Over25</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Under25</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Over35</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Under35</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_BTTS_Yes</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_BTTS_No</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_H_D</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_A_D</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -677,57 +612,18 @@
         <v>3.1</v>
       </c>
       <c r="R2" t="n">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="S2" t="n">
-        <v>2.94</v>
+        <v>1.95</v>
       </c>
       <c r="T2" t="n">
-        <v>2.73</v>
+        <v>1.7</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V2" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF2" t="n">
         <v>2.05</v>
       </c>
-      <c r="AG2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI2" s="3" t="n">
+      <c r="V2" s="3" t="n">
         <v>46010.16666666666</v>
       </c>
     </row>
@@ -796,10 +692,10 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -807,46 +703,7 @@
       <c r="U3" t="n">
         <v>0</v>
       </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="3" t="n">
+      <c r="V3" s="3" t="n">
         <v>46010.25</v>
       </c>
     </row>
@@ -915,57 +772,18 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.28</v>
+        <v>1.7</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1</v>
+        <v>2.02</v>
       </c>
       <c r="T4" t="n">
-        <v>2.56</v>
+        <v>1.6</v>
       </c>
       <c r="U4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V4" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF4" t="n">
         <v>2.25</v>
       </c>
-      <c r="AG4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI4" s="3" t="n">
+      <c r="V4" s="3" t="n">
         <v>46010.25</v>
       </c>
     </row>
@@ -1045,46 +863,7 @@
       <c r="U5" t="n">
         <v>0</v>
       </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" s="3" t="n">
+      <c r="V5" s="3" t="n">
         <v>46010.29166666666</v>
       </c>
     </row>
@@ -1164,46 +943,7 @@
       <c r="U6" t="n">
         <v>0</v>
       </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="3" t="n">
+      <c r="V6" s="3" t="n">
         <v>46010.375</v>
       </c>
     </row>
@@ -1283,46 +1023,7 @@
       <c r="U7" t="n">
         <v>0</v>
       </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="3" t="n">
+      <c r="V7" s="3" t="n">
         <v>46010.375</v>
       </c>
     </row>
@@ -1402,46 +1103,7 @@
       <c r="U8" t="n">
         <v>0</v>
       </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="3" t="n">
+      <c r="V8" s="3" t="n">
         <v>46010.38541666666</v>
       </c>
     </row>
@@ -1521,46 +1183,7 @@
       <c r="U9" t="n">
         <v>0</v>
       </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="3" t="n">
+      <c r="V9" s="3" t="n">
         <v>46010.40625</v>
       </c>
     </row>
@@ -1640,46 +1263,7 @@
       <c r="U10" t="n">
         <v>0</v>
       </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" s="3" t="n">
+      <c r="V10" s="3" t="n">
         <v>46010.41666666666</v>
       </c>
     </row>
@@ -1759,46 +1343,7 @@
       <c r="U11" t="n">
         <v>0</v>
       </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" s="3" t="n">
+      <c r="V11" s="3" t="n">
         <v>46010.4375</v>
       </c>
     </row>
@@ -1878,46 +1423,7 @@
       <c r="U12" t="n">
         <v>0</v>
       </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="3" t="n">
+      <c r="V12" s="3" t="n">
         <v>46010.44791666666</v>
       </c>
     </row>
@@ -1997,46 +1503,7 @@
       <c r="U13" t="n">
         <v>0</v>
       </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="3" t="n">
+      <c r="V13" s="3" t="n">
         <v>46010.47916666666</v>
       </c>
     </row>
@@ -2116,46 +1583,7 @@
       <c r="U14" t="n">
         <v>0</v>
       </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="3" t="n">
+      <c r="V14" s="3" t="n">
         <v>46010.5</v>
       </c>
     </row>
@@ -2235,46 +1663,7 @@
       <c r="U15" t="n">
         <v>0</v>
       </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="3" t="n">
+      <c r="V15" s="3" t="n">
         <v>46010.51041666666</v>
       </c>
     </row>
@@ -2343,57 +1732,18 @@
         <v>1.91</v>
       </c>
       <c r="R16" t="n">
-        <v>1.37</v>
+        <v>1.74</v>
       </c>
       <c r="S16" t="n">
-        <v>2.81</v>
+        <v>1.96</v>
       </c>
       <c r="T16" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF16" t="n">
         <v>1.62</v>
       </c>
-      <c r="AG16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AI16" s="3" t="n">
+      <c r="V16" s="3" t="n">
         <v>46010.52083333334</v>
       </c>
     </row>
@@ -2473,46 +1823,7 @@
       <c r="U17" t="n">
         <v>0</v>
       </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" s="3" t="n">
+      <c r="V17" s="3" t="n">
         <v>46010.54166666666</v>
       </c>
     </row>
@@ -2527,7 +1838,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +1848,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,75 +1874,36 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V18" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3" t="n">
         <v>46010.58333333334</v>
       </c>
     </row>
@@ -2646,7 +1918,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +1928,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,75 +1954,36 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.66</v>
+        <v>1.87</v>
       </c>
       <c r="M19" t="n">
-        <v>3.66</v>
+        <v>3.74</v>
       </c>
       <c r="N19" t="n">
-        <v>5.25</v>
+        <v>3.29</v>
       </c>
       <c r="O19" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>2.51</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.7</v>
+        <v>3.82</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="S19" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="T19" t="n">
-        <v>2.99</v>
+        <v>1.44</v>
       </c>
       <c r="U19" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI19" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V19" s="3" t="n">
         <v>46010.58333333334</v>
       </c>
     </row>
@@ -2765,7 +1998,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2008,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,75 +2034,36 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.74</v>
+        <v>3.05</v>
       </c>
       <c r="N20" t="n">
-        <v>3.29</v>
+        <v>2.98</v>
       </c>
       <c r="O20" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="P20" t="n">
-        <v>2.51</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.24</v>
+        <v>2.2</v>
       </c>
       <c r="S20" t="n">
-        <v>3.34</v>
+        <v>1.62</v>
       </c>
       <c r="T20" t="n">
-        <v>2.32</v>
+        <v>1.83</v>
       </c>
       <c r="U20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI20" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V20" s="3" t="n">
         <v>46010.58333333334</v>
       </c>
     </row>
@@ -2884,7 +2078,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2088,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,75 +2114,36 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" s="3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V21" s="3" t="n">
         <v>46010.58333333334</v>
       </c>
     </row>
@@ -3003,7 +2158,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +2168,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,75 +2194,36 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3" t="n">
         <v>46010.60416666666</v>
       </c>
     </row>
@@ -3132,12 +2248,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,75 +2274,36 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="M23" t="n">
-        <v>3.02</v>
+        <v>3.52</v>
       </c>
       <c r="N23" t="n">
-        <v>3.83</v>
+        <v>3.4</v>
       </c>
       <c r="O23" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="P23" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.35</v>
+        <v>1.72</v>
       </c>
       <c r="S23" t="n">
-        <v>2.94</v>
+        <v>2.12</v>
       </c>
       <c r="T23" t="n">
-        <v>2.7</v>
+        <v>1.58</v>
       </c>
       <c r="U23" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V23" t="n">
-        <v>6</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI23" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="V23" s="3" t="n">
         <v>46010.60416666666</v>
       </c>
     </row>
@@ -3241,7 +2318,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +2328,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,75 +2354,36 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V24" s="3" t="n">
         <v>46010.60416666666</v>
       </c>
     </row>
@@ -3414,57 +2452,18 @@
         <v>4.62</v>
       </c>
       <c r="R25" t="n">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="S25" t="n">
-        <v>2.47</v>
+        <v>1.62</v>
       </c>
       <c r="T25" t="n">
-        <v>3.14</v>
+        <v>1.89</v>
       </c>
       <c r="U25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V25" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF25" t="n">
         <v>1.79</v>
       </c>
-      <c r="AG25" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AI25" s="3" t="n">
+      <c r="V25" s="3" t="n">
         <v>46010.61458333334</v>
       </c>
     </row>
@@ -3533,57 +2532,18 @@
         <v>4.52</v>
       </c>
       <c r="R26" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="S26" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="T26" t="n">
-        <v>2.41</v>
+        <v>1.53</v>
       </c>
       <c r="U26" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V26" t="n">
-        <v>5</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF26" t="n">
         <v>2.3</v>
       </c>
-      <c r="AG26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AI26" s="3" t="n">
+      <c r="V26" s="3" t="n">
         <v>46010.625</v>
       </c>
     </row>
@@ -3652,57 +2612,18 @@
         <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.39</v>
+        <v>1.9</v>
       </c>
       <c r="S27" t="n">
-        <v>2.73</v>
+        <v>1.8</v>
       </c>
       <c r="T27" t="n">
-        <v>2.85</v>
+        <v>1.71</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V27" t="n">
-        <v>7</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF27" t="n">
         <v>2.02</v>
       </c>
-      <c r="AG27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI27" s="3" t="n">
+      <c r="V27" s="3" t="n">
         <v>46010.625</v>
       </c>
     </row>
@@ -3771,57 +2692,18 @@
         <v>2.25</v>
       </c>
       <c r="R28" t="n">
-        <v>1.28</v>
+        <v>1.65</v>
       </c>
       <c r="S28" t="n">
-        <v>3.15</v>
+        <v>2.1</v>
       </c>
       <c r="T28" t="n">
-        <v>2.37</v>
+        <v>1.5</v>
       </c>
       <c r="U28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V28" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF28" t="n">
         <v>2.4</v>
       </c>
-      <c r="AG28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI28" s="3" t="n">
+      <c r="V28" s="3" t="n">
         <v>46010.64583333334</v>
       </c>
     </row>
@@ -3846,12 +2728,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,75 +2754,36 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="O29" t="n">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="P29" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="Q29" t="n">
         <v>3.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="S29" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="T29" t="n">
-        <v>2.44</v>
+        <v>1.44</v>
       </c>
       <c r="U29" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V29" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI29" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V29" s="3" t="n">
         <v>46010.66666666666</v>
       </c>
     </row>
@@ -3965,12 +2808,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,75 +2834,36 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="M30" t="n">
-        <v>7.5</v>
+        <v>5.4</v>
       </c>
       <c r="N30" t="n">
-        <v>11</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O30" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="P30" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>8.5</v>
+        <v>7.22</v>
       </c>
       <c r="R30" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="S30" t="n">
-        <v>5.1</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="U30" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="V30" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AI30" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V30" s="3" t="n">
         <v>46010.66666666666</v>
       </c>
     </row>
@@ -4074,7 +2878,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +2888,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,75 +2914,36 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.95</v>
+        <v>1.16</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="N31" t="n">
-        <v>3.55</v>
+        <v>11</v>
       </c>
       <c r="O31" t="n">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="P31" t="n">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.12</v>
+        <v>8.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="S31" t="n">
-        <v>2.91</v>
+        <v>4.4</v>
       </c>
       <c r="T31" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="U31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V31" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI31" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V31" s="3" t="n">
         <v>46010.66666666666</v>
       </c>
     </row>
@@ -4193,7 +2958,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +2968,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,75 +2994,36 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.31</v>
+        <v>1.93</v>
       </c>
       <c r="M32" t="n">
-        <v>5.4</v>
+        <v>3.55</v>
       </c>
       <c r="N32" t="n">
-        <v>8.550000000000001</v>
+        <v>3.55</v>
       </c>
       <c r="O32" t="n">
-        <v>1.73</v>
+        <v>2.41</v>
       </c>
       <c r="P32" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>7.22</v>
+        <v>4.25</v>
       </c>
       <c r="R32" t="n">
-        <v>1.18</v>
+        <v>1.68</v>
       </c>
       <c r="S32" t="n">
-        <v>3.94</v>
+        <v>2.06</v>
       </c>
       <c r="T32" t="n">
-        <v>2.01</v>
+        <v>1.6</v>
       </c>
       <c r="U32" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V32" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AI32" s="3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V32" s="3" t="n">
         <v>46010.66666666666</v>
       </c>
     </row>
@@ -4312,7 +3038,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +3048,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,75 +3074,36 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>5.8</v>
+        <v>2.35</v>
       </c>
       <c r="M33" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>1.37</v>
+        <v>2.65</v>
       </c>
       <c r="O33" t="n">
-        <v>6.5</v>
+        <v>2.8</v>
       </c>
       <c r="P33" t="n">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.73</v>
+        <v>3.2</v>
       </c>
       <c r="R33" t="n">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="S33" t="n">
-        <v>3.78</v>
+        <v>2.1</v>
       </c>
       <c r="T33" t="n">
-        <v>2.02</v>
+        <v>1.57</v>
       </c>
       <c r="U33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V33" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI33" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V33" s="3" t="n">
         <v>46010.66666666666</v>
       </c>
     </row>
@@ -4431,7 +3118,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +3128,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,75 +3154,36 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.15</v>
+        <v>5.8</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="N34" t="n">
-        <v>2.85</v>
+        <v>1.37</v>
       </c>
       <c r="O34" t="n">
-        <v>2.71</v>
+        <v>6.5</v>
       </c>
       <c r="P34" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.2</v>
+        <v>1.73</v>
       </c>
       <c r="R34" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S34" t="n">
-        <v>3.28</v>
+        <v>2.9</v>
       </c>
       <c r="T34" t="n">
-        <v>2.27</v>
+        <v>1.6</v>
       </c>
       <c r="U34" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V34" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI34" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V34" s="3" t="n">
         <v>46010.66666666666</v>
       </c>
     </row>
@@ -4560,12 +3208,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,75 +3234,36 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="M35" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N35" t="n">
         <v>3.55</v>
       </c>
       <c r="O35" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="P35" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.25</v>
+        <v>4.12</v>
       </c>
       <c r="R35" t="n">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="S35" t="n">
-        <v>3.08</v>
+        <v>1.91</v>
       </c>
       <c r="T35" t="n">
-        <v>2.41</v>
+        <v>1.64</v>
       </c>
       <c r="U35" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V35" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI35" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V35" s="3" t="n">
         <v>46010.66666666666</v>
       </c>
     </row>
@@ -4679,12 +3288,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,75 +3314,36 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.12</v>
+        <v>3.64</v>
       </c>
       <c r="M36" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>2.89</v>
+        <v>1.79</v>
       </c>
       <c r="O36" t="n">
-        <v>2.63</v>
+        <v>3.6</v>
       </c>
       <c r="P36" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.25</v>
+        <v>2.46</v>
       </c>
       <c r="R36" t="n">
-        <v>1.27</v>
+        <v>1.75</v>
       </c>
       <c r="S36" t="n">
-        <v>3.25</v>
+        <v>1.95</v>
       </c>
       <c r="T36" t="n">
-        <v>2.33</v>
+        <v>1.67</v>
       </c>
       <c r="U36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V36" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI36" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V36" s="3" t="n">
         <v>46010.67708333334</v>
       </c>
     </row>
@@ -4798,12 +3368,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,75 +3394,36 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.64</v>
+        <v>2.12</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>1.79</v>
+        <v>2.89</v>
       </c>
       <c r="O37" t="n">
-        <v>3.6</v>
+        <v>2.63</v>
       </c>
       <c r="P37" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.46</v>
+        <v>3.25</v>
       </c>
       <c r="R37" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="S37" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="T37" t="n">
-        <v>2.62</v>
+        <v>1.5</v>
       </c>
       <c r="U37" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V37" t="n">
-        <v>6</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI37" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V37" s="3" t="n">
         <v>46010.67708333334</v>
       </c>
     </row>
@@ -4907,7 +3438,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +3448,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,75 +3474,36 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V38" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="3" t="n">
         <v>46010.6875</v>
       </c>
     </row>
@@ -5036,12 +3528,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5091,46 +3583,7 @@
       <c r="U39" t="n">
         <v>0</v>
       </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" s="3" t="n">
+      <c r="V39" s="3" t="n">
         <v>46010.6875</v>
       </c>
     </row>
@@ -5145,7 +3598,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +3608,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,75 +3634,36 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.58</v>
+        <v>2.19</v>
       </c>
       <c r="M40" t="n">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="N40" t="n">
-        <v>2.81</v>
+        <v>3.39</v>
       </c>
       <c r="O40" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="P40" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.25</v>
+        <v>3.72</v>
       </c>
       <c r="R40" t="n">
-        <v>1.48</v>
+        <v>2.2</v>
       </c>
       <c r="S40" t="n">
-        <v>2.47</v>
+        <v>1.6</v>
       </c>
       <c r="T40" t="n">
-        <v>3.27</v>
+        <v>1.91</v>
       </c>
       <c r="U40" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V40" t="n">
-        <v>8</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE40" t="n">
         <v>1.83</v>
       </c>
-      <c r="AF40" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI40" s="3" t="n">
+      <c r="V40" s="3" t="n">
         <v>46010.6875</v>
       </c>
     </row>
@@ -5264,7 +3678,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +3688,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,75 +3714,36 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V41" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AI41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="3" t="n">
         <v>46010.6875</v>
       </c>
     </row>
@@ -5383,7 +3758,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +3768,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,75 +3794,36 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI42" s="3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V42" s="3" t="n">
         <v>46010.6875</v>
       </c>
     </row>
@@ -5502,7 +3838,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +3848,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,75 +3874,36 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI43" s="3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="V43" s="3" t="n">
         <v>46010.6875</v>
       </c>
     </row>
@@ -5675,57 +3972,18 @@
         <v>3.8</v>
       </c>
       <c r="R44" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="S44" t="n">
-        <v>2.44</v>
+        <v>1.6</v>
       </c>
       <c r="T44" t="n">
-        <v>3.25</v>
+        <v>1.95</v>
       </c>
       <c r="U44" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V44" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF44" t="n">
         <v>1.75</v>
       </c>
-      <c r="AG44" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI44" s="3" t="n">
+      <c r="V44" s="3" t="n">
         <v>46010.69791666666</v>
       </c>
     </row>
@@ -5740,7 +3998,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +4008,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,75 +4034,36 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.86</v>
+        <v>2.63</v>
       </c>
       <c r="M45" t="n">
-        <v>3.15</v>
+        <v>2.91</v>
       </c>
       <c r="N45" t="n">
-        <v>3.77</v>
+        <v>2.53</v>
       </c>
       <c r="O45" t="n">
-        <v>2.23</v>
+        <v>3.3</v>
       </c>
       <c r="P45" t="n">
         <v>2.15</v>
       </c>
       <c r="Q45" t="n">
-        <v>5.75</v>
+        <v>2.9</v>
       </c>
       <c r="R45" t="n">
-        <v>1.44</v>
+        <v>1.93</v>
       </c>
       <c r="S45" t="n">
-        <v>2.56</v>
+        <v>1.77</v>
       </c>
       <c r="T45" t="n">
-        <v>3.19</v>
+        <v>1.75</v>
       </c>
       <c r="U45" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V45" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI45" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V45" s="3" t="n">
         <v>46010.69791666666</v>
       </c>
     </row>
@@ -5913,57 +4132,18 @@
         <v>4.82</v>
       </c>
       <c r="R46" t="n">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="S46" t="n">
-        <v>2.73</v>
+        <v>1.85</v>
       </c>
       <c r="T46" t="n">
-        <v>2.73</v>
+        <v>1.75</v>
       </c>
       <c r="U46" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V46" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF46" t="n">
         <v>1.98</v>
       </c>
-      <c r="AG46" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI46" s="3" t="n">
+      <c r="V46" s="3" t="n">
         <v>46010.69791666666</v>
       </c>
     </row>
@@ -5978,7 +4158,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +4168,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,75 +4194,36 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.55</v>
+        <v>1.86</v>
       </c>
       <c r="M47" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N47" t="n">
-        <v>2.55</v>
+        <v>3.77</v>
       </c>
       <c r="O47" t="n">
-        <v>3.3</v>
+        <v>2.23</v>
       </c>
       <c r="P47" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.8</v>
+        <v>5.75</v>
       </c>
       <c r="R47" t="n">
-        <v>1.39</v>
+        <v>2.15</v>
       </c>
       <c r="S47" t="n">
-        <v>2.66</v>
+        <v>1.62</v>
       </c>
       <c r="T47" t="n">
-        <v>2.84</v>
+        <v>2.05</v>
       </c>
       <c r="U47" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V47" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X47" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI47" s="3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V47" s="3" t="n">
         <v>46010.69791666666</v>
       </c>
     </row>
@@ -6097,7 +4238,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +4248,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,75 +4274,36 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="M48" t="n">
-        <v>3.19</v>
+        <v>3.25</v>
       </c>
       <c r="N48" t="n">
-        <v>3.59</v>
+        <v>2.55</v>
       </c>
       <c r="O48" t="n">
-        <v>2.58</v>
+        <v>3.3</v>
       </c>
       <c r="P48" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.45</v>
+        <v>2.8</v>
       </c>
       <c r="R48" t="n">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="S48" t="n">
-        <v>2.69</v>
+        <v>1.72</v>
       </c>
       <c r="T48" t="n">
-        <v>2.85</v>
+        <v>1.75</v>
       </c>
       <c r="U48" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V48" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI48" s="3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V48" s="3" t="n">
         <v>46010.69791666666</v>
       </c>
     </row>
@@ -6216,7 +4318,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +4328,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,75 +4354,36 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.63</v>
+        <v>1.9</v>
       </c>
       <c r="M49" t="n">
-        <v>2.91</v>
+        <v>3.19</v>
       </c>
       <c r="N49" t="n">
-        <v>2.53</v>
+        <v>3.59</v>
       </c>
       <c r="O49" t="n">
-        <v>3.3</v>
+        <v>2.58</v>
       </c>
       <c r="P49" t="n">
         <v>2.15</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.9</v>
+        <v>4.45</v>
       </c>
       <c r="R49" t="n">
-        <v>1.41</v>
+        <v>1.95</v>
       </c>
       <c r="S49" t="n">
-        <v>2.69</v>
+        <v>1.75</v>
       </c>
       <c r="T49" t="n">
-        <v>2.96</v>
+        <v>1.8</v>
       </c>
       <c r="U49" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V49" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X49" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI49" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V49" s="3" t="n">
         <v>46010.69791666666</v>
       </c>
     </row>
@@ -6389,57 +4452,18 @@
         <v>4.6</v>
       </c>
       <c r="R50" t="n">
-        <v>1.51</v>
+        <v>2.33</v>
       </c>
       <c r="S50" t="n">
-        <v>2.55</v>
+        <v>1.6</v>
       </c>
       <c r="T50" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="U50" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V50" t="n">
-        <v>8</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X50" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF50" t="n">
         <v>1.73</v>
       </c>
-      <c r="AG50" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI50" s="3" t="n">
+      <c r="V50" s="3" t="n">
         <v>46010.70833333334</v>
       </c>
     </row>
@@ -6508,57 +4532,18 @@
         <v>3.75</v>
       </c>
       <c r="R51" t="n">
-        <v>1.46</v>
+        <v>2.15</v>
       </c>
       <c r="S51" t="n">
-        <v>2.53</v>
+        <v>1.63</v>
       </c>
       <c r="T51" t="n">
-        <v>3.21</v>
+        <v>1.85</v>
       </c>
       <c r="U51" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V51" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X51" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE51" t="n">
         <v>1.85</v>
       </c>
-      <c r="AF51" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI51" s="3" t="n">
+      <c r="V51" s="3" t="n">
         <v>46010.70833333334</v>
       </c>
     </row>
@@ -6627,57 +4612,18 @@
         <v>2.15</v>
       </c>
       <c r="R52" t="n">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="S52" t="n">
-        <v>2.94</v>
+        <v>1.85</v>
       </c>
       <c r="T52" t="n">
-        <v>2.62</v>
+        <v>1.75</v>
       </c>
       <c r="U52" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V52" t="n">
-        <v>6</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X52" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF52" t="n">
         <v>1.98</v>
       </c>
-      <c r="AG52" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI52" s="3" t="n">
+      <c r="V52" s="3" t="n">
         <v>46010.71875</v>
       </c>
     </row>

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V52"/>
+  <dimension ref="A1:AI52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,25 +523,90 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>HT_Odd_Over05</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Under05</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Over15</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Under15</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Over25</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Under25</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>FT_Odd_Over05</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Over15</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Under15</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>Odd_Over25</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under25</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Over35</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Under35</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_Yes</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_No</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_H_D</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_A_D</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -612,18 +677,57 @@
         <v>3.1</v>
       </c>
       <c r="R2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V2" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA2" t="n">
         <v>1.75</v>
       </c>
-      <c r="S2" t="n">
+      <c r="AB2" t="n">
         <v>1.95</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AC2" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE2" t="n">
         <v>1.7</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AF2" t="n">
         <v>2.05</v>
       </c>
-      <c r="V2" s="3" t="n">
+      <c r="AG2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI2" s="3" t="n">
         <v>46010.16666666666</v>
       </c>
     </row>
@@ -638,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -648,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Western Sydney Wanderers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -674,36 +778,75 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>1.76</v>
+        <v>2.35</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.67</v>
+        <v>1.28</v>
       </c>
       <c r="S3" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V3" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI3" s="3" t="n">
         <v>46010.25</v>
       </c>
     </row>
@@ -718,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -728,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Western Sydney Wanderers</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -754,36 +897,75 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="M4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>1.76</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="3" t="n">
         <v>46010.25</v>
       </c>
     </row>
@@ -863,7 +1045,46 @@
       <c r="U5" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="3" t="n">
         <v>46010.29166666666</v>
       </c>
     </row>
@@ -888,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -914,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -943,7 +1164,46 @@
       <c r="U6" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="3" t="n">
         <v>46010.375</v>
       </c>
     </row>
@@ -968,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -994,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1023,7 +1283,46 @@
       <c r="U7" t="n">
         <v>0</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="3" t="n">
         <v>46010.375</v>
       </c>
     </row>
@@ -1103,7 +1402,46 @@
       <c r="U8" t="n">
         <v>0</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="3" t="n">
         <v>46010.38541666666</v>
       </c>
     </row>
@@ -1183,7 +1521,46 @@
       <c r="U9" t="n">
         <v>0</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="3" t="n">
         <v>46010.40625</v>
       </c>
     </row>
@@ -1263,7 +1640,46 @@
       <c r="U10" t="n">
         <v>0</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="3" t="n">
         <v>46010.41666666666</v>
       </c>
     </row>
@@ -1343,7 +1759,46 @@
       <c r="U11" t="n">
         <v>0</v>
       </c>
-      <c r="V11" s="3" t="n">
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="3" t="n">
         <v>46010.4375</v>
       </c>
     </row>
@@ -1423,7 +1878,46 @@
       <c r="U12" t="n">
         <v>0</v>
       </c>
-      <c r="V12" s="3" t="n">
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="3" t="n">
         <v>46010.44791666666</v>
       </c>
     </row>
@@ -1503,7 +1997,46 @@
       <c r="U13" t="n">
         <v>0</v>
       </c>
-      <c r="V13" s="3" t="n">
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3" t="n">
         <v>46010.47916666666</v>
       </c>
     </row>
@@ -1583,7 +2116,46 @@
       <c r="U14" t="n">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="n">
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3" t="n">
         <v>46010.5</v>
       </c>
     </row>
@@ -1663,7 +2235,46 @@
       <c r="U15" t="n">
         <v>0</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3" t="n">
         <v>46010.51041666666</v>
       </c>
     </row>
@@ -1732,18 +2343,57 @@
         <v>1.91</v>
       </c>
       <c r="R16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA16" t="n">
         <v>1.74</v>
       </c>
-      <c r="S16" t="n">
+      <c r="AB16" t="n">
         <v>1.96</v>
       </c>
-      <c r="T16" t="n">
+      <c r="AC16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE16" t="n">
         <v>2.1</v>
       </c>
-      <c r="U16" t="n">
+      <c r="AF16" t="n">
         <v>1.62</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="AG16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AI16" s="3" t="n">
         <v>46010.52083333334</v>
       </c>
     </row>
@@ -1823,7 +2473,46 @@
       <c r="U17" t="n">
         <v>0</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="3" t="n">
         <v>46010.54166666666</v>
       </c>
     </row>
@@ -1838,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1848,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1874,36 +2563,75 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V18" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI18" s="3" t="n">
         <v>46010.58333333334</v>
       </c>
     </row>
@@ -1918,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1928,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1954,36 +2682,75 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="M19" t="n">
-        <v>3.74</v>
+        <v>3.66</v>
       </c>
       <c r="N19" t="n">
-        <v>3.29</v>
+        <v>5.25</v>
       </c>
       <c r="O19" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="P19" t="n">
-        <v>2.51</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.82</v>
+        <v>5.7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="T19" t="n">
-        <v>1.44</v>
+        <v>2.99</v>
       </c>
       <c r="U19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V19" s="3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI19" s="3" t="n">
         <v>46010.58333333334</v>
       </c>
     </row>
@@ -1998,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2008,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2034,36 +2801,75 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="M20" t="n">
-        <v>3.05</v>
+        <v>3.74</v>
       </c>
       <c r="N20" t="n">
-        <v>2.98</v>
+        <v>3.29</v>
       </c>
       <c r="O20" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>2.51</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2</v>
+        <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>1.62</v>
+        <v>3.34</v>
       </c>
       <c r="T20" t="n">
-        <v>1.83</v>
+        <v>2.32</v>
       </c>
       <c r="U20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V20" s="3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI20" s="3" t="n">
         <v>46010.58333333334</v>
       </c>
     </row>
@@ -2078,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2088,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2114,36 +2920,75 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="3" t="n">
         <v>46010.58333333334</v>
       </c>
     </row>
@@ -2158,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2168,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -2194,36 +3039,75 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V22" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI22" s="3" t="n">
         <v>46010.60416666666</v>
       </c>
     </row>
@@ -2248,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -2274,36 +3158,75 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="M23" t="n">
-        <v>3.52</v>
+        <v>3.02</v>
       </c>
       <c r="N23" t="n">
-        <v>3.4</v>
+        <v>3.83</v>
       </c>
       <c r="O23" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>1.72</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>2.12</v>
+        <v>2.94</v>
       </c>
       <c r="T23" t="n">
-        <v>1.58</v>
+        <v>2.7</v>
       </c>
       <c r="U23" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="V23" s="3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI23" s="3" t="n">
         <v>46010.60416666666</v>
       </c>
     </row>
@@ -2318,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2328,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -2354,36 +3277,75 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3" t="n">
         <v>46010.60416666666</v>
       </c>
     </row>
@@ -2452,18 +3414,57 @@
         <v>4.62</v>
       </c>
       <c r="R25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V25" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA25" t="n">
         <v>2.2</v>
       </c>
-      <c r="S25" t="n">
+      <c r="AB25" t="n">
         <v>1.62</v>
       </c>
-      <c r="T25" t="n">
+      <c r="AC25" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE25" t="n">
         <v>1.89</v>
       </c>
-      <c r="U25" t="n">
+      <c r="AF25" t="n">
         <v>1.79</v>
       </c>
-      <c r="V25" s="3" t="n">
+      <c r="AG25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI25" s="3" t="n">
         <v>46010.61458333334</v>
       </c>
     </row>
@@ -2532,18 +3533,57 @@
         <v>4.52</v>
       </c>
       <c r="R26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V26" t="n">
+        <v>5</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA26" t="n">
         <v>1.6</v>
       </c>
-      <c r="S26" t="n">
+      <c r="AB26" t="n">
         <v>2.25</v>
       </c>
-      <c r="T26" t="n">
+      <c r="AC26" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE26" t="n">
         <v>1.53</v>
       </c>
-      <c r="U26" t="n">
+      <c r="AF26" t="n">
         <v>2.3</v>
       </c>
-      <c r="V26" s="3" t="n">
+      <c r="AG26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI26" s="3" t="n">
         <v>46010.625</v>
       </c>
     </row>
@@ -2612,18 +3652,57 @@
         <v>3</v>
       </c>
       <c r="R27" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V27" t="n">
+        <v>7</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA27" t="n">
         <v>1.9</v>
       </c>
-      <c r="S27" t="n">
+      <c r="AB27" t="n">
         <v>1.8</v>
       </c>
-      <c r="T27" t="n">
+      <c r="AC27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE27" t="n">
         <v>1.71</v>
       </c>
-      <c r="U27" t="n">
+      <c r="AF27" t="n">
         <v>2.02</v>
       </c>
-      <c r="V27" s="3" t="n">
+      <c r="AG27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI27" s="3" t="n">
         <v>46010.625</v>
       </c>
     </row>
@@ -2692,18 +3771,57 @@
         <v>2.25</v>
       </c>
       <c r="R28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V28" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA28" t="n">
         <v>1.65</v>
       </c>
-      <c r="S28" t="n">
+      <c r="AB28" t="n">
         <v>2.1</v>
       </c>
-      <c r="T28" t="n">
+      <c r="AC28" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.5</v>
       </c>
-      <c r="U28" t="n">
+      <c r="AE28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF28" t="n">
         <v>2.4</v>
       </c>
-      <c r="V28" s="3" t="n">
+      <c r="AG28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI28" s="3" t="n">
         <v>46010.64583333334</v>
       </c>
     </row>
@@ -2728,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2754,36 +3872,75 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="O29" t="n">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="P29" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="Q29" t="n">
         <v>3.2</v>
       </c>
       <c r="R29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V29" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE29" t="n">
         <v>1.57</v>
       </c>
-      <c r="S29" t="n">
+      <c r="AF29" t="n">
         <v>2.3</v>
       </c>
-      <c r="T29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="U29" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="V29" s="3" t="n">
+      <c r="AG29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI29" s="3" t="n">
         <v>46010.66666666666</v>
       </c>
     </row>
@@ -2808,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2834,36 +3991,75 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="M30" t="n">
-        <v>5.4</v>
+        <v>7.5</v>
       </c>
       <c r="N30" t="n">
-        <v>8.550000000000001</v>
+        <v>11</v>
       </c>
       <c r="O30" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="P30" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>7.22</v>
+        <v>8.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>5.1</v>
       </c>
       <c r="T30" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="U30" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V30" s="3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V30" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AI30" s="3" t="n">
         <v>46010.66666666666</v>
       </c>
     </row>
@@ -2878,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2888,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2914,36 +4110,75 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.16</v>
+        <v>1.95</v>
       </c>
       <c r="M31" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>11</v>
+        <v>3.55</v>
       </c>
       <c r="O31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U31" t="n">
         <v>1.44</v>
       </c>
-      <c r="P31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V31" s="3" t="n">
+      <c r="V31" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI31" s="3" t="n">
         <v>46010.66666666666</v>
       </c>
     </row>
@@ -2958,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2968,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2994,36 +4229,75 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.93</v>
+        <v>1.31</v>
       </c>
       <c r="M32" t="n">
-        <v>3.55</v>
+        <v>5.4</v>
       </c>
       <c r="N32" t="n">
-        <v>3.55</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O32" t="n">
-        <v>2.41</v>
+        <v>1.73</v>
       </c>
       <c r="P32" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.25</v>
+        <v>7.22</v>
       </c>
       <c r="R32" t="n">
-        <v>1.68</v>
+        <v>1.18</v>
       </c>
       <c r="S32" t="n">
-        <v>2.06</v>
+        <v>3.94</v>
       </c>
       <c r="T32" t="n">
-        <v>1.6</v>
+        <v>2.01</v>
       </c>
       <c r="U32" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V32" s="3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V32" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AI32" s="3" t="n">
         <v>46010.66666666666</v>
       </c>
     </row>
@@ -3038,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3048,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -3074,36 +4348,75 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.35</v>
+        <v>5.8</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="N33" t="n">
-        <v>2.65</v>
+        <v>1.37</v>
       </c>
       <c r="O33" t="n">
-        <v>2.8</v>
+        <v>6.5</v>
       </c>
       <c r="P33" t="n">
-        <v>2.18</v>
+        <v>2.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.2</v>
+        <v>1.73</v>
       </c>
       <c r="R33" t="n">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="S33" t="n">
-        <v>2.1</v>
+        <v>3.78</v>
       </c>
       <c r="T33" t="n">
-        <v>1.57</v>
+        <v>2.02</v>
       </c>
       <c r="U33" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V33" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI33" s="3" t="n">
         <v>46010.66666666666</v>
       </c>
     </row>
@@ -3118,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3128,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -3154,36 +4467,75 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5.8</v>
+        <v>2.15</v>
       </c>
       <c r="M34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V34" t="n">
         <v>4.6</v>
       </c>
-      <c r="N34" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="O34" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V34" s="3" t="n">
+      <c r="W34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI34" s="3" t="n">
         <v>46010.66666666666</v>
       </c>
     </row>
@@ -3208,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -3234,36 +4586,75 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N35" t="n">
         <v>3.55</v>
       </c>
       <c r="O35" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="P35" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.12</v>
+        <v>4.25</v>
       </c>
       <c r="R35" t="n">
-        <v>1.73</v>
+        <v>1.3</v>
       </c>
       <c r="S35" t="n">
-        <v>1.91</v>
+        <v>3.08</v>
       </c>
       <c r="T35" t="n">
-        <v>1.64</v>
+        <v>2.41</v>
       </c>
       <c r="U35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V35" s="3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V35" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI35" s="3" t="n">
         <v>46010.66666666666</v>
       </c>
     </row>
@@ -3288,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -3314,36 +4705,75 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.64</v>
+        <v>2.12</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N36" t="n">
-        <v>1.79</v>
+        <v>2.89</v>
       </c>
       <c r="O36" t="n">
-        <v>3.6</v>
+        <v>2.63</v>
       </c>
       <c r="P36" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.46</v>
+        <v>3.25</v>
       </c>
       <c r="R36" t="n">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="S36" t="n">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="T36" t="n">
-        <v>1.67</v>
+        <v>2.33</v>
       </c>
       <c r="U36" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V36" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V36" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI36" s="3" t="n">
         <v>46010.67708333334</v>
       </c>
     </row>
@@ -3368,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -3394,36 +4824,75 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.12</v>
+        <v>3.64</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>2.89</v>
+        <v>1.79</v>
       </c>
       <c r="O37" t="n">
-        <v>2.63</v>
+        <v>3.6</v>
       </c>
       <c r="P37" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.25</v>
+        <v>2.46</v>
       </c>
       <c r="R37" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="S37" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="T37" t="n">
-        <v>1.5</v>
+        <v>2.62</v>
       </c>
       <c r="U37" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="V37" s="3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V37" t="n">
+        <v>6</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI37" s="3" t="n">
         <v>46010.67708333334</v>
       </c>
     </row>
@@ -3438,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3448,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -3474,36 +4943,75 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" s="3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V38" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI38" s="3" t="n">
         <v>46010.6875</v>
       </c>
     </row>
@@ -3528,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -3583,7 +5091,46 @@
       <c r="U39" t="n">
         <v>0</v>
       </c>
-      <c r="V39" s="3" t="n">
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" s="3" t="n">
         <v>46010.6875</v>
       </c>
     </row>
@@ -3598,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3608,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -3634,36 +5181,75 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" s="3" t="n">
         <v>46010.6875</v>
       </c>
     </row>
@@ -3678,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3688,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -3714,36 +5300,75 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" s="3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V41" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI41" s="3" t="n">
         <v>46010.6875</v>
       </c>
     </row>
@@ -3758,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3768,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -3794,36 +5419,75 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3" t="n">
         <v>46010.6875</v>
       </c>
     </row>
@@ -3838,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3848,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -3874,36 +5538,75 @@
         </is>
       </c>
       <c r="L43" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="M43" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R43" t="n">
         <v>1.48</v>
       </c>
-      <c r="M43" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N43" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O43" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.53</v>
-      </c>
       <c r="S43" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="T43" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V43" t="n">
+        <v>8</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB43" t="n">
         <v>1.65</v>
       </c>
-      <c r="U43" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="V43" s="3" t="n">
+      <c r="AC43" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI43" s="3" t="n">
         <v>46010.6875</v>
       </c>
     </row>
@@ -3972,18 +5675,57 @@
         <v>3.8</v>
       </c>
       <c r="R44" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V44" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA44" t="n">
         <v>2.2</v>
       </c>
-      <c r="S44" t="n">
+      <c r="AB44" t="n">
         <v>1.6</v>
       </c>
-      <c r="T44" t="n">
+      <c r="AC44" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE44" t="n">
         <v>1.95</v>
       </c>
-      <c r="U44" t="n">
+      <c r="AF44" t="n">
         <v>1.75</v>
       </c>
-      <c r="V44" s="3" t="n">
+      <c r="AG44" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI44" s="3" t="n">
         <v>46010.69791666666</v>
       </c>
     </row>
@@ -3998,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4008,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -4034,36 +5776,75 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.63</v>
+        <v>1.78</v>
       </c>
       <c r="M45" t="n">
-        <v>2.91</v>
+        <v>3.17</v>
       </c>
       <c r="N45" t="n">
-        <v>2.53</v>
+        <v>4.1</v>
       </c>
       <c r="O45" t="n">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="P45" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.9</v>
+        <v>4.82</v>
       </c>
       <c r="R45" t="n">
-        <v>1.93</v>
+        <v>1.35</v>
       </c>
       <c r="S45" t="n">
-        <v>1.77</v>
+        <v>2.73</v>
       </c>
       <c r="T45" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V45" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE45" t="n">
         <v>1.75</v>
       </c>
-      <c r="U45" t="n">
-        <v>2</v>
-      </c>
-      <c r="V45" s="3" t="n">
+      <c r="AF45" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI45" s="3" t="n">
         <v>46010.69791666666</v>
       </c>
     </row>
@@ -4088,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -4114,36 +5895,75 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="M46" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="N46" t="n">
-        <v>4.1</v>
+        <v>3.59</v>
       </c>
       <c r="O46" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="P46" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.82</v>
+        <v>4.45</v>
       </c>
       <c r="R46" t="n">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="S46" t="n">
-        <v>1.85</v>
+        <v>2.69</v>
       </c>
       <c r="T46" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V46" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB46" t="n">
         <v>1.75</v>
       </c>
-      <c r="U46" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V46" s="3" t="n">
+      <c r="AC46" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI46" s="3" t="n">
         <v>46010.69791666666</v>
       </c>
     </row>
@@ -4158,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4168,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -4194,36 +6014,75 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.86</v>
+        <v>2.55</v>
       </c>
       <c r="M47" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N47" t="n">
-        <v>3.77</v>
+        <v>2.55</v>
       </c>
       <c r="O47" t="n">
-        <v>2.23</v>
+        <v>3.3</v>
       </c>
       <c r="P47" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q47" t="n">
-        <v>5.75</v>
+        <v>2.8</v>
       </c>
       <c r="R47" t="n">
-        <v>2.15</v>
+        <v>1.39</v>
       </c>
       <c r="S47" t="n">
-        <v>1.62</v>
+        <v>2.66</v>
       </c>
       <c r="T47" t="n">
-        <v>2.05</v>
+        <v>2.84</v>
       </c>
       <c r="U47" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V47" s="3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V47" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI47" s="3" t="n">
         <v>46010.69791666666</v>
       </c>
     </row>
@@ -4238,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4248,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -4274,36 +6133,75 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.55</v>
+        <v>1.86</v>
       </c>
       <c r="M48" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N48" t="n">
-        <v>2.55</v>
+        <v>3.77</v>
       </c>
       <c r="O48" t="n">
-        <v>3.3</v>
+        <v>2.23</v>
       </c>
       <c r="P48" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.8</v>
+        <v>5.75</v>
       </c>
       <c r="R48" t="n">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="S48" t="n">
-        <v>1.72</v>
+        <v>2.56</v>
       </c>
       <c r="T48" t="n">
-        <v>1.75</v>
+        <v>3.19</v>
       </c>
       <c r="U48" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V48" s="3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V48" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI48" s="3" t="n">
         <v>46010.69791666666</v>
       </c>
     </row>
@@ -4318,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4328,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -4354,36 +6252,75 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.9</v>
+        <v>2.63</v>
       </c>
       <c r="M49" t="n">
-        <v>3.19</v>
+        <v>2.91</v>
       </c>
       <c r="N49" t="n">
-        <v>3.59</v>
+        <v>2.53</v>
       </c>
       <c r="O49" t="n">
-        <v>2.58</v>
+        <v>3.3</v>
       </c>
       <c r="P49" t="n">
         <v>2.15</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.45</v>
+        <v>2.9</v>
       </c>
       <c r="R49" t="n">
-        <v>1.95</v>
+        <v>1.41</v>
       </c>
       <c r="S49" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V49" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE49" t="n">
         <v>1.75</v>
       </c>
-      <c r="T49" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V49" s="3" t="n">
+      <c r="AF49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI49" s="3" t="n">
         <v>46010.69791666666</v>
       </c>
     </row>
@@ -4452,18 +6389,57 @@
         <v>4.6</v>
       </c>
       <c r="R50" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V50" t="n">
+        <v>8</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X50" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA50" t="n">
         <v>2.33</v>
       </c>
-      <c r="S50" t="n">
+      <c r="AB50" t="n">
         <v>1.6</v>
       </c>
-      <c r="T50" t="n">
+      <c r="AC50" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE50" t="n">
         <v>2</v>
       </c>
-      <c r="U50" t="n">
+      <c r="AF50" t="n">
         <v>1.73</v>
       </c>
-      <c r="V50" s="3" t="n">
+      <c r="AG50" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI50" s="3" t="n">
         <v>46010.70833333334</v>
       </c>
     </row>
@@ -4532,18 +6508,57 @@
         <v>3.75</v>
       </c>
       <c r="R51" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V51" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA51" t="n">
         <v>2.15</v>
       </c>
-      <c r="S51" t="n">
+      <c r="AB51" t="n">
         <v>1.63</v>
       </c>
-      <c r="T51" t="n">
+      <c r="AC51" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE51" t="n">
         <v>1.85</v>
       </c>
-      <c r="U51" t="n">
+      <c r="AF51" t="n">
         <v>1.85</v>
       </c>
-      <c r="V51" s="3" t="n">
+      <c r="AG51" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI51" s="3" t="n">
         <v>46010.70833333334</v>
       </c>
     </row>
@@ -4612,18 +6627,57 @@
         <v>2.15</v>
       </c>
       <c r="R52" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V52" t="n">
+        <v>6</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X52" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA52" t="n">
         <v>1.85</v>
       </c>
-      <c r="S52" t="n">
+      <c r="AB52" t="n">
         <v>1.85</v>
       </c>
-      <c r="T52" t="n">
+      <c r="AC52" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE52" t="n">
         <v>1.75</v>
       </c>
-      <c r="U52" t="n">
+      <c r="AF52" t="n">
         <v>1.98</v>
       </c>
-      <c r="V52" s="3" t="n">
+      <c r="AG52" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI52" s="3" t="n">
         <v>46010.71875</v>
       </c>
     </row>

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -698,7 +698,7 @@
         <v>1.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z2" t="n">
         <v>3.3</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Western Sydney Wanderers</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>2.35</v>
+        <v>1.76</v>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46010.25</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Western Sydney Wanderers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N4" t="n">
-        <v>1.76</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46010.25</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="N11" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1769,7 +1769,7 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Z11" t="n">
         <v>2.35</v>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="M14" t="n">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="N14" t="n">
         <v>2.75</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2334,13 +2334,13 @@
         <v>1.27</v>
       </c>
       <c r="O16" t="n">
-        <v>6.25</v>
+        <v>6.6</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="R16" t="n">
         <v>1.37</v>
@@ -2361,10 +2361,10 @@
         <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z16" t="n">
         <v>3.8</v>
@@ -2382,13 +2382,13 @@
         <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AH16" t="n">
         <v>1.06</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.66</v>
+        <v>1.87</v>
       </c>
       <c r="M19" t="n">
-        <v>3.66</v>
+        <v>3.74</v>
       </c>
       <c r="N19" t="n">
-        <v>5.25</v>
+        <v>3.29</v>
       </c>
       <c r="O19" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>2.51</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.7</v>
+        <v>3.82</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="S19" t="n">
-        <v>2.65</v>
+        <v>3.34</v>
       </c>
       <c r="T19" t="n">
-        <v>2.99</v>
+        <v>2.32</v>
       </c>
       <c r="U19" t="n">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="V19" t="n">
-        <v>7.8</v>
+        <v>5.15</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.04</v>
+        <v>1.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.6</v>
+        <v>2.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.74</v>
+        <v>3.05</v>
       </c>
       <c r="N20" t="n">
-        <v>3.29</v>
+        <v>2.98</v>
       </c>
       <c r="O20" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="P20" t="n">
-        <v>2.51</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="S20" t="n">
-        <v>3.34</v>
+        <v>2.44</v>
       </c>
       <c r="T20" t="n">
-        <v>2.32</v>
+        <v>3.16</v>
       </c>
       <c r="U20" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="V20" t="n">
-        <v>5.15</v>
+        <v>8.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="Z20" t="n">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="AA20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.8</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46010.58333333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46010.60416666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="M23" t="n">
-        <v>3.02</v>
+        <v>3.52</v>
       </c>
       <c r="N23" t="n">
-        <v>3.83</v>
+        <v>3.4</v>
       </c>
       <c r="O23" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="P23" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="R23" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="T23" t="n">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="U23" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="V23" t="n">
-        <v>6</v>
+        <v>5.65</v>
       </c>
       <c r="W23" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
         <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z23" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46010.60416666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46010.60416666666</v>
@@ -3396,16 +3396,16 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="O25" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="P25" t="n">
         <v>1.94</v>
@@ -3438,28 +3438,28 @@
         <v>1.33</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC25" t="n">
         <v>3.99</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
         <v>1.68</v>
@@ -3649,7 +3649,7 @@
         <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R27" t="n">
         <v>1.39</v>
@@ -3688,10 +3688,10 @@
         <v>3.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AF27" t="n">
         <v>2.02</v>
@@ -3762,13 +3762,13 @@
         <v>1.86</v>
       </c>
       <c r="O28" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P28" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="R28" t="n">
         <v>1.28</v>
@@ -3777,7 +3777,7 @@
         <v>3.15</v>
       </c>
       <c r="T28" t="n">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="U28" t="n">
         <v>1.5</v>
@@ -3792,10 +3792,10 @@
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.6</v>
+        <v>4.36</v>
       </c>
       <c r="AA28" t="n">
         <v>1.65</v>
@@ -3804,10 +3804,10 @@
         <v>2.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE28" t="n">
         <v>1.5</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="O29" t="n">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="P29" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="Q29" t="n">
         <v>3.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S29" t="n">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="T29" t="n">
-        <v>2.44</v>
+        <v>2.27</v>
       </c>
       <c r="U29" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="V29" t="n">
-        <v>5.75</v>
+        <v>4.6</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.63</v>
+        <v>2.28</v>
       </c>
       <c r="AD29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE29" t="n">
         <v>1.44</v>
       </c>
-      <c r="AE29" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AF29" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AG29" t="n">
         <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46010.66666666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="M30" t="n">
-        <v>7.5</v>
+        <v>5.4</v>
       </c>
       <c r="N30" t="n">
-        <v>11</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O30" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="P30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V30" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH30" t="n">
         <v>3.3</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="S30" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="V30" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>4.8</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="M31" t="n">
         <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O31" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="P31" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.12</v>
+        <v>3.9</v>
       </c>
       <c r="R31" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S31" t="n">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="T31" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="U31" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="V31" t="n">
-        <v>5.75</v>
+        <v>5.45</v>
       </c>
       <c r="W31" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X31" t="n">
         <v>1.04</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="M32" t="n">
-        <v>5.4</v>
+        <v>7.5</v>
       </c>
       <c r="N32" t="n">
-        <v>8.550000000000001</v>
+        <v>11</v>
       </c>
       <c r="O32" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="P32" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>7.22</v>
+        <v>8.5</v>
       </c>
       <c r="R32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V32" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AA32" t="n">
         <v>1.18</v>
       </c>
-      <c r="S32" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V32" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AB32" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AH32" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>5.8</v>
+        <v>2.35</v>
       </c>
       <c r="M33" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>1.37</v>
+        <v>2.65</v>
       </c>
       <c r="O33" t="n">
-        <v>6.5</v>
+        <v>2.8</v>
       </c>
       <c r="P33" t="n">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.73</v>
+        <v>3.2</v>
       </c>
       <c r="R33" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="S33" t="n">
-        <v>3.78</v>
+        <v>3.05</v>
       </c>
       <c r="T33" t="n">
-        <v>2.02</v>
+        <v>2.44</v>
       </c>
       <c r="U33" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="V33" t="n">
-        <v>4.1</v>
+        <v>5.75</v>
       </c>
       <c r="W33" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="Z33" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.93</v>
+        <v>2.63</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.77</v>
+        <v>1.44</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.15</v>
+        <v>5.8</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="N34" t="n">
-        <v>2.85</v>
+        <v>1.37</v>
       </c>
       <c r="O34" t="n">
-        <v>2.71</v>
+        <v>6.5</v>
       </c>
       <c r="P34" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.2</v>
+        <v>1.73</v>
       </c>
       <c r="R34" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="S34" t="n">
-        <v>3.28</v>
+        <v>3.78</v>
       </c>
       <c r="T34" t="n">
-        <v>2.27</v>
+        <v>2.04</v>
       </c>
       <c r="U34" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="V34" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="W34" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="X34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG34" t="n">
         <v>1.17</v>
       </c>
-      <c r="Z34" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH34" t="n">
-        <v>1.65</v>
+        <v>1.11</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="M35" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N35" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="O35" t="n">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="P35" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.25</v>
+        <v>4.13</v>
       </c>
       <c r="R35" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S35" t="n">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="T35" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="U35" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="V35" t="n">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="W35" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X35" t="n">
         <v>1.04</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.84</v>
+        <v>3.58</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.12</v>
+        <v>3.64</v>
       </c>
       <c r="M36" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>2.89</v>
+        <v>1.79</v>
       </c>
       <c r="O36" t="n">
-        <v>2.63</v>
+        <v>3.6</v>
       </c>
       <c r="P36" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.25</v>
+        <v>2.45</v>
       </c>
       <c r="R36" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="S36" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="T36" t="n">
-        <v>2.33</v>
+        <v>2.53</v>
       </c>
       <c r="U36" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="V36" t="n">
-        <v>5.45</v>
+        <v>6.5</v>
       </c>
       <c r="W36" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X36" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z36" t="n">
-        <v>4.6</v>
+        <v>3.58</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46010.67708333334</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.64</v>
+        <v>2.12</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>1.79</v>
+        <v>2.89</v>
       </c>
       <c r="O37" t="n">
-        <v>3.6</v>
+        <v>2.63</v>
       </c>
       <c r="P37" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.46</v>
+        <v>3.25</v>
       </c>
       <c r="R37" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="S37" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="T37" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="U37" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="V37" t="n">
-        <v>6</v>
+        <v>5.55</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X37" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.21</v>
+        <v>1.62</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46010.67708333334</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46010.6875</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46010.6875</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46010.6875</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46010.6875</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.58</v>
+        <v>1.48</v>
       </c>
       <c r="M43" t="n">
-        <v>3.06</v>
+        <v>4.6</v>
       </c>
       <c r="N43" t="n">
-        <v>2.81</v>
+        <v>5.7</v>
       </c>
       <c r="O43" t="n">
-        <v>3.3</v>
+        <v>1.85</v>
       </c>
       <c r="P43" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.25</v>
+        <v>5.8</v>
       </c>
       <c r="R43" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="S43" t="n">
-        <v>2.47</v>
+        <v>3.75</v>
       </c>
       <c r="T43" t="n">
-        <v>3.27</v>
+        <v>2.15</v>
       </c>
       <c r="U43" t="n">
-        <v>1.31</v>
+        <v>1.67</v>
       </c>
       <c r="V43" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="W43" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="X43" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.88</v>
+        <v>5.05</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AB43" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE43" t="n">
         <v>1.65</v>
       </c>
-      <c r="AC43" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AF43" t="n">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46010.6875</v>
@@ -5693,13 +5693,13 @@
         <v>1</v>
       </c>
       <c r="X44" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="AA44" t="n">
         <v>2.2</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.78</v>
+        <v>2.63</v>
       </c>
       <c r="M45" t="n">
-        <v>3.17</v>
+        <v>2.91</v>
       </c>
       <c r="N45" t="n">
-        <v>4.1</v>
+        <v>2.53</v>
       </c>
       <c r="O45" t="n">
-        <v>2.45</v>
+        <v>3.3</v>
       </c>
       <c r="P45" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.82</v>
+        <v>2.9</v>
       </c>
       <c r="R45" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="S45" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="T45" t="n">
-        <v>2.73</v>
+        <v>2.96</v>
       </c>
       <c r="U45" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="V45" t="n">
-        <v>6.85</v>
+        <v>7.5</v>
       </c>
       <c r="W45" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X45" t="n">
         <v>1.06</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AE45" t="n">
         <v>1.75</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46010.69791666666</v>
@@ -5904,13 +5904,13 @@
         <v>3.59</v>
       </c>
       <c r="O46" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="P46" t="n">
         <v>2.15</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.45</v>
+        <v>4.53</v>
       </c>
       <c r="R46" t="n">
         <v>1.36</v>
@@ -5931,10 +5931,10 @@
         <v>1.04</v>
       </c>
       <c r="X46" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z46" t="n">
         <v>3.2</v>
@@ -5949,7 +5949,7 @@
         <v>3.34</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE46" t="n">
         <v>1.8</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,58 +6014,58 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.55</v>
+        <v>1.78</v>
       </c>
       <c r="M47" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="N47" t="n">
-        <v>2.55</v>
+        <v>4.1</v>
       </c>
       <c r="O47" t="n">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="P47" t="n">
         <v>2.2</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.8</v>
+        <v>4.82</v>
       </c>
       <c r="R47" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S47" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U47" t="n">
         <v>1.39</v>
       </c>
-      <c r="S47" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.36</v>
-      </c>
       <c r="V47" t="n">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="W47" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X47" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA47" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="AD47" t="n">
         <v>1.3</v>
@@ -6077,10 +6077,10 @@
         <v>1.98</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46010.69791666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.86</v>
+        <v>2.55</v>
       </c>
       <c r="M48" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N48" t="n">
-        <v>3.77</v>
+        <v>2.55</v>
       </c>
       <c r="O48" t="n">
-        <v>2.23</v>
+        <v>3.3</v>
       </c>
       <c r="P48" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q48" t="n">
-        <v>5.75</v>
+        <v>2.8</v>
       </c>
       <c r="R48" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S48" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="T48" t="n">
-        <v>3.19</v>
+        <v>2.85</v>
       </c>
       <c r="U48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V48" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y48" t="n">
         <v>1.32</v>
       </c>
-      <c r="V48" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.38</v>
-      </c>
       <c r="Z48" t="n">
-        <v>2.83</v>
+        <v>3.4</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AC48" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AE48" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH48" t="n">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46010.69791666666</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.63</v>
+        <v>1.86</v>
       </c>
       <c r="M49" t="n">
-        <v>2.91</v>
+        <v>3.15</v>
       </c>
       <c r="N49" t="n">
-        <v>2.53</v>
+        <v>3.77</v>
       </c>
       <c r="O49" t="n">
-        <v>3.3</v>
+        <v>2.24</v>
       </c>
       <c r="P49" t="n">
         <v>2.15</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.9</v>
+        <v>5.75</v>
       </c>
       <c r="R49" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S49" t="n">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="T49" t="n">
-        <v>2.96</v>
+        <v>3.19</v>
       </c>
       <c r="U49" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="V49" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W49" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X49" t="n">
         <v>1.06</v>
       </c>
       <c r="Y49" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG49" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z49" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH49" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46010.69791666666</v>
@@ -6502,10 +6502,10 @@
         <v>2.8</v>
       </c>
       <c r="P51" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.75</v>
+        <v>3.96</v>
       </c>
       <c r="R51" t="n">
         <v>1.46</v>
@@ -6514,7 +6514,7 @@
         <v>2.53</v>
       </c>
       <c r="T51" t="n">
-        <v>3.21</v>
+        <v>2.8</v>
       </c>
       <c r="U51" t="n">
         <v>1.32</v>
@@ -6532,7 +6532,7 @@
         <v>1.36</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="AA51" t="n">
         <v>2.15</v>
@@ -6541,10 +6541,10 @@
         <v>1.63</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.97</v>
+        <v>4.1</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE51" t="n">
         <v>1.85</v>
@@ -6618,7 +6618,7 @@
         <v>1.85</v>
       </c>
       <c r="O52" t="n">
-        <v>5.2</v>
+        <v>4.55</v>
       </c>
       <c r="P52" t="n">
         <v>2.3</v>
@@ -6627,13 +6627,13 @@
         <v>2.15</v>
       </c>
       <c r="R52" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S52" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="T52" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="U52" t="n">
         <v>1.43</v>
@@ -6651,7 +6651,7 @@
         <v>1.21</v>
       </c>
       <c r="Z52" t="n">
-        <v>3.8</v>
+        <v>3.92</v>
       </c>
       <c r="AA52" t="n">
         <v>1.85</v>
@@ -6669,7 +6669,7 @@
         <v>1.75</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AG52" t="n">
         <v>1.29</v>

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="M2" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="O2" t="n">
         <v>2.9</v>
@@ -698,19 +698,19 @@
         <v>1.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="AD2" t="n">
         <v>1.3</v>
@@ -897,28 +897,28 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="M4" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="N4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="P4" t="n">
         <v>2.35</v>
       </c>
-      <c r="O4" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="R4" t="n">
         <v>1.28</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="T4" t="n">
         <v>2.53</v>
@@ -930,7 +930,7 @@
         <v>5.95</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
         <v>1.05</v>
@@ -942,16 +942,16 @@
         <v>4.17</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="AC4" t="n">
         <v>2.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE4" t="n">
         <v>1.6</v>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.2</v>
+        <v>4.34</v>
       </c>
       <c r="M5" t="n">
         <v>3.5</v>
@@ -1025,13 +1025,13 @@
         <v>1.7</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1055,34 +1055,34 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46010.29166666666</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="M7" t="n">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="N7" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="M11" t="n">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="N11" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46010.4375</v>
@@ -2325,19 +2325,19 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M16" t="n">
         <v>4.5</v>
       </c>
       <c r="N16" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="O16" t="n">
         <v>6.6</v>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="Q16" t="n">
         <v>1.88</v>
@@ -2349,10 +2349,10 @@
         <v>2.81</v>
       </c>
       <c r="T16" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="U16" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="V16" t="n">
         <v>6.4</v>
@@ -2367,13 +2367,13 @@
         <v>1.26</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AC16" t="n">
         <v>3.4</v>
@@ -2382,10 +2382,10 @@
         <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG16" t="n">
         <v>1.2</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="M20" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>2.98</v>
+        <v>3.33</v>
       </c>
       <c r="O20" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
-        <v>2.44</v>
+        <v>3.48</v>
       </c>
       <c r="T20" t="n">
-        <v>3.16</v>
+        <v>2.3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="V20" t="n">
-        <v>8.5</v>
+        <v>4.85</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="M21" t="n">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="O21" t="n">
         <v>2.15</v>
@@ -2971,7 +2971,7 @@
         <v>1.75</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AD21" t="n">
         <v>1.25</v>
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="O25" t="n">
         <v>2.62</v>
@@ -3411,7 +3411,7 @@
         <v>1.94</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.62</v>
+        <v>4.05</v>
       </c>
       <c r="R25" t="n">
         <v>1.44</v>
@@ -3429,7 +3429,7 @@
         <v>8.1</v>
       </c>
       <c r="W25" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
         <v>1.05</v>
@@ -3441,10 +3441,10 @@
         <v>2.83</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AC25" t="n">
         <v>3.99</v>
@@ -3453,16 +3453,16 @@
         <v>1.18</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46010.61458333334</v>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="M27" t="n">
-        <v>2.94</v>
+        <v>3.22</v>
       </c>
       <c r="N27" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="O27" t="n">
         <v>3.3</v>
@@ -3649,7 +3649,7 @@
         <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="R27" t="n">
         <v>1.39</v>
@@ -3679,10 +3679,10 @@
         <v>3.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC27" t="n">
         <v>3.3</v>
@@ -3691,7 +3691,7 @@
         <v>1.31</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AF27" t="n">
         <v>2.02</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.31</v>
+        <v>5.8</v>
       </c>
       <c r="M30" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="N30" t="n">
-        <v>8.550000000000001</v>
+        <v>1.37</v>
       </c>
       <c r="O30" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q30" t="n">
         <v>1.73</v>
       </c>
-      <c r="P30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>7.22</v>
-      </c>
       <c r="R30" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S30" t="n">
-        <v>3.94</v>
+        <v>3.78</v>
       </c>
       <c r="T30" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="U30" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="V30" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="W30" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X30" t="n">
         <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z30" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB30" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AF30" t="n">
         <v>2.25</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AH30" t="n">
-        <v>3.3</v>
+        <v>1.11</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4113,70 +4113,70 @@
         <v>1.85</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N31" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="O31" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="P31" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="R31" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S31" t="n">
-        <v>3.02</v>
+        <v>2.91</v>
       </c>
       <c r="T31" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="U31" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="V31" t="n">
-        <v>5.45</v>
+        <v>5.75</v>
       </c>
       <c r="W31" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X31" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.16</v>
+        <v>1.85</v>
       </c>
       <c r="M32" t="n">
-        <v>7.5</v>
+        <v>3.52</v>
       </c>
       <c r="N32" t="n">
-        <v>11</v>
+        <v>3.65</v>
       </c>
       <c r="O32" t="n">
-        <v>1.44</v>
+        <v>2.4</v>
       </c>
       <c r="P32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S32" t="n">
         <v>3.3</v>
       </c>
-      <c r="Q32" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="S32" t="n">
-        <v>5.1</v>
-      </c>
       <c r="T32" t="n">
-        <v>1.71</v>
+        <v>2.38</v>
       </c>
       <c r="U32" t="n">
-        <v>2.05</v>
+        <v>1.48</v>
       </c>
       <c r="V32" t="n">
-        <v>3.12</v>
+        <v>5.35</v>
       </c>
       <c r="W32" t="n">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="Z32" t="n">
-        <v>9.6</v>
+        <v>3.9</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.18</v>
+        <v>1.65</v>
       </c>
       <c r="AB32" t="n">
-        <v>4.4</v>
+        <v>2.15</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.53</v>
+        <v>2.7</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>4.8</v>
+        <v>1.85</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5.8</v>
+        <v>1.16</v>
       </c>
       <c r="M34" t="n">
-        <v>4.6</v>
+        <v>7.5</v>
       </c>
       <c r="N34" t="n">
-        <v>1.37</v>
+        <v>11</v>
       </c>
       <c r="O34" t="n">
-        <v>6.5</v>
+        <v>1.44</v>
       </c>
       <c r="P34" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.73</v>
+        <v>8.5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="S34" t="n">
-        <v>3.78</v>
+        <v>5.1</v>
       </c>
       <c r="T34" t="n">
-        <v>2.04</v>
+        <v>1.71</v>
       </c>
       <c r="U34" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="V34" t="n">
-        <v>4.1</v>
+        <v>3.12</v>
       </c>
       <c r="W34" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Z34" t="n">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.93</v>
+        <v>1.53</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.77</v>
+        <v>2.38</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.11</v>
+        <v>4.8</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.88</v>
+        <v>1.31</v>
       </c>
       <c r="M35" t="n">
-        <v>3.45</v>
+        <v>5.4</v>
       </c>
       <c r="N35" t="n">
-        <v>3.45</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O35" t="n">
-        <v>2.48</v>
+        <v>1.73</v>
       </c>
       <c r="P35" t="n">
-        <v>2.16</v>
+        <v>2.8</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.13</v>
+        <v>7.22</v>
       </c>
       <c r="R35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V35" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA35" t="n">
         <v>1.33</v>
       </c>
-      <c r="S35" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V35" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AB35" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.95</v>
+        <v>1.91</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.35</v>
+        <v>1.8</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46010.6875</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46010.6875</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.19</v>
+        <v>2.75</v>
       </c>
       <c r="M40" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="N40" t="n">
-        <v>3.39</v>
+        <v>2.37</v>
       </c>
       <c r="O40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46010.6875</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.58</v>
+        <v>1.48</v>
       </c>
       <c r="M42" t="n">
-        <v>3.06</v>
+        <v>4.6</v>
       </c>
       <c r="N42" t="n">
-        <v>2.81</v>
+        <v>5.7</v>
       </c>
       <c r="O42" t="n">
-        <v>3.3</v>
+        <v>1.85</v>
       </c>
       <c r="P42" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.25</v>
+        <v>5.8</v>
       </c>
       <c r="R42" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="S42" t="n">
-        <v>2.47</v>
+        <v>3.75</v>
       </c>
       <c r="T42" t="n">
-        <v>3.27</v>
+        <v>2.15</v>
       </c>
       <c r="U42" t="n">
-        <v>1.31</v>
+        <v>1.67</v>
       </c>
       <c r="V42" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="W42" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="X42" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.88</v>
+        <v>5.05</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AB42" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE42" t="n">
         <v>1.65</v>
       </c>
-      <c r="AC42" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AF42" t="n">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46010.6875</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.48</v>
+        <v>2.7</v>
       </c>
       <c r="M43" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="N43" t="n">
-        <v>5.7</v>
+        <v>2.4</v>
       </c>
       <c r="O43" t="n">
-        <v>1.85</v>
+        <v>3.3</v>
       </c>
       <c r="P43" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="Q43" t="n">
-        <v>5.8</v>
+        <v>3.26</v>
       </c>
       <c r="R43" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V43" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="AD43" t="n">
         <v>1.22</v>
       </c>
-      <c r="S43" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V43" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AE43" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46010.6875</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.26</v>
+        <v>1.86</v>
       </c>
       <c r="M44" t="n">
-        <v>2.83</v>
+        <v>3.15</v>
       </c>
       <c r="N44" t="n">
-        <v>3.08</v>
+        <v>3.77</v>
       </c>
       <c r="O44" t="n">
-        <v>2.9</v>
+        <v>2.24</v>
       </c>
       <c r="P44" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.8</v>
+        <v>5.75</v>
       </c>
       <c r="R44" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="S44" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="T44" t="n">
-        <v>3.25</v>
+        <v>3.19</v>
       </c>
       <c r="U44" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="V44" t="n">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="W44" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X44" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC44" t="n">
-        <v>4.5</v>
+        <v>3.91</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46010.69791666666</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.63</v>
+        <v>1.78</v>
       </c>
       <c r="M45" t="n">
-        <v>2.91</v>
+        <v>3.17</v>
       </c>
       <c r="N45" t="n">
-        <v>2.53</v>
+        <v>4.1</v>
       </c>
       <c r="O45" t="n">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="P45" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.9</v>
+        <v>4.82</v>
       </c>
       <c r="R45" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U45" t="n">
         <v>1.39</v>
       </c>
-      <c r="S45" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.36</v>
-      </c>
       <c r="V45" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W45" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X45" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE45" t="n">
         <v>1.75</v>
       </c>
       <c r="AF45" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46010.69791666666</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.9</v>
+        <v>2.63</v>
       </c>
       <c r="M46" t="n">
-        <v>3.19</v>
+        <v>2.91</v>
       </c>
       <c r="N46" t="n">
-        <v>3.59</v>
+        <v>2.53</v>
       </c>
       <c r="O46" t="n">
-        <v>2.56</v>
+        <v>3.3</v>
       </c>
       <c r="P46" t="n">
         <v>2.15</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.53</v>
+        <v>2.9</v>
       </c>
       <c r="R46" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S46" t="n">
         <v>2.69</v>
       </c>
       <c r="T46" t="n">
-        <v>2.85</v>
+        <v>2.96</v>
       </c>
       <c r="U46" t="n">
         <v>1.36</v>
       </c>
       <c r="V46" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="W46" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X46" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z46" t="n">
         <v>3.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="AD46" t="n">
         <v>1.24</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46010.69791666666</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="M47" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="N47" t="n">
-        <v>4.1</v>
+        <v>3.59</v>
       </c>
       <c r="O47" t="n">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="P47" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.82</v>
+        <v>4.53</v>
       </c>
       <c r="R47" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S47" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="T47" t="n">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="U47" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="V47" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="W47" t="n">
         <v>1.04</v>
       </c>
       <c r="X47" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.05</v>
+        <v>3.34</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AG47" t="n">
         <v>1.3</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46010.69791666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.55</v>
+        <v>2.26</v>
       </c>
       <c r="M48" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="O48" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T48" t="n">
         <v>3.25</v>
       </c>
-      <c r="N48" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="O48" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P48" t="n">
+      <c r="U48" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V48" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AA48" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q48" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V48" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>2</v>
-      </c>
       <c r="AB48" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AE48" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF48" t="n">
         <v>1.75</v>
       </c>
-      <c r="AF48" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AG48" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46010.69791666666</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.86</v>
+        <v>3</v>
       </c>
       <c r="M49" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N49" t="n">
-        <v>3.77</v>
+        <v>2.2</v>
       </c>
       <c r="O49" t="n">
-        <v>2.24</v>
+        <v>3.3</v>
       </c>
       <c r="P49" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q49" t="n">
-        <v>5.75</v>
+        <v>2.79</v>
       </c>
       <c r="R49" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S49" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="T49" t="n">
-        <v>3.19</v>
+        <v>2.85</v>
       </c>
       <c r="U49" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="V49" t="n">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="W49" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X49" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y49" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH49" t="n">
         <v>1.36</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>2.1</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46010.69791666666</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.93</v>
+        <v>2.42</v>
       </c>
       <c r="M50" t="n">
-        <v>3.42</v>
+        <v>3.09</v>
       </c>
       <c r="N50" t="n">
-        <v>4.17</v>
+        <v>3</v>
       </c>
       <c r="O50" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="P50" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.6</v>
+        <v>3.96</v>
       </c>
       <c r="R50" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="S50" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="T50" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="U50" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V50" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W50" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X50" t="n">
         <v>1.08</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AC50" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE50" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46010.70833333334</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,73 +6490,73 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.42</v>
+        <v>1.93</v>
       </c>
       <c r="M51" t="n">
-        <v>3.09</v>
+        <v>3.42</v>
       </c>
       <c r="N51" t="n">
-        <v>3</v>
+        <v>4.17</v>
       </c>
       <c r="O51" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="P51" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.96</v>
+        <v>4.6</v>
       </c>
       <c r="R51" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="S51" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="T51" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="U51" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V51" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W51" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X51" t="n">
         <v>1.08</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z51" t="n">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AC51" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46010.70833333334</v>
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="M52" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N52" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="O52" t="n">
         <v>4.55</v>
@@ -6651,13 +6651,13 @@
         <v>1.21</v>
       </c>
       <c r="Z52" t="n">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC52" t="n">
         <v>3</v>

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Western Sydney Wanderers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="N3" t="n">
-        <v>1.76</v>
+        <v>2.6</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46010.25</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Western Sydney Wanderers</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="M4" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>2.6</v>
+        <v>1.76</v>
       </c>
       <c r="O4" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46010.25</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="M7" t="n">
-        <v>2.85</v>
+        <v>2.97</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.68</v>
+        <v>2.43</v>
       </c>
       <c r="M21" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q21" t="n">
         <v>3.6</v>
       </c>
-      <c r="N21" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="O21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="P21" t="n">
+      <c r="R21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA21" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q21" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AB21" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46010.58333333334</v>
@@ -3158,37 +3158,37 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q23" t="n">
         <v>3.4</v>
       </c>
-      <c r="O23" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.78</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S23" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T23" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="U23" t="n">
         <v>1.55</v>
       </c>
       <c r="V23" t="n">
-        <v>5.65</v>
+        <v>5.55</v>
       </c>
       <c r="W23" t="n">
         <v>1.08</v>
@@ -3200,13 +3200,13 @@
         <v>1.22</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.05</v>
+        <v>4.58</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AC23" t="n">
         <v>2.6</v>
@@ -3215,16 +3215,16 @@
         <v>1.44</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46010.60416666666</v>
@@ -3277,16 +3277,16 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="M24" t="n">
-        <v>3.02</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>3.83</v>
+        <v>3.25</v>
       </c>
       <c r="O24" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="P24" t="n">
         <v>2.3</v>
@@ -3295,16 +3295,16 @@
         <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S24" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="T24" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="U24" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V24" t="n">
         <v>5.5</v>
@@ -3316,16 +3316,16 @@
         <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z24" t="n">
         <v>4.33</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AC24" t="n">
         <v>2.6</v>
@@ -3334,7 +3334,7 @@
         <v>1.44</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AF24" t="n">
         <v>2.25</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.82</v>
+        <v>2.65</v>
       </c>
       <c r="M26" t="n">
-        <v>3.8</v>
+        <v>3.22</v>
       </c>
       <c r="N26" t="n">
-        <v>3.6</v>
+        <v>2.37</v>
       </c>
       <c r="O26" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.52</v>
+        <v>3.1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="S26" t="n">
-        <v>3.18</v>
+        <v>2.73</v>
       </c>
       <c r="T26" t="n">
-        <v>2.41</v>
+        <v>2.85</v>
       </c>
       <c r="U26" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="V26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W26" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X26" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.48</v>
+        <v>3.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46010.625</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.65</v>
+        <v>1.7</v>
       </c>
       <c r="M27" t="n">
-        <v>3.22</v>
+        <v>3.75</v>
       </c>
       <c r="N27" t="n">
-        <v>2.37</v>
+        <v>3.75</v>
       </c>
       <c r="O27" t="n">
-        <v>3.3</v>
+        <v>2.15</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.1</v>
+        <v>4.47</v>
       </c>
       <c r="R27" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="S27" t="n">
-        <v>2.73</v>
+        <v>3.25</v>
       </c>
       <c r="T27" t="n">
-        <v>2.85</v>
+        <v>2.41</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="V27" t="n">
-        <v>7</v>
+        <v>4.95</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.3</v>
+        <v>2.48</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46010.625</v>
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="M28" t="n">
-        <v>3.41</v>
+        <v>3.6</v>
       </c>
       <c r="N28" t="n">
-        <v>1.86</v>
+        <v>2.01</v>
       </c>
       <c r="O28" t="n">
         <v>3.7</v>
@@ -3771,22 +3771,22 @@
         <v>2.4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S28" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="T28" t="n">
         <v>2.44</v>
       </c>
       <c r="U28" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="V28" t="n">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="W28" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X28" t="n">
         <v>1.03</v>
@@ -3795,13 +3795,13 @@
         <v>1.17</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.36</v>
+        <v>4.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC28" t="n">
         <v>2.55</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N29" t="n">
-        <v>2.85</v>
+        <v>3.95</v>
       </c>
       <c r="O29" t="n">
-        <v>2.71</v>
+        <v>2.3</v>
       </c>
       <c r="P29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T29" t="n">
         <v>2.45</v>
       </c>
-      <c r="Q29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.27</v>
-      </c>
       <c r="U29" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="V29" t="n">
-        <v>4.6</v>
+        <v>5.75</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X29" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.28</v>
+        <v>3</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AG29" t="n">
         <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46010.66666666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5.8</v>
+        <v>2.41</v>
       </c>
       <c r="M30" t="n">
-        <v>4.6</v>
+        <v>3.54</v>
       </c>
       <c r="N30" t="n">
-        <v>1.37</v>
+        <v>2.74</v>
       </c>
       <c r="O30" t="n">
-        <v>6.5</v>
+        <v>2.8</v>
       </c>
       <c r="P30" t="n">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.73</v>
+        <v>3.2</v>
       </c>
       <c r="R30" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V30" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y30" t="n">
         <v>1.22</v>
       </c>
-      <c r="S30" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U30" t="n">
+      <c r="Z30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA30" t="n">
         <v>1.7</v>
       </c>
-      <c r="V30" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AB30" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.93</v>
+        <v>2.62</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.77</v>
+        <v>1.44</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.85</v>
+        <v>1.1</v>
       </c>
       <c r="M31" t="n">
-        <v>3.65</v>
+        <v>7.5</v>
       </c>
       <c r="N31" t="n">
-        <v>3.95</v>
+        <v>10</v>
       </c>
       <c r="O31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V31" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AD31" t="n">
         <v>2.3</v>
       </c>
-      <c r="P31" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V31" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE31" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="M32" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>3.65</v>
+        <v>2.85</v>
       </c>
       <c r="O32" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="P32" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB32" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V32" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AC32" t="n">
-        <v>2.7</v>
+        <v>2.28</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AG32" t="n">
         <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.35</v>
+        <v>6.6</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="N33" t="n">
-        <v>2.65</v>
+        <v>1.3</v>
       </c>
       <c r="O33" t="n">
-        <v>2.8</v>
+        <v>6.5</v>
       </c>
       <c r="P33" t="n">
-        <v>2.18</v>
+        <v>2.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.2</v>
+        <v>1.73</v>
       </c>
       <c r="R33" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="S33" t="n">
-        <v>3.05</v>
+        <v>3.78</v>
       </c>
       <c r="T33" t="n">
-        <v>2.44</v>
+        <v>2.13</v>
       </c>
       <c r="U33" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="V33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z33" t="n">
         <v>5.75</v>
       </c>
-      <c r="W33" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AA33" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.53</v>
+        <v>1.11</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="M34" t="n">
-        <v>7.5</v>
+        <v>5.25</v>
       </c>
       <c r="N34" t="n">
-        <v>11</v>
+        <v>7.25</v>
       </c>
       <c r="O34" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="P34" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="Q34" t="n">
-        <v>8.5</v>
+        <v>6.96</v>
       </c>
       <c r="R34" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="S34" t="n">
-        <v>5.1</v>
+        <v>3.96</v>
       </c>
       <c r="T34" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="U34" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="V34" t="n">
-        <v>3.12</v>
+        <v>3.9</v>
       </c>
       <c r="W34" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z34" t="n">
-        <v>9.6</v>
+        <v>6.35</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AB34" t="n">
-        <v>4.4</v>
+        <v>2.88</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.53</v>
+        <v>1.97</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AG34" t="n">
         <v>1.08</v>
       </c>
       <c r="AH34" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.31</v>
+        <v>1.85</v>
       </c>
       <c r="M35" t="n">
-        <v>5.4</v>
+        <v>3.52</v>
       </c>
       <c r="N35" t="n">
-        <v>8.550000000000001</v>
+        <v>3.65</v>
       </c>
       <c r="O35" t="n">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="P35" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>7.22</v>
+        <v>3.8</v>
       </c>
       <c r="R35" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="S35" t="n">
-        <v>3.94</v>
+        <v>3.3</v>
       </c>
       <c r="T35" t="n">
-        <v>2.01</v>
+        <v>2.38</v>
       </c>
       <c r="U35" t="n">
-        <v>1.74</v>
+        <v>1.48</v>
       </c>
       <c r="V35" t="n">
-        <v>4.15</v>
+        <v>5.35</v>
       </c>
       <c r="W35" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="X35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="Z35" t="n">
-        <v>6.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="AB35" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.91</v>
+        <v>2.7</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AF35" t="n">
         <v>2.25</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AH35" t="n">
-        <v>3.3</v>
+        <v>1.85</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.64</v>
+        <v>2.25</v>
       </c>
       <c r="M36" t="n">
         <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>1.79</v>
+        <v>2.85</v>
       </c>
       <c r="O36" t="n">
-        <v>3.6</v>
+        <v>2.63</v>
       </c>
       <c r="P36" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V36" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF36" t="n">
         <v>2.45</v>
       </c>
-      <c r="R36" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V36" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AG36" t="n">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46010.67708333334</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.12</v>
+        <v>3.5</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>2.89</v>
+        <v>1.81</v>
       </c>
       <c r="O37" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="P37" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.25</v>
+        <v>2.42</v>
       </c>
       <c r="R37" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="S37" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="T37" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="U37" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="V37" t="n">
-        <v>5.55</v>
+        <v>6.5</v>
       </c>
       <c r="W37" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X37" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Z37" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.3</v>
+        <v>1.83</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46010.67708333334</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.44</v>
+        <v>1.48</v>
       </c>
       <c r="M38" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="N38" t="n">
-        <v>3</v>
+        <v>5.76</v>
       </c>
       <c r="O38" t="n">
-        <v>2.94</v>
+        <v>1.85</v>
       </c>
       <c r="P38" t="n">
-        <v>1.96</v>
+        <v>2.63</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.28</v>
+        <v>5.75</v>
       </c>
       <c r="R38" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="S38" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH38" t="n">
         <v>2.5</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V38" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.52</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46010.6875</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="M39" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N39" t="n">
-        <v>2.44</v>
+        <v>3</v>
       </c>
       <c r="O39" t="n">
-        <v>3.16</v>
+        <v>2.94</v>
       </c>
       <c r="P39" t="n">
-        <v>2.13</v>
+        <v>1.96</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.96</v>
+        <v>3.28</v>
       </c>
       <c r="R39" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="S39" t="n">
-        <v>2.92</v>
+        <v>2.5</v>
       </c>
       <c r="T39" t="n">
-        <v>2.6</v>
+        <v>3.28</v>
       </c>
       <c r="U39" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="V39" t="n">
-        <v>6.25</v>
+        <v>8.9</v>
       </c>
       <c r="W39" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X39" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.58</v>
+        <v>2.76</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.88</v>
+        <v>4.33</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.61</v>
+        <v>1.91</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46010.6875</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.48</v>
+        <v>2.6</v>
       </c>
       <c r="M42" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="N42" t="n">
-        <v>5.7</v>
+        <v>2.44</v>
       </c>
       <c r="O42" t="n">
-        <v>1.85</v>
+        <v>3.16</v>
       </c>
       <c r="P42" t="n">
-        <v>2.63</v>
+        <v>2.13</v>
       </c>
       <c r="Q42" t="n">
-        <v>5.8</v>
+        <v>2.96</v>
       </c>
       <c r="R42" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="S42" t="n">
-        <v>3.75</v>
+        <v>2.92</v>
       </c>
       <c r="T42" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="U42" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="V42" t="n">
-        <v>4.8</v>
+        <v>6.25</v>
       </c>
       <c r="W42" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="X42" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="Z42" t="n">
-        <v>5.05</v>
+        <v>3.58</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.45</v>
+        <v>1.92</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.63</v>
+        <v>1.32</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46010.6875</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.86</v>
+        <v>3</v>
       </c>
       <c r="M44" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N44" t="n">
-        <v>3.77</v>
+        <v>2.2</v>
       </c>
       <c r="O44" t="n">
-        <v>2.24</v>
+        <v>3.3</v>
       </c>
       <c r="P44" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q44" t="n">
-        <v>5.75</v>
+        <v>2.79</v>
       </c>
       <c r="R44" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S44" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="T44" t="n">
-        <v>3.19</v>
+        <v>2.85</v>
       </c>
       <c r="U44" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="V44" t="n">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="W44" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X44" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y44" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH44" t="n">
         <v>1.36</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>2.1</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46010.69791666666</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="M45" t="n">
-        <v>3.17</v>
+        <v>3.45</v>
       </c>
       <c r="N45" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="O45" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="P45" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.82</v>
+        <v>4.45</v>
       </c>
       <c r="R45" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S45" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="T45" t="n">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="U45" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="V45" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="W45" t="n">
         <v>1.04</v>
       </c>
       <c r="X45" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.05</v>
+        <v>3.34</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AG45" t="n">
         <v>1.3</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46010.69791666666</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.63</v>
+        <v>1.93</v>
       </c>
       <c r="M46" t="n">
-        <v>2.91</v>
+        <v>3.5</v>
       </c>
       <c r="N46" t="n">
-        <v>2.53</v>
+        <v>3.8</v>
       </c>
       <c r="O46" t="n">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="P46" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.9</v>
+        <v>3.92</v>
       </c>
       <c r="R46" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U46" t="n">
         <v>1.39</v>
       </c>
-      <c r="S46" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.36</v>
-      </c>
       <c r="V46" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W46" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X46" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE46" t="n">
         <v>1.75</v>
       </c>
       <c r="AF46" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46010.69791666666</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="M47" t="n">
-        <v>3.19</v>
+        <v>3.6</v>
       </c>
       <c r="N47" t="n">
-        <v>3.59</v>
+        <v>5.25</v>
       </c>
       <c r="O47" t="n">
-        <v>2.56</v>
+        <v>2.26</v>
       </c>
       <c r="P47" t="n">
         <v>2.15</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.53</v>
+        <v>5.75</v>
       </c>
       <c r="R47" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="S47" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="T47" t="n">
-        <v>2.85</v>
+        <v>3.16</v>
       </c>
       <c r="U47" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V47" t="n">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="W47" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X47" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.34</v>
+        <v>3.95</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AG47" t="n">
         <v>1.3</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46010.69791666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.26</v>
+        <v>2.84</v>
       </c>
       <c r="M48" t="n">
-        <v>2.83</v>
+        <v>3.3</v>
       </c>
       <c r="N48" t="n">
-        <v>3.08</v>
+        <v>2.36</v>
       </c>
       <c r="O48" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q48" t="n">
         <v>2.9</v>
       </c>
-      <c r="P48" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>3.8</v>
-      </c>
       <c r="R48" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="S48" t="n">
-        <v>2.44</v>
+        <v>2.69</v>
       </c>
       <c r="T48" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="U48" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="V48" t="n">
-        <v>9.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="W48" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X48" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AC48" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AG48" t="n">
         <v>1.36</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46010.69791666666</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3</v>
+        <v>2.32</v>
       </c>
       <c r="M49" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N49" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="O49" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="P49" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.79</v>
+        <v>3.8</v>
       </c>
       <c r="R49" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="S49" t="n">
-        <v>2.7</v>
+        <v>2.39</v>
       </c>
       <c r="T49" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="U49" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="V49" t="n">
-        <v>7.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W49" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="X49" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.94</v>
+        <v>2.35</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AE49" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF49" t="n">
         <v>1.75</v>
       </c>
-      <c r="AF49" t="n">
-        <v>2</v>
-      </c>
       <c r="AG49" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46010.69791666666</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="M50" t="n">
-        <v>3.09</v>
+        <v>3.31</v>
       </c>
       <c r="N50" t="n">
-        <v>3</v>
+        <v>4.04</v>
       </c>
       <c r="O50" t="n">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="P50" t="n">
         <v>1.97</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.96</v>
+        <v>4.32</v>
       </c>
       <c r="R50" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="S50" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="T50" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="U50" t="n">
         <v>1.32</v>
       </c>
       <c r="V50" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W50" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X50" t="n">
         <v>1.08</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AC50" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46010.70833333334</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,73 +6490,73 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.93</v>
+        <v>2.35</v>
       </c>
       <c r="M51" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="N51" t="n">
-        <v>4.17</v>
+        <v>3.1</v>
       </c>
       <c r="O51" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="P51" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="R51" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="S51" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="T51" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="U51" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V51" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y51" t="n">
         <v>1.33</v>
       </c>
-      <c r="V51" t="n">
-        <v>8</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X51" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.4</v>
-      </c>
       <c r="Z51" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AC51" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE51" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46010.70833333334</v>

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Western Sydney Wanderers</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="M3" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>2.6</v>
+        <v>1.76</v>
       </c>
       <c r="O3" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46010.25</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Western Sydney Wanderers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="N4" t="n">
-        <v>1.76</v>
+        <v>2.6</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46010.25</v>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.34</v>
+        <v>4.2</v>
       </c>
       <c r="M5" t="n">
         <v>3.5</v>
@@ -1730,34 +1730,34 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="M11" t="n">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="N11" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="P11" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="R11" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S11" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="T11" t="n">
         <v>3.58</v>
       </c>
       <c r="U11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="V11" t="n">
         <v>8.9</v>
@@ -1769,34 +1769,34 @@
         <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="AD11" t="n">
         <v>1.13</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46010.4375</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46010.58333333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46010.60416666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46010.60416666666</v>
@@ -3396,34 +3396,34 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O25" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="P25" t="n">
         <v>1.94</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.05</v>
+        <v>3.85</v>
       </c>
       <c r="R25" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S25" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="T25" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="U25" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V25" t="n">
         <v>8.1</v>
@@ -3432,22 +3432,22 @@
         <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y25" t="n">
         <v>1.33</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.99</v>
+        <v>4.1</v>
       </c>
       <c r="AD25" t="n">
         <v>1.18</v>
@@ -3456,7 +3456,7 @@
         <v>1.89</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AG25" t="n">
         <v>1.26</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.65</v>
+        <v>1.7</v>
       </c>
       <c r="M26" t="n">
-        <v>3.22</v>
+        <v>3.75</v>
       </c>
       <c r="N26" t="n">
-        <v>2.37</v>
+        <v>3.75</v>
       </c>
       <c r="O26" t="n">
-        <v>3.3</v>
+        <v>2.15</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.1</v>
+        <v>4.47</v>
       </c>
       <c r="R26" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="S26" t="n">
-        <v>2.73</v>
+        <v>3.25</v>
       </c>
       <c r="T26" t="n">
-        <v>2.85</v>
+        <v>2.41</v>
       </c>
       <c r="U26" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="V26" t="n">
-        <v>7</v>
+        <v>4.95</v>
       </c>
       <c r="W26" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X26" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.3</v>
+        <v>2.48</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46010.625</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.7</v>
+        <v>2.65</v>
       </c>
       <c r="M27" t="n">
-        <v>3.75</v>
+        <v>3.22</v>
       </c>
       <c r="N27" t="n">
-        <v>3.75</v>
+        <v>2.37</v>
       </c>
       <c r="O27" t="n">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="P27" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.47</v>
+        <v>3.1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="S27" t="n">
-        <v>3.25</v>
+        <v>2.73</v>
       </c>
       <c r="T27" t="n">
-        <v>2.41</v>
+        <v>2.85</v>
       </c>
       <c r="U27" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
-        <v>4.95</v>
+        <v>7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.35</v>
+        <v>1.83</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.48</v>
+        <v>3.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46010.625</v>
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="M29" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="N29" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="O29" t="n">
         <v>2.3</v>
@@ -3917,7 +3917,7 @@
         <v>3.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB29" t="n">
         <v>1.95</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.41</v>
+        <v>1.85</v>
       </c>
       <c r="M30" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>2.74</v>
+        <v>3.5</v>
       </c>
       <c r="O30" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="P30" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="R30" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="T30" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="U30" t="n">
         <v>1.48</v>
       </c>
       <c r="V30" t="n">
-        <v>5.75</v>
+        <v>5.35</v>
       </c>
       <c r="W30" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X30" t="n">
         <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AA30" t="n">
         <v>1.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AG30" t="n">
         <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.1</v>
+        <v>6.6</v>
       </c>
       <c r="M31" t="n">
-        <v>7.5</v>
+        <v>5.2</v>
       </c>
       <c r="N31" t="n">
-        <v>10</v>
+        <v>1.3</v>
       </c>
       <c r="O31" t="n">
-        <v>1.44</v>
+        <v>6.5</v>
       </c>
       <c r="P31" t="n">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>8.5</v>
+        <v>1.73</v>
       </c>
       <c r="R31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y31" t="n">
         <v>1.11</v>
       </c>
-      <c r="S31" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V31" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Z31" t="n">
-        <v>9.6</v>
+        <v>5.75</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="AB31" t="n">
-        <v>4.15</v>
+        <v>2.7</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.52</v>
+        <v>2.05</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AH31" t="n">
-        <v>4.8</v>
+        <v>1.11</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.15</v>
+        <v>1.3</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
       <c r="N32" t="n">
-        <v>2.85</v>
+        <v>7.25</v>
       </c>
       <c r="O32" t="n">
-        <v>2.7</v>
+        <v>1.73</v>
       </c>
       <c r="P32" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.2</v>
+        <v>6.96</v>
       </c>
       <c r="R32" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="S32" t="n">
-        <v>3.28</v>
+        <v>3.96</v>
       </c>
       <c r="T32" t="n">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="U32" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="V32" t="n">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="W32" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="Z32" t="n">
-        <v>4.8</v>
+        <v>6.35</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.28</v>
+        <v>1.97</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.65</v>
+        <v>3.3</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>6.6</v>
+        <v>1.1</v>
       </c>
       <c r="M33" t="n">
-        <v>5.2</v>
+        <v>7.5</v>
       </c>
       <c r="N33" t="n">
-        <v>1.3</v>
+        <v>10</v>
       </c>
       <c r="O33" t="n">
-        <v>6.5</v>
+        <v>1.44</v>
       </c>
       <c r="P33" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.73</v>
+        <v>8.5</v>
       </c>
       <c r="R33" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="S33" t="n">
-        <v>3.78</v>
+        <v>5.15</v>
       </c>
       <c r="T33" t="n">
-        <v>2.13</v>
+        <v>1.71</v>
       </c>
       <c r="U33" t="n">
-        <v>1.7</v>
+        <v>2.14</v>
       </c>
       <c r="V33" t="n">
-        <v>4.1</v>
+        <v>3.12</v>
       </c>
       <c r="W33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AA33" t="n">
         <v>1.16</v>
       </c>
-      <c r="X33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AB33" t="n">
-        <v>2.7</v>
+        <v>4.15</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.05</v>
+        <v>1.52</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.11</v>
+        <v>4.8</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.3</v>
+        <v>2.41</v>
       </c>
       <c r="M34" t="n">
-        <v>5.25</v>
+        <v>3.54</v>
       </c>
       <c r="N34" t="n">
-        <v>7.25</v>
+        <v>2.74</v>
       </c>
       <c r="O34" t="n">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="P34" t="n">
-        <v>2.8</v>
+        <v>2.18</v>
       </c>
       <c r="Q34" t="n">
-        <v>6.96</v>
+        <v>3.2</v>
       </c>
       <c r="R34" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="S34" t="n">
-        <v>3.96</v>
+        <v>3.05</v>
       </c>
       <c r="T34" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="U34" t="n">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="V34" t="n">
-        <v>3.9</v>
+        <v>5.75</v>
       </c>
       <c r="W34" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="Z34" t="n">
-        <v>6.35</v>
+        <v>4.2</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.97</v>
+        <v>2.62</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AE34" t="n">
         <v>1.57</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>3.3</v>
+        <v>1.53</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="M35" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="N35" t="n">
-        <v>3.65</v>
+        <v>2.85</v>
       </c>
       <c r="O35" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="P35" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V35" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB35" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q35" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V35" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AC35" t="n">
-        <v>2.7</v>
+        <v>2.28</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AG35" t="n">
         <v>1.3</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.48</v>
+        <v>3.4</v>
       </c>
       <c r="M38" t="n">
-        <v>4.9</v>
+        <v>3.15</v>
       </c>
       <c r="N38" t="n">
-        <v>5.76</v>
+        <v>2.08</v>
       </c>
       <c r="O38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.54</v>
+        <v>2.1</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.43</v>
+        <v>1.65</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46010.6875</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S39" t="n">
         <v>2.44</v>
       </c>
-      <c r="M39" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N39" t="n">
-        <v>3</v>
-      </c>
-      <c r="O39" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.5</v>
-      </c>
       <c r="T39" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="U39" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="V39" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="W39" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X39" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC39" t="n">
-        <v>4.33</v>
+        <v>4.02</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AG39" t="n">
         <v>1.36</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46010.6875</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="M40" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N40" t="n">
-        <v>2.37</v>
+        <v>3</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46010.6875</v>
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="M41" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N41" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="M42" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N42" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="O42" t="n">
-        <v>3.16</v>
+        <v>3.38</v>
       </c>
       <c r="P42" t="n">
-        <v>2.13</v>
+        <v>1.96</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="R42" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="S42" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V42" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z42" t="n">
         <v>2.92</v>
       </c>
-      <c r="T42" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V42" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y42" t="n">
+      <c r="AA42" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AD42" t="n">
         <v>1.21</v>
       </c>
-      <c r="Z42" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AE42" t="n">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46010.6875</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.7</v>
+        <v>1.48</v>
       </c>
       <c r="M43" t="n">
-        <v>2.9</v>
+        <v>4.9</v>
       </c>
       <c r="N43" t="n">
-        <v>2.4</v>
+        <v>5.76</v>
       </c>
       <c r="O43" t="n">
-        <v>3.3</v>
+        <v>1.85</v>
       </c>
       <c r="P43" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.26</v>
+        <v>5.75</v>
       </c>
       <c r="R43" t="n">
-        <v>1.49</v>
+        <v>1.22</v>
       </c>
       <c r="S43" t="n">
-        <v>2.44</v>
+        <v>3.66</v>
       </c>
       <c r="T43" t="n">
-        <v>3.27</v>
+        <v>2.15</v>
       </c>
       <c r="U43" t="n">
-        <v>1.31</v>
+        <v>1.66</v>
       </c>
       <c r="V43" t="n">
-        <v>8.1</v>
+        <v>4.8</v>
       </c>
       <c r="W43" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="X43" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.88</v>
+        <v>5.05</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.2</v>
+        <v>1.54</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.62</v>
+        <v>2.43</v>
       </c>
       <c r="AC43" t="n">
-        <v>4.02</v>
+        <v>2.33</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46010.6875</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,58 +5657,58 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3</v>
+        <v>1.93</v>
       </c>
       <c r="M44" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N44" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="O44" t="n">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="P44" t="n">
         <v>2.2</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.79</v>
+        <v>3.92</v>
       </c>
       <c r="R44" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S44" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="T44" t="n">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="U44" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="V44" t="n">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="W44" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X44" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="AD44" t="n">
         <v>1.3</v>
@@ -5717,13 +5717,13 @@
         <v>1.75</v>
       </c>
       <c r="AF44" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46010.69791666666</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="M45" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N45" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="O45" t="n">
-        <v>2.58</v>
+        <v>2.9</v>
       </c>
       <c r="P45" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.45</v>
+        <v>3.8</v>
       </c>
       <c r="R45" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V45" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG45" t="n">
         <v>1.36</v>
       </c>
-      <c r="S45" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V45" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH45" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46010.69791666666</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="M46" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N46" t="n">
-        <v>3.8</v>
+        <v>5.25</v>
       </c>
       <c r="O46" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="P46" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V46" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA46" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q46" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S46" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V46" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AB46" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.05</v>
+        <v>3.95</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="AG46" t="n">
         <v>1.3</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46010.69791666666</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="M47" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N47" t="n">
         <v>3.6</v>
       </c>
-      <c r="N47" t="n">
-        <v>5.25</v>
-      </c>
       <c r="O47" t="n">
-        <v>2.26</v>
+        <v>2.58</v>
       </c>
       <c r="P47" t="n">
         <v>2.15</v>
       </c>
       <c r="Q47" t="n">
-        <v>5.75</v>
+        <v>4.45</v>
       </c>
       <c r="R47" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="S47" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="T47" t="n">
-        <v>3.16</v>
+        <v>2.85</v>
       </c>
       <c r="U47" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V47" t="n">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="W47" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X47" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.95</v>
+        <v>3.34</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AE47" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AG47" t="n">
         <v>1.3</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46010.69791666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,61 +6133,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="M48" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N48" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="O48" t="n">
         <v>3.3</v>
       </c>
       <c r="P48" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="R48" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S48" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="T48" t="n">
-        <v>2.96</v>
+        <v>2.85</v>
       </c>
       <c r="U48" t="n">
         <v>1.37</v>
       </c>
       <c r="V48" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="W48" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X48" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y48" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD48" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.25</v>
       </c>
       <c r="AE48" t="n">
         <v>1.75</v>
@@ -6196,10 +6196,10 @@
         <v>2</v>
       </c>
       <c r="AG48" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH48" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.4</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46010.69791666666</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.32</v>
+        <v>2.84</v>
       </c>
       <c r="M49" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O49" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V49" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z49" t="n">
         <v>3.2</v>
       </c>
-      <c r="N49" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O49" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P49" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S49" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="T49" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V49" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1</v>
-      </c>
-      <c r="X49" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AA49" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AC49" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AG49" t="n">
         <v>1.36</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46010.69791666666</v>
@@ -6371,40 +6371,40 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="M50" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="N50" t="n">
-        <v>4.04</v>
+        <v>4.2</v>
       </c>
       <c r="O50" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="P50" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.32</v>
+        <v>4.6</v>
       </c>
       <c r="R50" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="S50" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="T50" t="n">
         <v>3.1</v>
       </c>
       <c r="U50" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V50" t="n">
         <v>8.5</v>
       </c>
       <c r="W50" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X50" t="n">
         <v>1.08</v>
@@ -6416,16 +6416,16 @@
         <v>2.7</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AC50" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE50" t="n">
         <v>1.99</v>
@@ -6434,7 +6434,7 @@
         <v>1.73</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH50" t="n">
         <v>1.8</v>
@@ -6490,31 +6490,31 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="M51" t="n">
         <v>3.25</v>
       </c>
       <c r="N51" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O51" t="n">
         <v>2.8</v>
       </c>
       <c r="P51" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.7</v>
+        <v>3.96</v>
       </c>
       <c r="R51" t="n">
         <v>1.46</v>
       </c>
       <c r="S51" t="n">
-        <v>2.53</v>
+        <v>2.69</v>
       </c>
       <c r="T51" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U51" t="n">
         <v>1.31</v>
@@ -6529,34 +6529,34 @@
         <v>1.06</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z51" t="n">
         <v>2.9</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AC51" t="n">
         <v>4.1</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE51" t="n">
         <v>1.85</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46010.70833333334</v>
@@ -6609,37 +6609,37 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="M52" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N52" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="O52" t="n">
-        <v>4.55</v>
+        <v>5.2</v>
       </c>
       <c r="P52" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="R52" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S52" t="n">
         <v>2.89</v>
       </c>
       <c r="T52" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="U52" t="n">
         <v>1.43</v>
       </c>
       <c r="V52" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="W52" t="n">
         <v>1.06</v>
@@ -6648,28 +6648,28 @@
         <v>1.05</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z52" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AB52" t="n">
         <v>1.95</v>
       </c>
       <c r="AC52" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE52" t="n">
         <v>1.75</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AG52" t="n">
         <v>1.29</v>

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.93</v>
+        <v>2.43</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="N18" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="P18" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="R18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.22</v>
       </c>
-      <c r="S18" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V18" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AE18" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.43</v>
+        <v>1.93</v>
       </c>
       <c r="M21" t="n">
-        <v>3.04</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="O21" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="R21" t="n">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="S21" t="n">
-        <v>2.71</v>
+        <v>3.48</v>
       </c>
       <c r="T21" t="n">
-        <v>3.19</v>
+        <v>2.3</v>
       </c>
       <c r="U21" t="n">
-        <v>1.32</v>
+        <v>1.58</v>
       </c>
       <c r="V21" t="n">
-        <v>8.6</v>
+        <v>4.85</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.95</v>
+        <v>2.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46010.58333333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46010.60416666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46010.60416666666</v>
@@ -3753,22 +3753,22 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="M28" t="n">
-        <v>3.6</v>
+        <v>3.41</v>
       </c>
       <c r="N28" t="n">
-        <v>2.01</v>
+        <v>1.86</v>
       </c>
       <c r="O28" t="n">
         <v>3.7</v>
       </c>
       <c r="P28" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="R28" t="n">
         <v>1.29</v>
@@ -3777,10 +3777,10 @@
         <v>3.12</v>
       </c>
       <c r="T28" t="n">
-        <v>2.44</v>
+        <v>2.33</v>
       </c>
       <c r="U28" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V28" t="n">
         <v>5.25</v>
@@ -3792,31 +3792,31 @@
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.1</v>
+        <v>4.36</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AH28" t="n">
         <v>1.3</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="M29" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>3.45</v>
+        <v>2.85</v>
       </c>
       <c r="O29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB29" t="n">
         <v>2.3</v>
       </c>
-      <c r="P29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U29" t="n">
+      <c r="AC29" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE29" t="n">
         <v>1.44</v>
       </c>
-      <c r="V29" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AF29" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="AG29" t="n">
         <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46010.66666666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,61 +3991,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.85</v>
+        <v>5.8</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="N30" t="n">
-        <v>3.5</v>
+        <v>1.37</v>
       </c>
       <c r="O30" t="n">
-        <v>2.4</v>
+        <v>6.5</v>
       </c>
       <c r="P30" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.8</v>
+        <v>1.73</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="S30" t="n">
-        <v>3.3</v>
+        <v>3.78</v>
       </c>
       <c r="T30" t="n">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="U30" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="V30" t="n">
-        <v>5.35</v>
+        <v>4.4</v>
       </c>
       <c r="W30" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.9</v>
+        <v>6</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.02</v>
+        <v>2.9</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.7</v>
+        <v>1.93</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AE30" t="n">
         <v>1.6</v>
@@ -4054,10 +4054,10 @@
         <v>2.25</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.85</v>
+        <v>1.11</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>6.6</v>
+        <v>1.88</v>
       </c>
       <c r="M31" t="n">
-        <v>5.2</v>
+        <v>3.45</v>
       </c>
       <c r="N31" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V31" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG31" t="n">
         <v>1.3</v>
       </c>
-      <c r="O31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AH31" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.1</v>
+        <v>1.85</v>
       </c>
       <c r="M33" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="O33" t="n">
-        <v>1.44</v>
+        <v>2.4</v>
       </c>
       <c r="P33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S33" t="n">
         <v>3.3</v>
       </c>
-      <c r="Q33" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="S33" t="n">
-        <v>5.15</v>
-      </c>
       <c r="T33" t="n">
-        <v>1.71</v>
+        <v>2.38</v>
       </c>
       <c r="U33" t="n">
-        <v>2.14</v>
+        <v>1.48</v>
       </c>
       <c r="V33" t="n">
-        <v>3.12</v>
+        <v>5.35</v>
       </c>
       <c r="W33" t="n">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="Z33" t="n">
-        <v>9.6</v>
+        <v>3.9</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.16</v>
+        <v>1.7</v>
       </c>
       <c r="AB33" t="n">
-        <v>4.15</v>
+        <v>2.02</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.52</v>
+        <v>2.7</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>4.8</v>
+        <v>1.85</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.41</v>
+        <v>1.1</v>
       </c>
       <c r="M34" t="n">
-        <v>3.54</v>
+        <v>7.5</v>
       </c>
       <c r="N34" t="n">
-        <v>2.74</v>
+        <v>10</v>
       </c>
       <c r="O34" t="n">
-        <v>2.8</v>
+        <v>1.44</v>
       </c>
       <c r="P34" t="n">
-        <v>2.18</v>
+        <v>3.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.2</v>
+        <v>8.5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="S34" t="n">
-        <v>3.05</v>
+        <v>5.15</v>
       </c>
       <c r="T34" t="n">
-        <v>2.44</v>
+        <v>1.71</v>
       </c>
       <c r="U34" t="n">
-        <v>1.48</v>
+        <v>2.14</v>
       </c>
       <c r="V34" t="n">
-        <v>5.75</v>
+        <v>3.12</v>
       </c>
       <c r="W34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG34" t="n">
         <v>1.08</v>
       </c>
-      <c r="X34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH34" t="n">
-        <v>1.53</v>
+        <v>4.8</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.15</v>
+        <v>2.41</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="N35" t="n">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="O35" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="P35" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="Q35" t="n">
         <v>3.2</v>
       </c>
       <c r="R35" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S35" t="n">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="T35" t="n">
-        <v>2.27</v>
+        <v>2.44</v>
       </c>
       <c r="U35" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="V35" t="n">
-        <v>5.1</v>
+        <v>5.75</v>
       </c>
       <c r="W35" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X35" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z35" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AB35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF35" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>2.55</v>
       </c>
       <c r="AG35" t="n">
         <v>1.3</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4705,61 +4705,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="M36" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O36" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S36" t="n">
         <v>3.5</v>
       </c>
-      <c r="N36" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O36" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S36" t="n">
-        <v>3.25</v>
-      </c>
       <c r="T36" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="U36" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="V36" t="n">
-        <v>5.45</v>
+        <v>5</v>
       </c>
       <c r="W36" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X36" t="n">
         <v>1.03</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z36" t="n">
-        <v>4</v>
+        <v>4.55</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.65</v>
+        <v>2.43</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="AE36" t="n">
         <v>1.5</v>
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="M37" t="n">
         <v>3.5</v>
       </c>
-      <c r="M37" t="n">
-        <v>3.25</v>
-      </c>
       <c r="N37" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="O37" t="n">
         <v>4</v>
       </c>
       <c r="P37" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R37" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S37" t="n">
         <v>2.88</v>
       </c>
       <c r="T37" t="n">
-        <v>2.3</v>
+        <v>2.69</v>
       </c>
       <c r="U37" t="n">
         <v>1.43</v>
       </c>
       <c r="V37" t="n">
-        <v>6.5</v>
+        <v>5.85</v>
       </c>
       <c r="W37" t="n">
         <v>1.07</v>
       </c>
       <c r="X37" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46010.67708333334</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.4</v>
+        <v>1.48</v>
       </c>
       <c r="M38" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="N38" t="n">
-        <v>2.08</v>
+        <v>5.7</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.65</v>
+        <v>2.45</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46010.6875</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="M39" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="N39" t="n">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="O39" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q39" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V39" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AB39" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC39" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46010.6875</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="M40" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N40" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="O40" t="n">
-        <v>2.94</v>
+        <v>3.38</v>
       </c>
       <c r="P40" t="n">
         <v>1.96</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="R40" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="S40" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="T40" t="n">
-        <v>3.28</v>
+        <v>2.97</v>
       </c>
       <c r="U40" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="V40" t="n">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="W40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X40" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AC40" t="n">
-        <v>4.33</v>
+        <v>3.58</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46010.6875</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.55</v>
+        <v>2.19</v>
       </c>
       <c r="M42" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="N42" t="n">
-        <v>2.4</v>
+        <v>3.39</v>
       </c>
       <c r="O42" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="P42" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="R42" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="S42" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="T42" t="n">
-        <v>2.97</v>
+        <v>3.36</v>
       </c>
       <c r="U42" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="V42" t="n">
-        <v>7.7</v>
+        <v>9</v>
       </c>
       <c r="W42" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X42" t="n">
         <v>1.02</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.92</v>
+        <v>2.75</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AC42" t="n">
-        <v>3.58</v>
+        <v>4.33</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46010.6875</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.48</v>
+        <v>2.7</v>
       </c>
       <c r="M43" t="n">
-        <v>4.9</v>
+        <v>2.9</v>
       </c>
       <c r="N43" t="n">
-        <v>5.76</v>
+        <v>2.4</v>
       </c>
       <c r="O43" t="n">
-        <v>1.85</v>
+        <v>3.3</v>
       </c>
       <c r="P43" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="Q43" t="n">
-        <v>5.75</v>
+        <v>3.26</v>
       </c>
       <c r="R43" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V43" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="AD43" t="n">
         <v>1.22</v>
       </c>
-      <c r="S43" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V43" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AE43" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46010.6875</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.93</v>
+        <v>2.26</v>
       </c>
       <c r="M44" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="N44" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="O44" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q44" t="n">
         <v>3.5</v>
       </c>
-      <c r="N44" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O44" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P44" t="n">
+      <c r="R44" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V44" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA44" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q44" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V44" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AB44" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.05</v>
+        <v>4.8</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.98</v>
+        <v>1.71</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46010.69791666666</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.32</v>
+        <v>1.86</v>
       </c>
       <c r="M45" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N45" t="n">
-        <v>3.2</v>
+        <v>3.77</v>
       </c>
       <c r="O45" t="n">
-        <v>2.9</v>
+        <v>2.27</v>
       </c>
       <c r="P45" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.8</v>
+        <v>5.95</v>
       </c>
       <c r="R45" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="S45" t="n">
-        <v>2.39</v>
+        <v>2.63</v>
       </c>
       <c r="T45" t="n">
-        <v>3.4</v>
+        <v>3.19</v>
       </c>
       <c r="U45" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="V45" t="n">
-        <v>9.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="W45" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X45" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AC45" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="AD45" t="n">
         <v>1.17</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46010.69791666666</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="M46" t="n">
-        <v>3.6</v>
+        <v>3.19</v>
       </c>
       <c r="N46" t="n">
-        <v>5.25</v>
+        <v>3.59</v>
       </c>
       <c r="O46" t="n">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="P46" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.75</v>
+        <v>4</v>
       </c>
       <c r="R46" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="S46" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="T46" t="n">
-        <v>3.16</v>
+        <v>2.85</v>
       </c>
       <c r="U46" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V46" t="n">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="W46" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X46" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.75</v>
+        <v>3.21</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46010.69791666666</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="M47" t="n">
-        <v>3.45</v>
+        <v>3.17</v>
       </c>
       <c r="N47" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="O47" t="n">
-        <v>2.58</v>
+        <v>2.28</v>
       </c>
       <c r="P47" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="R47" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S47" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="T47" t="n">
-        <v>2.85</v>
+        <v>2.76</v>
       </c>
       <c r="U47" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V47" t="n">
-        <v>7.1</v>
+        <v>6.85</v>
       </c>
       <c r="W47" t="n">
         <v>1.04</v>
       </c>
       <c r="X47" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.34</v>
+        <v>3.05</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46010.69791666666</v>
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="M48" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N48" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="O48" t="n">
         <v>3.3</v>
@@ -6148,13 +6148,13 @@
         <v>2.2</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="R48" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S48" t="n">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="T48" t="n">
         <v>2.85</v>
@@ -6163,7 +6163,7 @@
         <v>1.37</v>
       </c>
       <c r="V48" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="W48" t="n">
         <v>1.06</v>
@@ -6172,31 +6172,31 @@
         <v>1.05</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.6</v>
+        <v>3.29</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AF48" t="n">
         <v>2</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH48" t="n">
         <v>1.36</v>
@@ -6490,10 +6490,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="M51" t="n">
-        <v>3.25</v>
+        <v>3.09</v>
       </c>
       <c r="N51" t="n">
         <v>3</v>
@@ -6535,10 +6535,10 @@
         <v>2.9</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AC51" t="n">
         <v>4.1</v>
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="M52" t="n">
         <v>3.5</v>
       </c>
       <c r="N52" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="O52" t="n">
         <v>5.2</v>
@@ -6654,10 +6654,10 @@
         <v>3.4</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC52" t="n">
         <v>2.83</v>

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="M7" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="N7" t="n">
-        <v>3.32</v>
+        <v>3.27</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.43</v>
+        <v>1.93</v>
       </c>
       <c r="M18" t="n">
-        <v>3.04</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="O18" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="R18" t="n">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="S18" t="n">
-        <v>2.71</v>
+        <v>3.48</v>
       </c>
       <c r="T18" t="n">
-        <v>3.19</v>
+        <v>2.3</v>
       </c>
       <c r="U18" t="n">
-        <v>1.32</v>
+        <v>1.58</v>
       </c>
       <c r="V18" t="n">
-        <v>8.6</v>
+        <v>4.85</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.95</v>
+        <v>2.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.93</v>
+        <v>2.43</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="N21" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="P21" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="R21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.22</v>
       </c>
-      <c r="S21" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46010.58333333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,52 +3039,52 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="P22" t="n">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="S22" t="n">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="T22" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="U22" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="V22" t="n">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="W22" t="n">
         <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.58</v>
+        <v>4.33</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AB22" t="n">
         <v>2.15</v>
@@ -3099,13 +3099,13 @@
         <v>1.54</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AG22" t="n">
         <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46010.60416666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,52 +3158,52 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="O23" t="n">
-        <v>2.57</v>
+        <v>2.69</v>
       </c>
       <c r="P23" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="S23" t="n">
-        <v>2.99</v>
+        <v>3.15</v>
       </c>
       <c r="T23" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="V23" t="n">
-        <v>5.5</v>
+        <v>5.55</v>
       </c>
       <c r="W23" t="n">
         <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.33</v>
+        <v>4.58</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AB23" t="n">
         <v>2.15</v>
@@ -3218,13 +3218,13 @@
         <v>1.54</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AG23" t="n">
         <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46010.60416666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.7</v>
+        <v>2.65</v>
       </c>
       <c r="M26" t="n">
-        <v>3.75</v>
+        <v>3.22</v>
       </c>
       <c r="N26" t="n">
-        <v>3.75</v>
+        <v>2.37</v>
       </c>
       <c r="O26" t="n">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.47</v>
+        <v>3.1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="S26" t="n">
-        <v>3.25</v>
+        <v>2.73</v>
       </c>
       <c r="T26" t="n">
-        <v>2.41</v>
+        <v>2.85</v>
       </c>
       <c r="U26" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="V26" t="n">
-        <v>4.95</v>
+        <v>7</v>
       </c>
       <c r="W26" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.35</v>
+        <v>1.83</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.48</v>
+        <v>3.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46010.625</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.65</v>
+        <v>1.7</v>
       </c>
       <c r="M27" t="n">
-        <v>3.22</v>
+        <v>3.75</v>
       </c>
       <c r="N27" t="n">
-        <v>2.37</v>
+        <v>3.75</v>
       </c>
       <c r="O27" t="n">
-        <v>3.3</v>
+        <v>2.15</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.1</v>
+        <v>4.47</v>
       </c>
       <c r="R27" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="S27" t="n">
-        <v>2.73</v>
+        <v>3.25</v>
       </c>
       <c r="T27" t="n">
-        <v>2.85</v>
+        <v>2.41</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="V27" t="n">
-        <v>7</v>
+        <v>4.95</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.3</v>
+        <v>2.48</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46010.625</v>
@@ -3777,7 +3777,7 @@
         <v>3.12</v>
       </c>
       <c r="T28" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="U28" t="n">
         <v>1.5</v>
@@ -3792,10 +3792,10 @@
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.36</v>
+        <v>4.4</v>
       </c>
       <c r="AA28" t="n">
         <v>1.65</v>
@@ -3807,13 +3807,13 @@
         <v>2.43</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AG28" t="n">
         <v>1.22</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.15</v>
+        <v>2.41</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="N29" t="n">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="O29" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="P29" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="Q29" t="n">
         <v>3.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S29" t="n">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="T29" t="n">
-        <v>2.27</v>
+        <v>2.44</v>
       </c>
       <c r="U29" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="V29" t="n">
-        <v>5.1</v>
+        <v>5.75</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AB29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF29" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2.55</v>
       </c>
       <c r="AG29" t="n">
         <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="M31" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>3.45</v>
+        <v>2.85</v>
       </c>
       <c r="O31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB31" t="n">
         <v>2.3</v>
       </c>
-      <c r="P31" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U31" t="n">
+      <c r="AC31" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE31" t="n">
         <v>1.44</v>
       </c>
-      <c r="V31" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AF31" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="AG31" t="n">
         <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N33" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O33" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="P33" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="R33" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S33" t="n">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="T33" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="U33" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="V33" t="n">
-        <v>5.35</v>
+        <v>5.75</v>
       </c>
       <c r="W33" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X33" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AG33" t="n">
         <v>1.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.1</v>
+        <v>1.85</v>
       </c>
       <c r="M34" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="O34" t="n">
-        <v>1.44</v>
+        <v>2.4</v>
       </c>
       <c r="P34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S34" t="n">
         <v>3.3</v>
       </c>
-      <c r="Q34" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="S34" t="n">
-        <v>5.15</v>
-      </c>
       <c r="T34" t="n">
-        <v>1.71</v>
+        <v>2.38</v>
       </c>
       <c r="U34" t="n">
-        <v>2.14</v>
+        <v>1.48</v>
       </c>
       <c r="V34" t="n">
-        <v>3.12</v>
+        <v>5.35</v>
       </c>
       <c r="W34" t="n">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="Z34" t="n">
-        <v>9.6</v>
+        <v>3.9</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.16</v>
+        <v>1.7</v>
       </c>
       <c r="AB34" t="n">
-        <v>4.15</v>
+        <v>2.02</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.52</v>
+        <v>2.7</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>4.8</v>
+        <v>1.85</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.41</v>
+        <v>1.1</v>
       </c>
       <c r="M35" t="n">
-        <v>3.54</v>
+        <v>7.5</v>
       </c>
       <c r="N35" t="n">
-        <v>2.74</v>
+        <v>10</v>
       </c>
       <c r="O35" t="n">
-        <v>2.8</v>
+        <v>1.44</v>
       </c>
       <c r="P35" t="n">
-        <v>2.18</v>
+        <v>3.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.2</v>
+        <v>8.5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="S35" t="n">
-        <v>3.05</v>
+        <v>5.15</v>
       </c>
       <c r="T35" t="n">
-        <v>2.44</v>
+        <v>1.71</v>
       </c>
       <c r="U35" t="n">
-        <v>1.48</v>
+        <v>2.14</v>
       </c>
       <c r="V35" t="n">
-        <v>5.75</v>
+        <v>3.12</v>
       </c>
       <c r="W35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG35" t="n">
         <v>1.08</v>
       </c>
-      <c r="X35" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH35" t="n">
-        <v>1.53</v>
+        <v>4.8</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.12</v>
+        <v>3.64</v>
       </c>
       <c r="M36" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>2.89</v>
+        <v>1.79</v>
       </c>
       <c r="O36" t="n">
-        <v>2.49</v>
+        <v>4</v>
       </c>
       <c r="P36" t="n">
-        <v>2.42</v>
+        <v>2.13</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.14</v>
+        <v>2.38</v>
       </c>
       <c r="R36" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V36" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH36" t="n">
         <v>1.25</v>
-      </c>
-      <c r="S36" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V36" t="n">
-        <v>5</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.62</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46010.67708333334</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.64</v>
+        <v>2.12</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>1.79</v>
+        <v>2.89</v>
       </c>
       <c r="O37" t="n">
-        <v>4</v>
+        <v>2.73</v>
       </c>
       <c r="P37" t="n">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="R37" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S37" t="n">
-        <v>2.88</v>
+        <v>3.18</v>
       </c>
       <c r="T37" t="n">
-        <v>2.69</v>
+        <v>2.34</v>
       </c>
       <c r="U37" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="V37" t="n">
-        <v>5.85</v>
+        <v>5</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.77</v>
+        <v>4.4</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.96</v>
+        <v>2.43</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.04</v>
+        <v>2.41</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.93</v>
+        <v>1.3</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.23</v>
+        <v>1.62</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46010.67708333334</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.48</v>
+        <v>2.19</v>
       </c>
       <c r="M38" t="n">
-        <v>4.6</v>
+        <v>3.14</v>
       </c>
       <c r="N38" t="n">
-        <v>5.7</v>
+        <v>3.39</v>
       </c>
       <c r="O38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V38" t="n">
+        <v>9</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AF38" t="n">
         <v>1.85</v>
       </c>
-      <c r="P38" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>5</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V38" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>2.26</v>
-      </c>
       <c r="AG38" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46010.6875</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="M39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q39" t="n">
         <v>3.15</v>
       </c>
-      <c r="N39" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46010.6875</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="N40" t="n">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="O40" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46010.6875</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.13</v>
+        <v>1.48</v>
       </c>
       <c r="M41" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="N41" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46010.6875</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="M42" t="n">
-        <v>3.14</v>
+        <v>3.45</v>
       </c>
       <c r="N42" t="n">
-        <v>3.39</v>
+        <v>3</v>
       </c>
       <c r="O42" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AC42" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46010.6875</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.26</v>
+        <v>1.9</v>
       </c>
       <c r="M44" t="n">
-        <v>2.83</v>
+        <v>3.19</v>
       </c>
       <c r="N44" t="n">
-        <v>3.08</v>
+        <v>3.59</v>
       </c>
       <c r="O44" t="n">
-        <v>3.1</v>
+        <v>2.56</v>
       </c>
       <c r="P44" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R44" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="S44" t="n">
-        <v>2.39</v>
+        <v>2.69</v>
       </c>
       <c r="T44" t="n">
-        <v>3.6</v>
+        <v>2.85</v>
       </c>
       <c r="U44" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="V44" t="n">
-        <v>9.9</v>
+        <v>7.1</v>
       </c>
       <c r="W44" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X44" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.6</v>
+        <v>3.21</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AC44" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE44" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46010.69791666666</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.86</v>
+        <v>2.84</v>
       </c>
       <c r="M45" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N45" t="n">
-        <v>3.77</v>
+        <v>2.36</v>
       </c>
       <c r="O45" t="n">
-        <v>2.27</v>
+        <v>3.3</v>
       </c>
       <c r="P45" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V45" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA45" t="n">
         <v>2</v>
       </c>
-      <c r="Q45" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="R45" t="n">
+      <c r="AB45" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH45" t="n">
         <v>1.4</v>
-      </c>
-      <c r="S45" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T45" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V45" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>2.1</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46010.69791666666</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="M46" t="n">
-        <v>3.19</v>
+        <v>3.25</v>
       </c>
       <c r="N46" t="n">
-        <v>3.59</v>
+        <v>2.55</v>
       </c>
       <c r="O46" t="n">
-        <v>2.56</v>
+        <v>3.3</v>
       </c>
       <c r="P46" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q46" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="R46" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S46" t="n">
-        <v>2.69</v>
+        <v>2.99</v>
       </c>
       <c r="T46" t="n">
         <v>2.85</v>
       </c>
       <c r="U46" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V46" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="W46" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X46" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.65</v>
+        <v>3.29</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AG46" t="n">
         <v>1.25</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46010.69791666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.55</v>
+        <v>1.86</v>
       </c>
       <c r="M48" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N48" t="n">
-        <v>2.55</v>
+        <v>3.77</v>
       </c>
       <c r="O48" t="n">
-        <v>3.3</v>
+        <v>2.27</v>
       </c>
       <c r="P48" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V48" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE48" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q48" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V48" t="n">
-        <v>7</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AF48" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46010.69791666666</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.84</v>
+        <v>2.26</v>
       </c>
       <c r="M49" t="n">
-        <v>3.3</v>
+        <v>2.83</v>
       </c>
       <c r="N49" t="n">
-        <v>2.36</v>
+        <v>3.08</v>
       </c>
       <c r="O49" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P49" t="n">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="R49" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="S49" t="n">
-        <v>2.69</v>
+        <v>2.39</v>
       </c>
       <c r="T49" t="n">
-        <v>2.96</v>
+        <v>3.6</v>
       </c>
       <c r="U49" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="V49" t="n">
-        <v>7.5</v>
+        <v>9.9</v>
       </c>
       <c r="W49" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X49" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AA49" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AF49" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46010.69791666666</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.95</v>
+        <v>2.42</v>
       </c>
       <c r="M50" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="N50" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="O50" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="P50" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.6</v>
+        <v>3.96</v>
       </c>
       <c r="R50" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S50" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="T50" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U50" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V50" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="W50" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X50" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AB50" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH50" t="n">
         <v>1.6</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>1.8</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46010.70833333334</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,73 +6490,73 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.42</v>
+        <v>1.95</v>
       </c>
       <c r="M51" t="n">
-        <v>3.09</v>
+        <v>3.3</v>
       </c>
       <c r="N51" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="O51" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="P51" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.96</v>
+        <v>4.6</v>
       </c>
       <c r="R51" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S51" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="T51" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U51" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V51" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W51" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X51" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AC51" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46010.70833333334</v>

--- a/jogos_2025-12-19.xlsx
+++ b/jogos_2025-12-19.xlsx
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="M2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q2" t="n">
         <v>3.3</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3.1</v>
       </c>
       <c r="R2" t="n">
         <v>1.35</v>
@@ -683,43 +683,43 @@
         <v>2.94</v>
       </c>
       <c r="T2" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="U2" t="n">
         <v>1.4</v>
       </c>
       <c r="V2" t="n">
-        <v>6.9</v>
+        <v>6.85</v>
       </c>
       <c r="W2" t="n">
         <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z2" t="n">
         <v>3.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="AD2" t="n">
         <v>1.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AG2" t="n">
         <v>1.3</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Western Sydney Wanderers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>1.76</v>
+        <v>2.35</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE3" t="n">
         <v>1.67</v>
       </c>
-      <c r="AB3" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46010.25</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Western Sydney Wanderers</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="M4" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>2.6</v>
+        <v>1.76</v>
       </c>
       <c r="O4" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46010.25</v>
@@ -1016,64 +1016,64 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="M5" t="n">
         <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="O5" t="n">
-        <v>4.5</v>
+        <v>4.97</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
         <v>1.21</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AF5" t="n">
         <v>1.89</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1739,22 +1739,22 @@
         <v>2.68</v>
       </c>
       <c r="O11" t="n">
-        <v>3.46</v>
+        <v>3.62</v>
       </c>
       <c r="P11" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S11" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="T11" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="U11" t="n">
         <v>1.2</v>
@@ -1766,7 +1766,7 @@
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y11" t="n">
         <v>1.53</v>
@@ -1775,25 +1775,25 @@
         <v>2.35</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
         <v>1.36</v>
@@ -2325,40 +2325,40 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M16" t="n">
         <v>4.5</v>
       </c>
       <c r="N16" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="O16" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="P16" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="R16" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="S16" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="T16" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="U16" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="V16" t="n">
-        <v>6.4</v>
+        <v>5.85</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
@@ -2367,28 +2367,28 @@
         <v>1.26</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.2</v>
+        <v>2.96</v>
       </c>
       <c r="AH16" t="n">
         <v>1.06</v>
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>5.71</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46010.54166666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.93</v>
+        <v>2.44</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="N18" t="n">
-        <v>3.33</v>
+        <v>2.99</v>
       </c>
       <c r="O18" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="R18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V18" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.22</v>
       </c>
-      <c r="S18" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V18" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="AE18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.8</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.68</v>
+        <v>2.36</v>
       </c>
       <c r="M19" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O19" t="n">
         <v>3.6</v>
       </c>
-      <c r="N19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.15</v>
-      </c>
       <c r="P19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S19" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q19" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.65</v>
-      </c>
       <c r="T19" t="n">
-        <v>2.99</v>
+        <v>3.7</v>
       </c>
       <c r="U19" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="V19" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="W19" t="n">
         <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.04</v>
+        <v>2.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.55</v>
+        <v>5.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.1</v>
+        <v>1.41</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46010.58333333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.43</v>
+        <v>1.87</v>
       </c>
       <c r="M21" t="n">
-        <v>3.04</v>
+        <v>3.62</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>3.46</v>
       </c>
       <c r="O21" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="S21" t="n">
-        <v>2.71</v>
+        <v>3.34</v>
       </c>
       <c r="T21" t="n">
-        <v>3.19</v>
+        <v>2.25</v>
       </c>
       <c r="U21" t="n">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="V21" t="n">
-        <v>8.6</v>
+        <v>5.05</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.88</v>
+        <v>4.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.2</v>
+        <v>1.52</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>2.26</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.95</v>
+        <v>2.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46010.58333333334</v>
@@ -3039,22 +3039,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="M22" t="n">
-        <v>3.7</v>
+        <v>3.02</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>3.83</v>
       </c>
       <c r="O22" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="R22" t="n">
         <v>1.34</v>
@@ -3063,46 +3063,46 @@
         <v>2.99</v>
       </c>
       <c r="T22" t="n">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="U22" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="V22" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X22" t="n">
         <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.33</v>
+        <v>4.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
         <v>1.75</v>
@@ -3158,67 +3158,67 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="N23" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="O23" t="n">
         <v>2.69</v>
       </c>
       <c r="P23" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="R23" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T23" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="U23" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="V23" t="n">
-        <v>5.55</v>
+        <v>5.6</v>
       </c>
       <c r="W23" t="n">
         <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.58</v>
+        <v>4.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="AD23" t="n">
         <v>1.44</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="AG23" t="n">
         <v>1.3</v>
@@ -3405,40 +3405,40 @@
         <v>3.8</v>
       </c>
       <c r="O25" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="P25" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="R25" t="n">
         <v>1.41</v>
       </c>
       <c r="S25" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="T25" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="U25" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V25" t="n">
         <v>8.1</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X25" t="n">
         <v>1.07</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="AA25" t="n">
         <v>2.15</v>
@@ -3447,22 +3447,22 @@
         <v>1.63</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.1</v>
+        <v>3.94</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE25" t="n">
         <v>1.89</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46010.61458333334</v>
@@ -3515,31 +3515,31 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="M26" t="n">
-        <v>3.22</v>
+        <v>2.94</v>
       </c>
       <c r="N26" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="O26" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="R26" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S26" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="T26" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
         <v>1.36</v>
@@ -3554,34 +3554,34 @@
         <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46010.625</v>
@@ -3634,67 +3634,67 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="M27" t="n">
         <v>3.75</v>
       </c>
       <c r="N27" t="n">
-        <v>3.75</v>
+        <v>3.94</v>
       </c>
       <c r="O27" t="n">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="P27" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.47</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S27" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="T27" t="n">
-        <v>2.41</v>
+        <v>2.29</v>
       </c>
       <c r="U27" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="V27" t="n">
-        <v>4.95</v>
+        <v>5.05</v>
       </c>
       <c r="W27" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X27" t="n">
         <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AA27" t="n">
         <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AC27" t="n">
         <v>2.48</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AG27" t="n">
         <v>1.25</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V29" t="n">
+        <v>5</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC29" t="n">
         <v>2.41</v>
       </c>
-      <c r="M29" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V29" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AD29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE29" t="n">
         <v>1.44</v>
       </c>
-      <c r="AE29" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AF29" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AG29" t="n">
         <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46010.66666666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5.8</v>
+        <v>1.34</v>
       </c>
       <c r="M30" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="N30" t="n">
-        <v>1.37</v>
+        <v>8.5</v>
       </c>
       <c r="O30" t="n">
-        <v>6.5</v>
+        <v>1.67</v>
       </c>
       <c r="P30" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.73</v>
+        <v>6</v>
       </c>
       <c r="R30" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>3.78</v>
+        <v>4.33</v>
       </c>
       <c r="T30" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="U30" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="V30" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="W30" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Z30" t="n">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="AA30" t="n">
         <v>1.36</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AF30" t="n">
         <v>2.25</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.11</v>
+        <v>2.98</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.15</v>
+        <v>1.18</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>7.25</v>
       </c>
       <c r="N31" t="n">
-        <v>2.85</v>
+        <v>10</v>
       </c>
       <c r="O31" t="n">
-        <v>2.7</v>
+        <v>1.44</v>
       </c>
       <c r="P31" t="n">
-        <v>2.45</v>
+        <v>3.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.2</v>
+        <v>8.5</v>
       </c>
       <c r="R31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V31" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="W31" t="n">
         <v>1.28</v>
       </c>
-      <c r="S31" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U31" t="n">
+      <c r="X31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC31" t="n">
         <v>1.55</v>
       </c>
-      <c r="V31" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB31" t="n">
+      <c r="AD31" t="n">
         <v>2.3</v>
       </c>
-      <c r="AC31" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AE31" t="n">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.65</v>
+        <v>4.5</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46010.66666666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.3</v>
+        <v>6.6</v>
       </c>
       <c r="M32" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="N32" t="n">
-        <v>7.25</v>
+        <v>1.34</v>
       </c>
       <c r="O32" t="n">
-        <v>1.73</v>
+        <v>5.85</v>
       </c>
       <